--- a/a_CI/APS_A.xlsx
+++ b/a_CI/APS_A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74558E63-688B-4D01-BE30-B39B534E5325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C562F8B0-EC42-4CDC-8E65-FA31EDE3CFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentacao" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="38">
   <si>
     <t>DISPLAY (bool)</t>
   </si>
@@ -118,9 +118,6 @@
     <t>SIMULAÇÃO - Transistor  (print)</t>
   </si>
   <si>
-    <t>V = ¬ABC + BC¬D + AC¬D + A¬BD</t>
-  </si>
-  <si>
     <t>V = (AC + BD)(¬A + ¬B + ¬C + ¬D)</t>
   </si>
   <si>
@@ -138,14 +135,14 @@
 3) https://youtu.be/t2BxfgsAuno </t>
   </si>
   <si>
-    <t>Link: https://encurtador.com.br/KJCd</t>
+    <t>V = ¬ABD + B¬CD + AC¬D + A¬BC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -175,14 +172,6 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -392,9 +381,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -477,28 +466,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
@@ -506,12 +484,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -571,8 +557,8 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>2948</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>197183</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2654300" cy="2165685"/>
     <xdr:pic>
@@ -594,7 +580,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6753412" y="3394595"/>
+          <a:off x="6747711" y="3154946"/>
           <a:ext cx="2654300" cy="2165685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -810,22 +796,22 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AD1000"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" customWidth="1"/>
-    <col min="4" max="4" width="2.6328125" customWidth="1"/>
-    <col min="5" max="5" width="63.453125" customWidth="1"/>
-    <col min="6" max="6" width="2.6328125" customWidth="1"/>
-    <col min="10" max="10" width="2.6328125" customWidth="1"/>
-    <col min="11" max="15" width="6.7265625" customWidth="1"/>
-    <col min="16" max="16" width="3.08984375" customWidth="1"/>
-    <col min="17" max="17" width="2.26953125" customWidth="1"/>
-    <col min="18" max="18" width="2.08984375" customWidth="1"/>
-    <col min="19" max="21" width="2.26953125" customWidth="1"/>
-    <col min="22" max="22" width="2.08984375" customWidth="1"/>
-    <col min="23" max="23" width="2.26953125" customWidth="1"/>
-    <col min="24" max="29" width="6.7265625" customWidth="1"/>
-    <col min="30" max="30" width="3.6328125" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" customWidth="1"/>
+    <col min="5" max="5" width="63.44140625" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" customWidth="1"/>
+    <col min="11" max="15" width="6.77734375" customWidth="1"/>
+    <col min="16" max="16" width="3.109375" customWidth="1"/>
+    <col min="17" max="17" width="2.21875" customWidth="1"/>
+    <col min="18" max="18" width="2.109375" customWidth="1"/>
+    <col min="19" max="21" width="2.21875" customWidth="1"/>
+    <col min="22" max="22" width="2.109375" customWidth="1"/>
+    <col min="23" max="23" width="2.21875" customWidth="1"/>
+    <col min="24" max="29" width="6.77734375" customWidth="1"/>
+    <col min="30" max="30" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -845,41 +831,41 @@
     </row>
     <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="1"/>
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="32"/>
       <c r="J2" s="2"/>
       <c r="K2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="32"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="32"/>
       <c r="AD2" s="1"/>
     </row>
-    <row r="3" spans="1:30" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -889,10 +875,10 @@
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="43" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="35"/>
@@ -946,7 +932,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="41"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="35"/>
       <c r="I4" s="36"/>
       <c r="K4" s="17" t="s">
@@ -997,7 +983,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="42"/>
+      <c r="G5" s="37"/>
       <c r="H5" s="35"/>
       <c r="I5" s="36"/>
       <c r="K5" s="17" t="s">
@@ -1047,7 +1033,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="42"/>
+      <c r="G6" s="37"/>
       <c r="H6" s="35"/>
       <c r="I6" s="36"/>
       <c r="K6" s="17" t="s">
@@ -1098,7 +1084,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="42"/>
+      <c r="G7" s="37"/>
       <c r="H7" s="35"/>
       <c r="I7" s="36"/>
       <c r="K7" s="23" t="s">
@@ -1149,16 +1135,16 @@
         <v>21</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="42"/>
+      <c r="G8" s="37"/>
       <c r="H8" s="35"/>
       <c r="I8" s="36"/>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="19" t="s">
         <v>17</v>
@@ -1190,16 +1176,16 @@
       <c r="D9" s="1"/>
       <c r="E9" s="22"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="42"/>
+      <c r="G9" s="37"/>
       <c r="H9" s="35"/>
       <c r="I9" s="36"/>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="12">
         <v>0</v>
@@ -1233,16 +1219,16 @@
         <v>24</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="42"/>
+      <c r="G10" s="37"/>
       <c r="H10" s="35"/>
       <c r="I10" s="36"/>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="19" t="s">
         <v>17</v>
@@ -1276,7 +1262,7 @@
         <v>26</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="42"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="35"/>
       <c r="I11" s="36"/>
       <c r="K11" s="8" t="s">
@@ -1325,7 +1311,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="22"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="42"/>
+      <c r="G12" s="37"/>
       <c r="H12" s="35"/>
       <c r="I12" s="36"/>
       <c r="K12" s="17" t="s">
@@ -1376,7 +1362,7 @@
         <v>27</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="42"/>
+      <c r="G13" s="37"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
       <c r="K13" s="17" t="s">
@@ -1427,9 +1413,9 @@
         <v>28</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="45"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
       <c r="K14" s="17" t="s">
         <v>11</v>
       </c>
@@ -1526,18 +1512,18 @@
         <v>30</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46"/>
       <c r="K16" s="33" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="19" t="s">
         <v>18</v>
@@ -1569,16 +1555,16 @@
       <c r="D17" s="1"/>
       <c r="E17" s="28"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="41"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
       <c r="K17" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="32"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="19" t="s">
         <v>18</v>
@@ -1609,16 +1595,16 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="42"/>
+      <c r="G18" s="37"/>
       <c r="H18" s="35"/>
       <c r="I18" s="36"/>
-      <c r="K18" s="37" t="s">
-        <v>34</v>
+      <c r="K18" s="30" t="s">
+        <v>33</v>
       </c>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="32"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="19" t="s">
         <v>18</v>
@@ -1649,7 +1635,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="42"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="35"/>
       <c r="I19" s="36"/>
       <c r="K19" s="8" t="s">
@@ -1697,7 +1683,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="42"/>
+      <c r="G20" s="37"/>
       <c r="H20" s="35"/>
       <c r="I20" s="36"/>
       <c r="K20" s="17" t="s">
@@ -1731,7 +1717,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="42"/>
+      <c r="G21" s="37"/>
       <c r="H21" s="35"/>
       <c r="I21" s="36"/>
       <c r="K21" s="17" t="s">
@@ -1760,7 +1746,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="42"/>
+      <c r="G22" s="37"/>
       <c r="H22" s="35"/>
       <c r="I22" s="36"/>
       <c r="K22" s="17" t="s">
@@ -1789,7 +1775,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="42"/>
+      <c r="G23" s="37"/>
       <c r="H23" s="35"/>
       <c r="I23" s="36"/>
       <c r="K23" s="23" t="s">
@@ -1818,16 +1804,16 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="42"/>
+      <c r="G24" s="37"/>
       <c r="H24" s="35"/>
       <c r="I24" s="36"/>
       <c r="K24" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -1839,16 +1825,16 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="42"/>
+      <c r="G25" s="37"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="K25" s="46" t="s">
-        <v>36</v>
+      <c r="K25" s="41" t="s">
+        <v>35</v>
       </c>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -1860,7 +1846,7 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="42"/>
+      <c r="G26" s="37"/>
       <c r="H26" s="35"/>
       <c r="I26" s="36"/>
       <c r="K26" s="1"/>
@@ -1879,9 +1865,9 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
       <c r="R27" s="1"/>
       <c r="AD27" s="1"/>
     </row>
@@ -1892,9 +1878,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
-      <c r="G28" s="47" t="s">
-        <v>38</v>
-      </c>
+      <c r="G28" s="28"/>
       <c r="H28" s="28"/>
       <c r="I28" s="28"/>
       <c r="R28" s="1"/>
@@ -2004,7 +1988,7 @@
       <c r="R36" s="1"/>
       <c r="AD36" s="1"/>
     </row>
-    <row r="37" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2017,7 +2001,7 @@
       <c r="R37" s="1"/>
       <c r="AD37" s="1"/>
     </row>
-    <row r="38" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2030,7 +2014,7 @@
       <c r="R38" s="1"/>
       <c r="AD38" s="1"/>
     </row>
-    <row r="39" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2043,7 +2027,7 @@
       <c r="R39" s="1"/>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2056,7 +2040,7 @@
       <c r="R40" s="1"/>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2066,7 +2050,7 @@
       <c r="R41" s="1"/>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2076,7 +2060,7 @@
       <c r="R42" s="1"/>
       <c r="AD42" s="1"/>
     </row>
-    <row r="43" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2086,7 +2070,7 @@
       <c r="R43" s="1"/>
       <c r="AD43" s="1"/>
     </row>
-    <row r="44" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2096,7 +2080,7 @@
       <c r="R44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
-    <row r="45" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2106,7 +2090,7 @@
       <c r="R45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2116,7 +2100,7 @@
       <c r="R46" s="1"/>
       <c r="AD46" s="1"/>
     </row>
-    <row r="47" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2126,7 +2110,7 @@
       <c r="R47" s="1"/>
       <c r="AD47" s="1"/>
     </row>
-    <row r="48" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2136,7 +2120,7 @@
       <c r="R48" s="1"/>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2146,7 +2130,7 @@
       <c r="R49" s="1"/>
       <c r="AD49" s="1"/>
     </row>
-    <row r="50" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2156,7 +2140,7 @@
       <c r="R50" s="1"/>
       <c r="AD50" s="1"/>
     </row>
-    <row r="51" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2166,7 +2150,7 @@
       <c r="R51" s="1"/>
       <c r="AD51" s="1"/>
     </row>
-    <row r="52" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2198,7 +2182,7 @@
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2230,7 +2214,7 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
     </row>
-    <row r="54" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2262,7 +2246,7 @@
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2294,7 +2278,7 @@
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
     </row>
-    <row r="56" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2326,7 +2310,7 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
     </row>
-    <row r="57" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2358,7 +2342,7 @@
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
     </row>
-    <row r="58" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2390,7 +2374,7 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
     </row>
-    <row r="59" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2422,7 +2406,7 @@
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
     </row>
-    <row r="60" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2454,7 +2438,7 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
     </row>
-    <row r="61" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2486,7 +2470,7 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
     </row>
-    <row r="62" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2518,7 +2502,7 @@
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
     </row>
-    <row r="63" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2550,7 +2534,7 @@
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
     </row>
-    <row r="64" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2582,7 +2566,7 @@
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
     </row>
-    <row r="65" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2614,7 +2598,7 @@
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
     </row>
-    <row r="66" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2646,7 +2630,7 @@
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
     </row>
-    <row r="67" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2678,7 +2662,7 @@
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
     </row>
-    <row r="68" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2710,7 +2694,7 @@
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
     </row>
-    <row r="69" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2742,7 +2726,7 @@
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
     </row>
-    <row r="70" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2774,7 +2758,7 @@
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
     </row>
-    <row r="71" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2806,7 +2790,7 @@
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
     </row>
-    <row r="72" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2838,7 +2822,7 @@
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
     </row>
-    <row r="73" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2870,7 +2854,7 @@
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
     </row>
-    <row r="74" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2902,7 +2886,7 @@
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
     </row>
-    <row r="75" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2934,7 +2918,7 @@
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
     </row>
-    <row r="76" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2966,7 +2950,7 @@
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
     </row>
-    <row r="77" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2998,7 +2982,7 @@
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
     </row>
-    <row r="78" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3030,7 +3014,7 @@
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
     </row>
-    <row r="79" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3062,7 +3046,7 @@
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
     </row>
-    <row r="80" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3094,7 +3078,7 @@
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
     </row>
-    <row r="81" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3126,7 +3110,7 @@
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
     </row>
-    <row r="82" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3158,7 +3142,7 @@
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
     </row>
-    <row r="83" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3190,7 +3174,7 @@
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
     </row>
-    <row r="84" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3222,7 +3206,7 @@
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
     </row>
-    <row r="85" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3254,7 +3238,7 @@
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
     </row>
-    <row r="86" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3286,7 +3270,7 @@
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
     </row>
-    <row r="87" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3318,7 +3302,7 @@
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
     </row>
-    <row r="88" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3350,7 +3334,7 @@
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
     </row>
-    <row r="89" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3382,7 +3366,7 @@
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
     </row>
-    <row r="90" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3414,7 +3398,7 @@
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
     </row>
-    <row r="91" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3446,7 +3430,7 @@
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
     </row>
-    <row r="92" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3478,7 +3462,7 @@
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
     </row>
-    <row r="93" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3510,7 +3494,7 @@
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
     </row>
-    <row r="94" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3542,7 +3526,7 @@
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
     </row>
-    <row r="95" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3574,7 +3558,7 @@
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
     </row>
-    <row r="96" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3606,7 +3590,7 @@
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
     </row>
-    <row r="97" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3638,7 +3622,7 @@
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
     </row>
-    <row r="98" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3670,7 +3654,7 @@
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
     </row>
-    <row r="99" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3702,7 +3686,7 @@
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
     </row>
-    <row r="100" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3734,7 +3718,7 @@
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
     </row>
-    <row r="101" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3766,7 +3750,7 @@
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
     </row>
-    <row r="102" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3798,7 +3782,7 @@
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
     </row>
-    <row r="103" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3830,7 +3814,7 @@
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
     </row>
-    <row r="104" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3862,7 +3846,7 @@
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
     </row>
-    <row r="105" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3894,7 +3878,7 @@
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
     </row>
-    <row r="106" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3926,7 +3910,7 @@
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
     </row>
-    <row r="107" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3958,7 +3942,7 @@
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
     </row>
-    <row r="108" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3990,7 +3974,7 @@
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
     </row>
-    <row r="109" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4022,7 +4006,7 @@
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
     </row>
-    <row r="110" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4054,7 +4038,7 @@
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
     </row>
-    <row r="111" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4086,7 +4070,7 @@
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
     </row>
-    <row r="112" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4118,7 +4102,7 @@
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
     </row>
-    <row r="113" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4150,7 +4134,7 @@
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
     </row>
-    <row r="114" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4182,7 +4166,7 @@
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
     </row>
-    <row r="115" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4214,7 +4198,7 @@
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
     </row>
-    <row r="116" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4246,7 +4230,7 @@
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
     </row>
-    <row r="117" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4278,7 +4262,7 @@
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
     </row>
-    <row r="118" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4310,7 +4294,7 @@
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
     </row>
-    <row r="119" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4342,7 +4326,7 @@
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
     </row>
-    <row r="120" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4374,7 +4358,7 @@
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
     </row>
-    <row r="121" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4406,7 +4390,7 @@
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
     </row>
-    <row r="122" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4438,7 +4422,7 @@
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
     </row>
-    <row r="123" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4470,7 +4454,7 @@
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
     </row>
-    <row r="124" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4502,7 +4486,7 @@
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
     </row>
-    <row r="125" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4534,7 +4518,7 @@
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
     </row>
-    <row r="126" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4566,7 +4550,7 @@
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
     </row>
-    <row r="127" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4598,7 +4582,7 @@
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
     </row>
-    <row r="128" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4630,7 +4614,7 @@
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
     </row>
-    <row r="129" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4662,7 +4646,7 @@
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
     </row>
-    <row r="130" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4694,7 +4678,7 @@
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
     </row>
-    <row r="131" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4726,7 +4710,7 @@
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
     </row>
-    <row r="132" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4758,7 +4742,7 @@
       <c r="AC132" s="1"/>
       <c r="AD132" s="1"/>
     </row>
-    <row r="133" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4790,7 +4774,7 @@
       <c r="AC133" s="1"/>
       <c r="AD133" s="1"/>
     </row>
-    <row r="134" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4822,7 +4806,7 @@
       <c r="AC134" s="1"/>
       <c r="AD134" s="1"/>
     </row>
-    <row r="135" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4854,7 +4838,7 @@
       <c r="AC135" s="1"/>
       <c r="AD135" s="1"/>
     </row>
-    <row r="136" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4886,7 +4870,7 @@
       <c r="AC136" s="1"/>
       <c r="AD136" s="1"/>
     </row>
-    <row r="137" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4918,7 +4902,7 @@
       <c r="AC137" s="1"/>
       <c r="AD137" s="1"/>
     </row>
-    <row r="138" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4950,7 +4934,7 @@
       <c r="AC138" s="1"/>
       <c r="AD138" s="1"/>
     </row>
-    <row r="139" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4982,7 +4966,7 @@
       <c r="AC139" s="1"/>
       <c r="AD139" s="1"/>
     </row>
-    <row r="140" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5014,7 +4998,7 @@
       <c r="AC140" s="1"/>
       <c r="AD140" s="1"/>
     </row>
-    <row r="141" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5046,7 +5030,7 @@
       <c r="AC141" s="1"/>
       <c r="AD141" s="1"/>
     </row>
-    <row r="142" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5078,7 +5062,7 @@
       <c r="AC142" s="1"/>
       <c r="AD142" s="1"/>
     </row>
-    <row r="143" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5110,7 +5094,7 @@
       <c r="AC143" s="1"/>
       <c r="AD143" s="1"/>
     </row>
-    <row r="144" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5142,7 +5126,7 @@
       <c r="AC144" s="1"/>
       <c r="AD144" s="1"/>
     </row>
-    <row r="145" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5174,7 +5158,7 @@
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
     </row>
-    <row r="146" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5206,7 +5190,7 @@
       <c r="AC146" s="1"/>
       <c r="AD146" s="1"/>
     </row>
-    <row r="147" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5238,7 +5222,7 @@
       <c r="AC147" s="1"/>
       <c r="AD147" s="1"/>
     </row>
-    <row r="148" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5270,7 +5254,7 @@
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
     </row>
-    <row r="149" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5302,7 +5286,7 @@
       <c r="AC149" s="1"/>
       <c r="AD149" s="1"/>
     </row>
-    <row r="150" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5334,7 +5318,7 @@
       <c r="AC150" s="1"/>
       <c r="AD150" s="1"/>
     </row>
-    <row r="151" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5366,7 +5350,7 @@
       <c r="AC151" s="1"/>
       <c r="AD151" s="1"/>
     </row>
-    <row r="152" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5398,7 +5382,7 @@
       <c r="AC152" s="1"/>
       <c r="AD152" s="1"/>
     </row>
-    <row r="153" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5430,7 +5414,7 @@
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
     </row>
-    <row r="154" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5462,7 +5446,7 @@
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
     </row>
-    <row r="155" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5494,7 +5478,7 @@
       <c r="AC155" s="1"/>
       <c r="AD155" s="1"/>
     </row>
-    <row r="156" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5526,7 +5510,7 @@
       <c r="AC156" s="1"/>
       <c r="AD156" s="1"/>
     </row>
-    <row r="157" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5558,7 +5542,7 @@
       <c r="AC157" s="1"/>
       <c r="AD157" s="1"/>
     </row>
-    <row r="158" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5590,7 +5574,7 @@
       <c r="AC158" s="1"/>
       <c r="AD158" s="1"/>
     </row>
-    <row r="159" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5622,7 +5606,7 @@
       <c r="AC159" s="1"/>
       <c r="AD159" s="1"/>
     </row>
-    <row r="160" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5654,7 +5638,7 @@
       <c r="AC160" s="1"/>
       <c r="AD160" s="1"/>
     </row>
-    <row r="161" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5686,7 +5670,7 @@
       <c r="AC161" s="1"/>
       <c r="AD161" s="1"/>
     </row>
-    <row r="162" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5718,7 +5702,7 @@
       <c r="AC162" s="1"/>
       <c r="AD162" s="1"/>
     </row>
-    <row r="163" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5750,7 +5734,7 @@
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
     </row>
-    <row r="164" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5782,7 +5766,7 @@
       <c r="AC164" s="1"/>
       <c r="AD164" s="1"/>
     </row>
-    <row r="165" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5814,7 +5798,7 @@
       <c r="AC165" s="1"/>
       <c r="AD165" s="1"/>
     </row>
-    <row r="166" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5846,7 +5830,7 @@
       <c r="AC166" s="1"/>
       <c r="AD166" s="1"/>
     </row>
-    <row r="167" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5878,7 +5862,7 @@
       <c r="AC167" s="1"/>
       <c r="AD167" s="1"/>
     </row>
-    <row r="168" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5910,7 +5894,7 @@
       <c r="AC168" s="1"/>
       <c r="AD168" s="1"/>
     </row>
-    <row r="169" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5942,7 +5926,7 @@
       <c r="AC169" s="1"/>
       <c r="AD169" s="1"/>
     </row>
-    <row r="170" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5974,7 +5958,7 @@
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
     </row>
-    <row r="171" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6006,7 +5990,7 @@
       <c r="AC171" s="1"/>
       <c r="AD171" s="1"/>
     </row>
-    <row r="172" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6038,7 +6022,7 @@
       <c r="AC172" s="1"/>
       <c r="AD172" s="1"/>
     </row>
-    <row r="173" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6070,7 +6054,7 @@
       <c r="AC173" s="1"/>
       <c r="AD173" s="1"/>
     </row>
-    <row r="174" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6102,7 +6086,7 @@
       <c r="AC174" s="1"/>
       <c r="AD174" s="1"/>
     </row>
-    <row r="175" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6134,7 +6118,7 @@
       <c r="AC175" s="1"/>
       <c r="AD175" s="1"/>
     </row>
-    <row r="176" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6166,7 +6150,7 @@
       <c r="AC176" s="1"/>
       <c r="AD176" s="1"/>
     </row>
-    <row r="177" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6198,7 +6182,7 @@
       <c r="AC177" s="1"/>
       <c r="AD177" s="1"/>
     </row>
-    <row r="178" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6230,7 +6214,7 @@
       <c r="AC178" s="1"/>
       <c r="AD178" s="1"/>
     </row>
-    <row r="179" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6262,7 +6246,7 @@
       <c r="AC179" s="1"/>
       <c r="AD179" s="1"/>
     </row>
-    <row r="180" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6294,7 +6278,7 @@
       <c r="AC180" s="1"/>
       <c r="AD180" s="1"/>
     </row>
-    <row r="181" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6326,7 +6310,7 @@
       <c r="AC181" s="1"/>
       <c r="AD181" s="1"/>
     </row>
-    <row r="182" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6358,7 +6342,7 @@
       <c r="AC182" s="1"/>
       <c r="AD182" s="1"/>
     </row>
-    <row r="183" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6390,7 +6374,7 @@
       <c r="AC183" s="1"/>
       <c r="AD183" s="1"/>
     </row>
-    <row r="184" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6422,7 +6406,7 @@
       <c r="AC184" s="1"/>
       <c r="AD184" s="1"/>
     </row>
-    <row r="185" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6454,7 +6438,7 @@
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
     </row>
-    <row r="186" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6486,7 +6470,7 @@
       <c r="AC186" s="1"/>
       <c r="AD186" s="1"/>
     </row>
-    <row r="187" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6518,7 +6502,7 @@
       <c r="AC187" s="1"/>
       <c r="AD187" s="1"/>
     </row>
-    <row r="188" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6550,7 +6534,7 @@
       <c r="AC188" s="1"/>
       <c r="AD188" s="1"/>
     </row>
-    <row r="189" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6582,7 +6566,7 @@
       <c r="AC189" s="1"/>
       <c r="AD189" s="1"/>
     </row>
-    <row r="190" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6614,7 +6598,7 @@
       <c r="AC190" s="1"/>
       <c r="AD190" s="1"/>
     </row>
-    <row r="191" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6646,7 +6630,7 @@
       <c r="AC191" s="1"/>
       <c r="AD191" s="1"/>
     </row>
-    <row r="192" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6678,7 +6662,7 @@
       <c r="AC192" s="1"/>
       <c r="AD192" s="1"/>
     </row>
-    <row r="193" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6710,7 +6694,7 @@
       <c r="AC193" s="1"/>
       <c r="AD193" s="1"/>
     </row>
-    <row r="194" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6742,7 +6726,7 @@
       <c r="AC194" s="1"/>
       <c r="AD194" s="1"/>
     </row>
-    <row r="195" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6774,7 +6758,7 @@
       <c r="AC195" s="1"/>
       <c r="AD195" s="1"/>
     </row>
-    <row r="196" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6806,7 +6790,7 @@
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
     </row>
-    <row r="197" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6838,7 +6822,7 @@
       <c r="AC197" s="1"/>
       <c r="AD197" s="1"/>
     </row>
-    <row r="198" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6870,7 +6854,7 @@
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
     </row>
-    <row r="199" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6902,7 +6886,7 @@
       <c r="AC199" s="1"/>
       <c r="AD199" s="1"/>
     </row>
-    <row r="200" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6934,7 +6918,7 @@
       <c r="AC200" s="1"/>
       <c r="AD200" s="1"/>
     </row>
-    <row r="201" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6966,7 +6950,7 @@
       <c r="AC201" s="1"/>
       <c r="AD201" s="1"/>
     </row>
-    <row r="202" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6998,7 +6982,7 @@
       <c r="AC202" s="1"/>
       <c r="AD202" s="1"/>
     </row>
-    <row r="203" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7030,7 +7014,7 @@
       <c r="AC203" s="1"/>
       <c r="AD203" s="1"/>
     </row>
-    <row r="204" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7062,7 +7046,7 @@
       <c r="AC204" s="1"/>
       <c r="AD204" s="1"/>
     </row>
-    <row r="205" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7094,7 +7078,7 @@
       <c r="AC205" s="1"/>
       <c r="AD205" s="1"/>
     </row>
-    <row r="206" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7126,7 +7110,7 @@
       <c r="AC206" s="1"/>
       <c r="AD206" s="1"/>
     </row>
-    <row r="207" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7158,7 +7142,7 @@
       <c r="AC207" s="1"/>
       <c r="AD207" s="1"/>
     </row>
-    <row r="208" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7190,7 +7174,7 @@
       <c r="AC208" s="1"/>
       <c r="AD208" s="1"/>
     </row>
-    <row r="209" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7222,7 +7206,7 @@
       <c r="AC209" s="1"/>
       <c r="AD209" s="1"/>
     </row>
-    <row r="210" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7254,7 +7238,7 @@
       <c r="AC210" s="1"/>
       <c r="AD210" s="1"/>
     </row>
-    <row r="211" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7286,7 +7270,7 @@
       <c r="AC211" s="1"/>
       <c r="AD211" s="1"/>
     </row>
-    <row r="212" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7318,7 +7302,7 @@
       <c r="AC212" s="1"/>
       <c r="AD212" s="1"/>
     </row>
-    <row r="213" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7350,7 +7334,7 @@
       <c r="AC213" s="1"/>
       <c r="AD213" s="1"/>
     </row>
-    <row r="214" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7382,7 +7366,7 @@
       <c r="AC214" s="1"/>
       <c r="AD214" s="1"/>
     </row>
-    <row r="215" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7414,7 +7398,7 @@
       <c r="AC215" s="1"/>
       <c r="AD215" s="1"/>
     </row>
-    <row r="216" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7446,7 +7430,7 @@
       <c r="AC216" s="1"/>
       <c r="AD216" s="1"/>
     </row>
-    <row r="217" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7478,7 +7462,7 @@
       <c r="AC217" s="1"/>
       <c r="AD217" s="1"/>
     </row>
-    <row r="218" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7510,7 +7494,7 @@
       <c r="AC218" s="1"/>
       <c r="AD218" s="1"/>
     </row>
-    <row r="219" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7542,7 +7526,7 @@
       <c r="AC219" s="1"/>
       <c r="AD219" s="1"/>
     </row>
-    <row r="220" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7574,7 +7558,7 @@
       <c r="AC220" s="1"/>
       <c r="AD220" s="1"/>
     </row>
-    <row r="221" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7606,7 +7590,7 @@
       <c r="AC221" s="1"/>
       <c r="AD221" s="1"/>
     </row>
-    <row r="222" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7638,7 +7622,7 @@
       <c r="AC222" s="1"/>
       <c r="AD222" s="1"/>
     </row>
-    <row r="223" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7670,7 +7654,7 @@
       <c r="AC223" s="1"/>
       <c r="AD223" s="1"/>
     </row>
-    <row r="224" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7702,7 +7686,7 @@
       <c r="AC224" s="1"/>
       <c r="AD224" s="1"/>
     </row>
-    <row r="225" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7734,7 +7718,7 @@
       <c r="AC225" s="1"/>
       <c r="AD225" s="1"/>
     </row>
-    <row r="226" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7766,7 +7750,7 @@
       <c r="AC226" s="1"/>
       <c r="AD226" s="1"/>
     </row>
-    <row r="227" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7798,7 +7782,7 @@
       <c r="AC227" s="1"/>
       <c r="AD227" s="1"/>
     </row>
-    <row r="228" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7830,7 +7814,7 @@
       <c r="AC228" s="1"/>
       <c r="AD228" s="1"/>
     </row>
-    <row r="229" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7862,7 +7846,7 @@
       <c r="AC229" s="1"/>
       <c r="AD229" s="1"/>
     </row>
-    <row r="230" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7894,7 +7878,7 @@
       <c r="AC230" s="1"/>
       <c r="AD230" s="1"/>
     </row>
-    <row r="231" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7926,7 +7910,7 @@
       <c r="AC231" s="1"/>
       <c r="AD231" s="1"/>
     </row>
-    <row r="232" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7958,7 +7942,7 @@
       <c r="AC232" s="1"/>
       <c r="AD232" s="1"/>
     </row>
-    <row r="233" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7990,7 +7974,7 @@
       <c r="AC233" s="1"/>
       <c r="AD233" s="1"/>
     </row>
-    <row r="234" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8022,7 +8006,7 @@
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
     </row>
-    <row r="235" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8054,7 +8038,7 @@
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
     </row>
-    <row r="236" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8086,7 +8070,7 @@
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
     </row>
-    <row r="237" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8118,7 +8102,7 @@
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
     </row>
-    <row r="238" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8150,7 +8134,7 @@
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
     </row>
-    <row r="239" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8182,7 +8166,7 @@
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
     </row>
-    <row r="240" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8214,7 +8198,7 @@
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
     </row>
-    <row r="241" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8246,7 +8230,7 @@
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
     </row>
-    <row r="242" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8278,7 +8262,7 @@
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
     </row>
-    <row r="243" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8310,7 +8294,7 @@
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
     </row>
-    <row r="244" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8342,7 +8326,7 @@
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
     </row>
-    <row r="245" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8374,7 +8358,7 @@
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
     </row>
-    <row r="246" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8406,7 +8390,7 @@
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
     </row>
-    <row r="247" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8438,7 +8422,7 @@
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
     </row>
-    <row r="248" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8470,7 +8454,7 @@
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
     </row>
-    <row r="249" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8502,7 +8486,7 @@
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
     </row>
-    <row r="250" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8534,7 +8518,7 @@
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
     </row>
-    <row r="251" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8566,7 +8550,7 @@
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
     </row>
-    <row r="252" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8598,7 +8582,7 @@
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
     </row>
-    <row r="253" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8630,7 +8614,7 @@
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
     </row>
-    <row r="254" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8662,7 +8646,7 @@
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
     </row>
-    <row r="255" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8694,7 +8678,7 @@
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
     </row>
-    <row r="256" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8726,7 +8710,7 @@
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
     </row>
-    <row r="257" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8758,7 +8742,7 @@
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
     </row>
-    <row r="258" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8790,7 +8774,7 @@
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
     </row>
-    <row r="259" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8822,7 +8806,7 @@
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
     </row>
-    <row r="260" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8854,7 +8838,7 @@
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
     </row>
-    <row r="261" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8886,7 +8870,7 @@
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
     </row>
-    <row r="262" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8918,7 +8902,7 @@
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
     </row>
-    <row r="263" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8950,7 +8934,7 @@
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
     </row>
-    <row r="264" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8982,7 +8966,7 @@
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
     </row>
-    <row r="265" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9014,7 +8998,7 @@
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
     </row>
-    <row r="266" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9046,7 +9030,7 @@
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
     </row>
-    <row r="267" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9078,7 +9062,7 @@
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
     </row>
-    <row r="268" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9110,7 +9094,7 @@
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
     </row>
-    <row r="269" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9142,7 +9126,7 @@
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
     </row>
-    <row r="270" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9174,7 +9158,7 @@
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
     </row>
-    <row r="271" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9206,7 +9190,7 @@
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
     </row>
-    <row r="272" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9238,7 +9222,7 @@
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
     </row>
-    <row r="273" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9270,7 +9254,7 @@
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
     </row>
-    <row r="274" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9302,7 +9286,7 @@
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
     </row>
-    <row r="275" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9334,7 +9318,7 @@
       <c r="AC275" s="1"/>
       <c r="AD275" s="1"/>
     </row>
-    <row r="276" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9366,7 +9350,7 @@
       <c r="AC276" s="1"/>
       <c r="AD276" s="1"/>
     </row>
-    <row r="277" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9398,7 +9382,7 @@
       <c r="AC277" s="1"/>
       <c r="AD277" s="1"/>
     </row>
-    <row r="278" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9430,7 +9414,7 @@
       <c r="AC278" s="1"/>
       <c r="AD278" s="1"/>
     </row>
-    <row r="279" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9462,7 +9446,7 @@
       <c r="AC279" s="1"/>
       <c r="AD279" s="1"/>
     </row>
-    <row r="280" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9494,7 +9478,7 @@
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
     </row>
-    <row r="281" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9526,7 +9510,7 @@
       <c r="AC281" s="1"/>
       <c r="AD281" s="1"/>
     </row>
-    <row r="282" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9558,7 +9542,7 @@
       <c r="AC282" s="1"/>
       <c r="AD282" s="1"/>
     </row>
-    <row r="283" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9590,7 +9574,7 @@
       <c r="AC283" s="1"/>
       <c r="AD283" s="1"/>
     </row>
-    <row r="284" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9622,7 +9606,7 @@
       <c r="AC284" s="1"/>
       <c r="AD284" s="1"/>
     </row>
-    <row r="285" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9654,7 +9638,7 @@
       <c r="AC285" s="1"/>
       <c r="AD285" s="1"/>
     </row>
-    <row r="286" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9686,7 +9670,7 @@
       <c r="AC286" s="1"/>
       <c r="AD286" s="1"/>
     </row>
-    <row r="287" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9718,7 +9702,7 @@
       <c r="AC287" s="1"/>
       <c r="AD287" s="1"/>
     </row>
-    <row r="288" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9750,7 +9734,7 @@
       <c r="AC288" s="1"/>
       <c r="AD288" s="1"/>
     </row>
-    <row r="289" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9782,7 +9766,7 @@
       <c r="AC289" s="1"/>
       <c r="AD289" s="1"/>
     </row>
-    <row r="290" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9814,7 +9798,7 @@
       <c r="AC290" s="1"/>
       <c r="AD290" s="1"/>
     </row>
-    <row r="291" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9846,7 +9830,7 @@
       <c r="AC291" s="1"/>
       <c r="AD291" s="1"/>
     </row>
-    <row r="292" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9878,7 +9862,7 @@
       <c r="AC292" s="1"/>
       <c r="AD292" s="1"/>
     </row>
-    <row r="293" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9910,7 +9894,7 @@
       <c r="AC293" s="1"/>
       <c r="AD293" s="1"/>
     </row>
-    <row r="294" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9942,7 +9926,7 @@
       <c r="AC294" s="1"/>
       <c r="AD294" s="1"/>
     </row>
-    <row r="295" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9974,7 +9958,7 @@
       <c r="AC295" s="1"/>
       <c r="AD295" s="1"/>
     </row>
-    <row r="296" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10006,7 +9990,7 @@
       <c r="AC296" s="1"/>
       <c r="AD296" s="1"/>
     </row>
-    <row r="297" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10038,7 +10022,7 @@
       <c r="AC297" s="1"/>
       <c r="AD297" s="1"/>
     </row>
-    <row r="298" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10070,7 +10054,7 @@
       <c r="AC298" s="1"/>
       <c r="AD298" s="1"/>
     </row>
-    <row r="299" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10102,7 +10086,7 @@
       <c r="AC299" s="1"/>
       <c r="AD299" s="1"/>
     </row>
-    <row r="300" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10134,7 +10118,7 @@
       <c r="AC300" s="1"/>
       <c r="AD300" s="1"/>
     </row>
-    <row r="301" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10166,7 +10150,7 @@
       <c r="AC301" s="1"/>
       <c r="AD301" s="1"/>
     </row>
-    <row r="302" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10198,7 +10182,7 @@
       <c r="AC302" s="1"/>
       <c r="AD302" s="1"/>
     </row>
-    <row r="303" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10230,7 +10214,7 @@
       <c r="AC303" s="1"/>
       <c r="AD303" s="1"/>
     </row>
-    <row r="304" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10262,7 +10246,7 @@
       <c r="AC304" s="1"/>
       <c r="AD304" s="1"/>
     </row>
-    <row r="305" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10294,7 +10278,7 @@
       <c r="AC305" s="1"/>
       <c r="AD305" s="1"/>
     </row>
-    <row r="306" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10326,7 +10310,7 @@
       <c r="AC306" s="1"/>
       <c r="AD306" s="1"/>
     </row>
-    <row r="307" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10358,7 +10342,7 @@
       <c r="AC307" s="1"/>
       <c r="AD307" s="1"/>
     </row>
-    <row r="308" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10390,7 +10374,7 @@
       <c r="AC308" s="1"/>
       <c r="AD308" s="1"/>
     </row>
-    <row r="309" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10422,7 +10406,7 @@
       <c r="AC309" s="1"/>
       <c r="AD309" s="1"/>
     </row>
-    <row r="310" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10454,7 +10438,7 @@
       <c r="AC310" s="1"/>
       <c r="AD310" s="1"/>
     </row>
-    <row r="311" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10486,7 +10470,7 @@
       <c r="AC311" s="1"/>
       <c r="AD311" s="1"/>
     </row>
-    <row r="312" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10518,7 +10502,7 @@
       <c r="AC312" s="1"/>
       <c r="AD312" s="1"/>
     </row>
-    <row r="313" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10550,7 +10534,7 @@
       <c r="AC313" s="1"/>
       <c r="AD313" s="1"/>
     </row>
-    <row r="314" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10582,7 +10566,7 @@
       <c r="AC314" s="1"/>
       <c r="AD314" s="1"/>
     </row>
-    <row r="315" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10614,7 +10598,7 @@
       <c r="AC315" s="1"/>
       <c r="AD315" s="1"/>
     </row>
-    <row r="316" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10646,7 +10630,7 @@
       <c r="AC316" s="1"/>
       <c r="AD316" s="1"/>
     </row>
-    <row r="317" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10678,7 +10662,7 @@
       <c r="AC317" s="1"/>
       <c r="AD317" s="1"/>
     </row>
-    <row r="318" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10710,7 +10694,7 @@
       <c r="AC318" s="1"/>
       <c r="AD318" s="1"/>
     </row>
-    <row r="319" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10742,7 +10726,7 @@
       <c r="AC319" s="1"/>
       <c r="AD319" s="1"/>
     </row>
-    <row r="320" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10774,7 +10758,7 @@
       <c r="AC320" s="1"/>
       <c r="AD320" s="1"/>
     </row>
-    <row r="321" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10806,7 +10790,7 @@
       <c r="AC321" s="1"/>
       <c r="AD321" s="1"/>
     </row>
-    <row r="322" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10838,7 +10822,7 @@
       <c r="AC322" s="1"/>
       <c r="AD322" s="1"/>
     </row>
-    <row r="323" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10870,7 +10854,7 @@
       <c r="AC323" s="1"/>
       <c r="AD323" s="1"/>
     </row>
-    <row r="324" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10902,7 +10886,7 @@
       <c r="AC324" s="1"/>
       <c r="AD324" s="1"/>
     </row>
-    <row r="325" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10934,7 +10918,7 @@
       <c r="AC325" s="1"/>
       <c r="AD325" s="1"/>
     </row>
-    <row r="326" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10966,7 +10950,7 @@
       <c r="AC326" s="1"/>
       <c r="AD326" s="1"/>
     </row>
-    <row r="327" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10998,7 +10982,7 @@
       <c r="AC327" s="1"/>
       <c r="AD327" s="1"/>
     </row>
-    <row r="328" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11030,7 +11014,7 @@
       <c r="AC328" s="1"/>
       <c r="AD328" s="1"/>
     </row>
-    <row r="329" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11062,7 +11046,7 @@
       <c r="AC329" s="1"/>
       <c r="AD329" s="1"/>
     </row>
-    <row r="330" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11094,7 +11078,7 @@
       <c r="AC330" s="1"/>
       <c r="AD330" s="1"/>
     </row>
-    <row r="331" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11126,7 +11110,7 @@
       <c r="AC331" s="1"/>
       <c r="AD331" s="1"/>
     </row>
-    <row r="332" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11158,7 +11142,7 @@
       <c r="AC332" s="1"/>
       <c r="AD332" s="1"/>
     </row>
-    <row r="333" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11190,7 +11174,7 @@
       <c r="AC333" s="1"/>
       <c r="AD333" s="1"/>
     </row>
-    <row r="334" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11222,7 +11206,7 @@
       <c r="AC334" s="1"/>
       <c r="AD334" s="1"/>
     </row>
-    <row r="335" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11254,7 +11238,7 @@
       <c r="AC335" s="1"/>
       <c r="AD335" s="1"/>
     </row>
-    <row r="336" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11286,7 +11270,7 @@
       <c r="AC336" s="1"/>
       <c r="AD336" s="1"/>
     </row>
-    <row r="337" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11318,7 +11302,7 @@
       <c r="AC337" s="1"/>
       <c r="AD337" s="1"/>
     </row>
-    <row r="338" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11350,7 +11334,7 @@
       <c r="AC338" s="1"/>
       <c r="AD338" s="1"/>
     </row>
-    <row r="339" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11382,7 +11366,7 @@
       <c r="AC339" s="1"/>
       <c r="AD339" s="1"/>
     </row>
-    <row r="340" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11414,7 +11398,7 @@
       <c r="AC340" s="1"/>
       <c r="AD340" s="1"/>
     </row>
-    <row r="341" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11446,7 +11430,7 @@
       <c r="AC341" s="1"/>
       <c r="AD341" s="1"/>
     </row>
-    <row r="342" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11478,7 +11462,7 @@
       <c r="AC342" s="1"/>
       <c r="AD342" s="1"/>
     </row>
-    <row r="343" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11510,7 +11494,7 @@
       <c r="AC343" s="1"/>
       <c r="AD343" s="1"/>
     </row>
-    <row r="344" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11542,7 +11526,7 @@
       <c r="AC344" s="1"/>
       <c r="AD344" s="1"/>
     </row>
-    <row r="345" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11574,7 +11558,7 @@
       <c r="AC345" s="1"/>
       <c r="AD345" s="1"/>
     </row>
-    <row r="346" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11606,7 +11590,7 @@
       <c r="AC346" s="1"/>
       <c r="AD346" s="1"/>
     </row>
-    <row r="347" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11638,7 +11622,7 @@
       <c r="AC347" s="1"/>
       <c r="AD347" s="1"/>
     </row>
-    <row r="348" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11670,7 +11654,7 @@
       <c r="AC348" s="1"/>
       <c r="AD348" s="1"/>
     </row>
-    <row r="349" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11702,7 +11686,7 @@
       <c r="AC349" s="1"/>
       <c r="AD349" s="1"/>
     </row>
-    <row r="350" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11734,7 +11718,7 @@
       <c r="AC350" s="1"/>
       <c r="AD350" s="1"/>
     </row>
-    <row r="351" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11766,7 +11750,7 @@
       <c r="AC351" s="1"/>
       <c r="AD351" s="1"/>
     </row>
-    <row r="352" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11798,7 +11782,7 @@
       <c r="AC352" s="1"/>
       <c r="AD352" s="1"/>
     </row>
-    <row r="353" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11830,7 +11814,7 @@
       <c r="AC353" s="1"/>
       <c r="AD353" s="1"/>
     </row>
-    <row r="354" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11862,7 +11846,7 @@
       <c r="AC354" s="1"/>
       <c r="AD354" s="1"/>
     </row>
-    <row r="355" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11894,7 +11878,7 @@
       <c r="AC355" s="1"/>
       <c r="AD355" s="1"/>
     </row>
-    <row r="356" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11926,7 +11910,7 @@
       <c r="AC356" s="1"/>
       <c r="AD356" s="1"/>
     </row>
-    <row r="357" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11958,7 +11942,7 @@
       <c r="AC357" s="1"/>
       <c r="AD357" s="1"/>
     </row>
-    <row r="358" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11990,7 +11974,7 @@
       <c r="AC358" s="1"/>
       <c r="AD358" s="1"/>
     </row>
-    <row r="359" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12022,7 +12006,7 @@
       <c r="AC359" s="1"/>
       <c r="AD359" s="1"/>
     </row>
-    <row r="360" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12054,7 +12038,7 @@
       <c r="AC360" s="1"/>
       <c r="AD360" s="1"/>
     </row>
-    <row r="361" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12086,7 +12070,7 @@
       <c r="AC361" s="1"/>
       <c r="AD361" s="1"/>
     </row>
-    <row r="362" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12118,7 +12102,7 @@
       <c r="AC362" s="1"/>
       <c r="AD362" s="1"/>
     </row>
-    <row r="363" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12150,7 +12134,7 @@
       <c r="AC363" s="1"/>
       <c r="AD363" s="1"/>
     </row>
-    <row r="364" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12182,7 +12166,7 @@
       <c r="AC364" s="1"/>
       <c r="AD364" s="1"/>
     </row>
-    <row r="365" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12214,7 +12198,7 @@
       <c r="AC365" s="1"/>
       <c r="AD365" s="1"/>
     </row>
-    <row r="366" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12246,7 +12230,7 @@
       <c r="AC366" s="1"/>
       <c r="AD366" s="1"/>
     </row>
-    <row r="367" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12278,7 +12262,7 @@
       <c r="AC367" s="1"/>
       <c r="AD367" s="1"/>
     </row>
-    <row r="368" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12310,7 +12294,7 @@
       <c r="AC368" s="1"/>
       <c r="AD368" s="1"/>
     </row>
-    <row r="369" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12342,7 +12326,7 @@
       <c r="AC369" s="1"/>
       <c r="AD369" s="1"/>
     </row>
-    <row r="370" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12374,7 +12358,7 @@
       <c r="AC370" s="1"/>
       <c r="AD370" s="1"/>
     </row>
-    <row r="371" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12406,7 +12390,7 @@
       <c r="AC371" s="1"/>
       <c r="AD371" s="1"/>
     </row>
-    <row r="372" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12438,7 +12422,7 @@
       <c r="AC372" s="1"/>
       <c r="AD372" s="1"/>
     </row>
-    <row r="373" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12470,7 +12454,7 @@
       <c r="AC373" s="1"/>
       <c r="AD373" s="1"/>
     </row>
-    <row r="374" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12502,7 +12486,7 @@
       <c r="AC374" s="1"/>
       <c r="AD374" s="1"/>
     </row>
-    <row r="375" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12534,7 +12518,7 @@
       <c r="AC375" s="1"/>
       <c r="AD375" s="1"/>
     </row>
-    <row r="376" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12566,7 +12550,7 @@
       <c r="AC376" s="1"/>
       <c r="AD376" s="1"/>
     </row>
-    <row r="377" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12598,7 +12582,7 @@
       <c r="AC377" s="1"/>
       <c r="AD377" s="1"/>
     </row>
-    <row r="378" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12630,7 +12614,7 @@
       <c r="AC378" s="1"/>
       <c r="AD378" s="1"/>
     </row>
-    <row r="379" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12662,7 +12646,7 @@
       <c r="AC379" s="1"/>
       <c r="AD379" s="1"/>
     </row>
-    <row r="380" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12694,7 +12678,7 @@
       <c r="AC380" s="1"/>
       <c r="AD380" s="1"/>
     </row>
-    <row r="381" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12726,7 +12710,7 @@
       <c r="AC381" s="1"/>
       <c r="AD381" s="1"/>
     </row>
-    <row r="382" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12758,7 +12742,7 @@
       <c r="AC382" s="1"/>
       <c r="AD382" s="1"/>
     </row>
-    <row r="383" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12790,7 +12774,7 @@
       <c r="AC383" s="1"/>
       <c r="AD383" s="1"/>
     </row>
-    <row r="384" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12822,7 +12806,7 @@
       <c r="AC384" s="1"/>
       <c r="AD384" s="1"/>
     </row>
-    <row r="385" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12854,7 +12838,7 @@
       <c r="AC385" s="1"/>
       <c r="AD385" s="1"/>
     </row>
-    <row r="386" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12886,7 +12870,7 @@
       <c r="AC386" s="1"/>
       <c r="AD386" s="1"/>
     </row>
-    <row r="387" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12918,7 +12902,7 @@
       <c r="AC387" s="1"/>
       <c r="AD387" s="1"/>
     </row>
-    <row r="388" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12950,7 +12934,7 @@
       <c r="AC388" s="1"/>
       <c r="AD388" s="1"/>
     </row>
-    <row r="389" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12982,7 +12966,7 @@
       <c r="AC389" s="1"/>
       <c r="AD389" s="1"/>
     </row>
-    <row r="390" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13014,7 +12998,7 @@
       <c r="AC390" s="1"/>
       <c r="AD390" s="1"/>
     </row>
-    <row r="391" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13046,7 +13030,7 @@
       <c r="AC391" s="1"/>
       <c r="AD391" s="1"/>
     </row>
-    <row r="392" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13078,7 +13062,7 @@
       <c r="AC392" s="1"/>
       <c r="AD392" s="1"/>
     </row>
-    <row r="393" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13110,7 +13094,7 @@
       <c r="AC393" s="1"/>
       <c r="AD393" s="1"/>
     </row>
-    <row r="394" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13142,7 +13126,7 @@
       <c r="AC394" s="1"/>
       <c r="AD394" s="1"/>
     </row>
-    <row r="395" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13174,7 +13158,7 @@
       <c r="AC395" s="1"/>
       <c r="AD395" s="1"/>
     </row>
-    <row r="396" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13206,7 +13190,7 @@
       <c r="AC396" s="1"/>
       <c r="AD396" s="1"/>
     </row>
-    <row r="397" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13238,7 +13222,7 @@
       <c r="AC397" s="1"/>
       <c r="AD397" s="1"/>
     </row>
-    <row r="398" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13270,7 +13254,7 @@
       <c r="AC398" s="1"/>
       <c r="AD398" s="1"/>
     </row>
-    <row r="399" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13302,7 +13286,7 @@
       <c r="AC399" s="1"/>
       <c r="AD399" s="1"/>
     </row>
-    <row r="400" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13334,7 +13318,7 @@
       <c r="AC400" s="1"/>
       <c r="AD400" s="1"/>
     </row>
-    <row r="401" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13366,7 +13350,7 @@
       <c r="AC401" s="1"/>
       <c r="AD401" s="1"/>
     </row>
-    <row r="402" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13398,7 +13382,7 @@
       <c r="AC402" s="1"/>
       <c r="AD402" s="1"/>
     </row>
-    <row r="403" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13430,7 +13414,7 @@
       <c r="AC403" s="1"/>
       <c r="AD403" s="1"/>
     </row>
-    <row r="404" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13462,7 +13446,7 @@
       <c r="AC404" s="1"/>
       <c r="AD404" s="1"/>
     </row>
-    <row r="405" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13494,7 +13478,7 @@
       <c r="AC405" s="1"/>
       <c r="AD405" s="1"/>
     </row>
-    <row r="406" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13526,7 +13510,7 @@
       <c r="AC406" s="1"/>
       <c r="AD406" s="1"/>
     </row>
-    <row r="407" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13558,7 +13542,7 @@
       <c r="AC407" s="1"/>
       <c r="AD407" s="1"/>
     </row>
-    <row r="408" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13590,7 +13574,7 @@
       <c r="AC408" s="1"/>
       <c r="AD408" s="1"/>
     </row>
-    <row r="409" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13622,7 +13606,7 @@
       <c r="AC409" s="1"/>
       <c r="AD409" s="1"/>
     </row>
-    <row r="410" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13654,7 +13638,7 @@
       <c r="AC410" s="1"/>
       <c r="AD410" s="1"/>
     </row>
-    <row r="411" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13686,7 +13670,7 @@
       <c r="AC411" s="1"/>
       <c r="AD411" s="1"/>
     </row>
-    <row r="412" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13718,7 +13702,7 @@
       <c r="AC412" s="1"/>
       <c r="AD412" s="1"/>
     </row>
-    <row r="413" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13750,7 +13734,7 @@
       <c r="AC413" s="1"/>
       <c r="AD413" s="1"/>
     </row>
-    <row r="414" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13782,7 +13766,7 @@
       <c r="AC414" s="1"/>
       <c r="AD414" s="1"/>
     </row>
-    <row r="415" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13814,7 +13798,7 @@
       <c r="AC415" s="1"/>
       <c r="AD415" s="1"/>
     </row>
-    <row r="416" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13846,7 +13830,7 @@
       <c r="AC416" s="1"/>
       <c r="AD416" s="1"/>
     </row>
-    <row r="417" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13878,7 +13862,7 @@
       <c r="AC417" s="1"/>
       <c r="AD417" s="1"/>
     </row>
-    <row r="418" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13910,7 +13894,7 @@
       <c r="AC418" s="1"/>
       <c r="AD418" s="1"/>
     </row>
-    <row r="419" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13942,7 +13926,7 @@
       <c r="AC419" s="1"/>
       <c r="AD419" s="1"/>
     </row>
-    <row r="420" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13974,7 +13958,7 @@
       <c r="AC420" s="1"/>
       <c r="AD420" s="1"/>
     </row>
-    <row r="421" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14006,7 +13990,7 @@
       <c r="AC421" s="1"/>
       <c r="AD421" s="1"/>
     </row>
-    <row r="422" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14038,7 +14022,7 @@
       <c r="AC422" s="1"/>
       <c r="AD422" s="1"/>
     </row>
-    <row r="423" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14070,7 +14054,7 @@
       <c r="AC423" s="1"/>
       <c r="AD423" s="1"/>
     </row>
-    <row r="424" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14102,7 +14086,7 @@
       <c r="AC424" s="1"/>
       <c r="AD424" s="1"/>
     </row>
-    <row r="425" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14134,7 +14118,7 @@
       <c r="AC425" s="1"/>
       <c r="AD425" s="1"/>
     </row>
-    <row r="426" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14166,7 +14150,7 @@
       <c r="AC426" s="1"/>
       <c r="AD426" s="1"/>
     </row>
-    <row r="427" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14198,7 +14182,7 @@
       <c r="AC427" s="1"/>
       <c r="AD427" s="1"/>
     </row>
-    <row r="428" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14230,7 +14214,7 @@
       <c r="AC428" s="1"/>
       <c r="AD428" s="1"/>
     </row>
-    <row r="429" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14262,7 +14246,7 @@
       <c r="AC429" s="1"/>
       <c r="AD429" s="1"/>
     </row>
-    <row r="430" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14294,7 +14278,7 @@
       <c r="AC430" s="1"/>
       <c r="AD430" s="1"/>
     </row>
-    <row r="431" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14326,7 +14310,7 @@
       <c r="AC431" s="1"/>
       <c r="AD431" s="1"/>
     </row>
-    <row r="432" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14358,7 +14342,7 @@
       <c r="AC432" s="1"/>
       <c r="AD432" s="1"/>
     </row>
-    <row r="433" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14390,7 +14374,7 @@
       <c r="AC433" s="1"/>
       <c r="AD433" s="1"/>
     </row>
-    <row r="434" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14422,7 +14406,7 @@
       <c r="AC434" s="1"/>
       <c r="AD434" s="1"/>
     </row>
-    <row r="435" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14454,7 +14438,7 @@
       <c r="AC435" s="1"/>
       <c r="AD435" s="1"/>
     </row>
-    <row r="436" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14486,7 +14470,7 @@
       <c r="AC436" s="1"/>
       <c r="AD436" s="1"/>
     </row>
-    <row r="437" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14518,7 +14502,7 @@
       <c r="AC437" s="1"/>
       <c r="AD437" s="1"/>
     </row>
-    <row r="438" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14550,7 +14534,7 @@
       <c r="AC438" s="1"/>
       <c r="AD438" s="1"/>
     </row>
-    <row r="439" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14582,7 +14566,7 @@
       <c r="AC439" s="1"/>
       <c r="AD439" s="1"/>
     </row>
-    <row r="440" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14614,7 +14598,7 @@
       <c r="AC440" s="1"/>
       <c r="AD440" s="1"/>
     </row>
-    <row r="441" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14646,7 +14630,7 @@
       <c r="AC441" s="1"/>
       <c r="AD441" s="1"/>
     </row>
-    <row r="442" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14678,7 +14662,7 @@
       <c r="AC442" s="1"/>
       <c r="AD442" s="1"/>
     </row>
-    <row r="443" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14710,7 +14694,7 @@
       <c r="AC443" s="1"/>
       <c r="AD443" s="1"/>
     </row>
-    <row r="444" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14742,7 +14726,7 @@
       <c r="AC444" s="1"/>
       <c r="AD444" s="1"/>
     </row>
-    <row r="445" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14774,7 +14758,7 @@
       <c r="AC445" s="1"/>
       <c r="AD445" s="1"/>
     </row>
-    <row r="446" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14806,7 +14790,7 @@
       <c r="AC446" s="1"/>
       <c r="AD446" s="1"/>
     </row>
-    <row r="447" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14838,7 +14822,7 @@
       <c r="AC447" s="1"/>
       <c r="AD447" s="1"/>
     </row>
-    <row r="448" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14870,7 +14854,7 @@
       <c r="AC448" s="1"/>
       <c r="AD448" s="1"/>
     </row>
-    <row r="449" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14902,7 +14886,7 @@
       <c r="AC449" s="1"/>
       <c r="AD449" s="1"/>
     </row>
-    <row r="450" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14934,7 +14918,7 @@
       <c r="AC450" s="1"/>
       <c r="AD450" s="1"/>
     </row>
-    <row r="451" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14966,7 +14950,7 @@
       <c r="AC451" s="1"/>
       <c r="AD451" s="1"/>
     </row>
-    <row r="452" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14998,7 +14982,7 @@
       <c r="AC452" s="1"/>
       <c r="AD452" s="1"/>
     </row>
-    <row r="453" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15030,7 +15014,7 @@
       <c r="AC453" s="1"/>
       <c r="AD453" s="1"/>
     </row>
-    <row r="454" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15062,7 +15046,7 @@
       <c r="AC454" s="1"/>
       <c r="AD454" s="1"/>
     </row>
-    <row r="455" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15094,7 +15078,7 @@
       <c r="AC455" s="1"/>
       <c r="AD455" s="1"/>
     </row>
-    <row r="456" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15126,7 +15110,7 @@
       <c r="AC456" s="1"/>
       <c r="AD456" s="1"/>
     </row>
-    <row r="457" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15158,7 +15142,7 @@
       <c r="AC457" s="1"/>
       <c r="AD457" s="1"/>
     </row>
-    <row r="458" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15190,7 +15174,7 @@
       <c r="AC458" s="1"/>
       <c r="AD458" s="1"/>
     </row>
-    <row r="459" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15222,7 +15206,7 @@
       <c r="AC459" s="1"/>
       <c r="AD459" s="1"/>
     </row>
-    <row r="460" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15254,7 +15238,7 @@
       <c r="AC460" s="1"/>
       <c r="AD460" s="1"/>
     </row>
-    <row r="461" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15286,7 +15270,7 @@
       <c r="AC461" s="1"/>
       <c r="AD461" s="1"/>
     </row>
-    <row r="462" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15318,7 +15302,7 @@
       <c r="AC462" s="1"/>
       <c r="AD462" s="1"/>
     </row>
-    <row r="463" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15350,7 +15334,7 @@
       <c r="AC463" s="1"/>
       <c r="AD463" s="1"/>
     </row>
-    <row r="464" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15382,7 +15366,7 @@
       <c r="AC464" s="1"/>
       <c r="AD464" s="1"/>
     </row>
-    <row r="465" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15414,7 +15398,7 @@
       <c r="AC465" s="1"/>
       <c r="AD465" s="1"/>
     </row>
-    <row r="466" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15446,7 +15430,7 @@
       <c r="AC466" s="1"/>
       <c r="AD466" s="1"/>
     </row>
-    <row r="467" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15478,7 +15462,7 @@
       <c r="AC467" s="1"/>
       <c r="AD467" s="1"/>
     </row>
-    <row r="468" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15510,7 +15494,7 @@
       <c r="AC468" s="1"/>
       <c r="AD468" s="1"/>
     </row>
-    <row r="469" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15542,7 +15526,7 @@
       <c r="AC469" s="1"/>
       <c r="AD469" s="1"/>
     </row>
-    <row r="470" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15574,7 +15558,7 @@
       <c r="AC470" s="1"/>
       <c r="AD470" s="1"/>
     </row>
-    <row r="471" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15606,7 +15590,7 @@
       <c r="AC471" s="1"/>
       <c r="AD471" s="1"/>
     </row>
-    <row r="472" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15638,7 +15622,7 @@
       <c r="AC472" s="1"/>
       <c r="AD472" s="1"/>
     </row>
-    <row r="473" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15670,7 +15654,7 @@
       <c r="AC473" s="1"/>
       <c r="AD473" s="1"/>
     </row>
-    <row r="474" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15702,7 +15686,7 @@
       <c r="AC474" s="1"/>
       <c r="AD474" s="1"/>
     </row>
-    <row r="475" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15734,7 +15718,7 @@
       <c r="AC475" s="1"/>
       <c r="AD475" s="1"/>
     </row>
-    <row r="476" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15766,7 +15750,7 @@
       <c r="AC476" s="1"/>
       <c r="AD476" s="1"/>
     </row>
-    <row r="477" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15798,7 +15782,7 @@
       <c r="AC477" s="1"/>
       <c r="AD477" s="1"/>
     </row>
-    <row r="478" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15830,7 +15814,7 @@
       <c r="AC478" s="1"/>
       <c r="AD478" s="1"/>
     </row>
-    <row r="479" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15862,7 +15846,7 @@
       <c r="AC479" s="1"/>
       <c r="AD479" s="1"/>
     </row>
-    <row r="480" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15894,7 +15878,7 @@
       <c r="AC480" s="1"/>
       <c r="AD480" s="1"/>
     </row>
-    <row r="481" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15926,7 +15910,7 @@
       <c r="AC481" s="1"/>
       <c r="AD481" s="1"/>
     </row>
-    <row r="482" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15958,7 +15942,7 @@
       <c r="AC482" s="1"/>
       <c r="AD482" s="1"/>
     </row>
-    <row r="483" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15990,7 +15974,7 @@
       <c r="AC483" s="1"/>
       <c r="AD483" s="1"/>
     </row>
-    <row r="484" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16022,7 +16006,7 @@
       <c r="AC484" s="1"/>
       <c r="AD484" s="1"/>
     </row>
-    <row r="485" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16054,7 +16038,7 @@
       <c r="AC485" s="1"/>
       <c r="AD485" s="1"/>
     </row>
-    <row r="486" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16086,7 +16070,7 @@
       <c r="AC486" s="1"/>
       <c r="AD486" s="1"/>
     </row>
-    <row r="487" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16118,7 +16102,7 @@
       <c r="AC487" s="1"/>
       <c r="AD487" s="1"/>
     </row>
-    <row r="488" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16150,7 +16134,7 @@
       <c r="AC488" s="1"/>
       <c r="AD488" s="1"/>
     </row>
-    <row r="489" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16182,7 +16166,7 @@
       <c r="AC489" s="1"/>
       <c r="AD489" s="1"/>
     </row>
-    <row r="490" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16214,7 +16198,7 @@
       <c r="AC490" s="1"/>
       <c r="AD490" s="1"/>
     </row>
-    <row r="491" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16246,7 +16230,7 @@
       <c r="AC491" s="1"/>
       <c r="AD491" s="1"/>
     </row>
-    <row r="492" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16278,7 +16262,7 @@
       <c r="AC492" s="1"/>
       <c r="AD492" s="1"/>
     </row>
-    <row r="493" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16310,7 +16294,7 @@
       <c r="AC493" s="1"/>
       <c r="AD493" s="1"/>
     </row>
-    <row r="494" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16342,7 +16326,7 @@
       <c r="AC494" s="1"/>
       <c r="AD494" s="1"/>
     </row>
-    <row r="495" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16374,7 +16358,7 @@
       <c r="AC495" s="1"/>
       <c r="AD495" s="1"/>
     </row>
-    <row r="496" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16406,7 +16390,7 @@
       <c r="AC496" s="1"/>
       <c r="AD496" s="1"/>
     </row>
-    <row r="497" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16438,7 +16422,7 @@
       <c r="AC497" s="1"/>
       <c r="AD497" s="1"/>
     </row>
-    <row r="498" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16470,7 +16454,7 @@
       <c r="AC498" s="1"/>
       <c r="AD498" s="1"/>
     </row>
-    <row r="499" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16502,7 +16486,7 @@
       <c r="AC499" s="1"/>
       <c r="AD499" s="1"/>
     </row>
-    <row r="500" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16534,7 +16518,7 @@
       <c r="AC500" s="1"/>
       <c r="AD500" s="1"/>
     </row>
-    <row r="501" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16566,7 +16550,7 @@
       <c r="AC501" s="1"/>
       <c r="AD501" s="1"/>
     </row>
-    <row r="502" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16598,7 +16582,7 @@
       <c r="AC502" s="1"/>
       <c r="AD502" s="1"/>
     </row>
-    <row r="503" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16630,7 +16614,7 @@
       <c r="AC503" s="1"/>
       <c r="AD503" s="1"/>
     </row>
-    <row r="504" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16662,7 +16646,7 @@
       <c r="AC504" s="1"/>
       <c r="AD504" s="1"/>
     </row>
-    <row r="505" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16694,7 +16678,7 @@
       <c r="AC505" s="1"/>
       <c r="AD505" s="1"/>
     </row>
-    <row r="506" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16726,7 +16710,7 @@
       <c r="AC506" s="1"/>
       <c r="AD506" s="1"/>
     </row>
-    <row r="507" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16758,7 +16742,7 @@
       <c r="AC507" s="1"/>
       <c r="AD507" s="1"/>
     </row>
-    <row r="508" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16790,7 +16774,7 @@
       <c r="AC508" s="1"/>
       <c r="AD508" s="1"/>
     </row>
-    <row r="509" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16822,7 +16806,7 @@
       <c r="AC509" s="1"/>
       <c r="AD509" s="1"/>
     </row>
-    <row r="510" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16854,7 +16838,7 @@
       <c r="AC510" s="1"/>
       <c r="AD510" s="1"/>
     </row>
-    <row r="511" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16886,7 +16870,7 @@
       <c r="AC511" s="1"/>
       <c r="AD511" s="1"/>
     </row>
-    <row r="512" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16918,7 +16902,7 @@
       <c r="AC512" s="1"/>
       <c r="AD512" s="1"/>
     </row>
-    <row r="513" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16950,7 +16934,7 @@
       <c r="AC513" s="1"/>
       <c r="AD513" s="1"/>
     </row>
-    <row r="514" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16982,7 +16966,7 @@
       <c r="AC514" s="1"/>
       <c r="AD514" s="1"/>
     </row>
-    <row r="515" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -17014,7 +16998,7 @@
       <c r="AC515" s="1"/>
       <c r="AD515" s="1"/>
     </row>
-    <row r="516" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17046,7 +17030,7 @@
       <c r="AC516" s="1"/>
       <c r="AD516" s="1"/>
     </row>
-    <row r="517" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17078,7 +17062,7 @@
       <c r="AC517" s="1"/>
       <c r="AD517" s="1"/>
     </row>
-    <row r="518" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17110,7 +17094,7 @@
       <c r="AC518" s="1"/>
       <c r="AD518" s="1"/>
     </row>
-    <row r="519" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17142,7 +17126,7 @@
       <c r="AC519" s="1"/>
       <c r="AD519" s="1"/>
     </row>
-    <row r="520" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17174,7 +17158,7 @@
       <c r="AC520" s="1"/>
       <c r="AD520" s="1"/>
     </row>
-    <row r="521" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17206,7 +17190,7 @@
       <c r="AC521" s="1"/>
       <c r="AD521" s="1"/>
     </row>
-    <row r="522" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17238,7 +17222,7 @@
       <c r="AC522" s="1"/>
       <c r="AD522" s="1"/>
     </row>
-    <row r="523" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17270,7 +17254,7 @@
       <c r="AC523" s="1"/>
       <c r="AD523" s="1"/>
     </row>
-    <row r="524" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17302,7 +17286,7 @@
       <c r="AC524" s="1"/>
       <c r="AD524" s="1"/>
     </row>
-    <row r="525" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17334,7 +17318,7 @@
       <c r="AC525" s="1"/>
       <c r="AD525" s="1"/>
     </row>
-    <row r="526" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17366,7 +17350,7 @@
       <c r="AC526" s="1"/>
       <c r="AD526" s="1"/>
     </row>
-    <row r="527" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17398,7 +17382,7 @@
       <c r="AC527" s="1"/>
       <c r="AD527" s="1"/>
     </row>
-    <row r="528" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17430,7 +17414,7 @@
       <c r="AC528" s="1"/>
       <c r="AD528" s="1"/>
     </row>
-    <row r="529" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17462,7 +17446,7 @@
       <c r="AC529" s="1"/>
       <c r="AD529" s="1"/>
     </row>
-    <row r="530" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17494,7 +17478,7 @@
       <c r="AC530" s="1"/>
       <c r="AD530" s="1"/>
     </row>
-    <row r="531" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17526,7 +17510,7 @@
       <c r="AC531" s="1"/>
       <c r="AD531" s="1"/>
     </row>
-    <row r="532" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17558,7 +17542,7 @@
       <c r="AC532" s="1"/>
       <c r="AD532" s="1"/>
     </row>
-    <row r="533" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17590,7 +17574,7 @@
       <c r="AC533" s="1"/>
       <c r="AD533" s="1"/>
     </row>
-    <row r="534" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17622,7 +17606,7 @@
       <c r="AC534" s="1"/>
       <c r="AD534" s="1"/>
     </row>
-    <row r="535" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17654,7 +17638,7 @@
       <c r="AC535" s="1"/>
       <c r="AD535" s="1"/>
     </row>
-    <row r="536" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17686,7 +17670,7 @@
       <c r="AC536" s="1"/>
       <c r="AD536" s="1"/>
     </row>
-    <row r="537" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17718,7 +17702,7 @@
       <c r="AC537" s="1"/>
       <c r="AD537" s="1"/>
     </row>
-    <row r="538" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17750,7 +17734,7 @@
       <c r="AC538" s="1"/>
       <c r="AD538" s="1"/>
     </row>
-    <row r="539" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17782,7 +17766,7 @@
       <c r="AC539" s="1"/>
       <c r="AD539" s="1"/>
     </row>
-    <row r="540" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17814,7 +17798,7 @@
       <c r="AC540" s="1"/>
       <c r="AD540" s="1"/>
     </row>
-    <row r="541" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17846,7 +17830,7 @@
       <c r="AC541" s="1"/>
       <c r="AD541" s="1"/>
     </row>
-    <row r="542" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17878,7 +17862,7 @@
       <c r="AC542" s="1"/>
       <c r="AD542" s="1"/>
     </row>
-    <row r="543" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17910,7 +17894,7 @@
       <c r="AC543" s="1"/>
       <c r="AD543" s="1"/>
     </row>
-    <row r="544" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17942,7 +17926,7 @@
       <c r="AC544" s="1"/>
       <c r="AD544" s="1"/>
     </row>
-    <row r="545" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17974,7 +17958,7 @@
       <c r="AC545" s="1"/>
       <c r="AD545" s="1"/>
     </row>
-    <row r="546" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -18006,7 +17990,7 @@
       <c r="AC546" s="1"/>
       <c r="AD546" s="1"/>
     </row>
-    <row r="547" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18038,7 +18022,7 @@
       <c r="AC547" s="1"/>
       <c r="AD547" s="1"/>
     </row>
-    <row r="548" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18070,7 +18054,7 @@
       <c r="AC548" s="1"/>
       <c r="AD548" s="1"/>
     </row>
-    <row r="549" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18102,7 +18086,7 @@
       <c r="AC549" s="1"/>
       <c r="AD549" s="1"/>
     </row>
-    <row r="550" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18134,7 +18118,7 @@
       <c r="AC550" s="1"/>
       <c r="AD550" s="1"/>
     </row>
-    <row r="551" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18166,7 +18150,7 @@
       <c r="AC551" s="1"/>
       <c r="AD551" s="1"/>
     </row>
-    <row r="552" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18198,7 +18182,7 @@
       <c r="AC552" s="1"/>
       <c r="AD552" s="1"/>
     </row>
-    <row r="553" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18230,7 +18214,7 @@
       <c r="AC553" s="1"/>
       <c r="AD553" s="1"/>
     </row>
-    <row r="554" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18262,7 +18246,7 @@
       <c r="AC554" s="1"/>
       <c r="AD554" s="1"/>
     </row>
-    <row r="555" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18294,7 +18278,7 @@
       <c r="AC555" s="1"/>
       <c r="AD555" s="1"/>
     </row>
-    <row r="556" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18326,7 +18310,7 @@
       <c r="AC556" s="1"/>
       <c r="AD556" s="1"/>
     </row>
-    <row r="557" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18358,7 +18342,7 @@
       <c r="AC557" s="1"/>
       <c r="AD557" s="1"/>
     </row>
-    <row r="558" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18390,7 +18374,7 @@
       <c r="AC558" s="1"/>
       <c r="AD558" s="1"/>
     </row>
-    <row r="559" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18422,7 +18406,7 @@
       <c r="AC559" s="1"/>
       <c r="AD559" s="1"/>
     </row>
-    <row r="560" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18454,7 +18438,7 @@
       <c r="AC560" s="1"/>
       <c r="AD560" s="1"/>
     </row>
-    <row r="561" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18486,7 +18470,7 @@
       <c r="AC561" s="1"/>
       <c r="AD561" s="1"/>
     </row>
-    <row r="562" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18518,7 +18502,7 @@
       <c r="AC562" s="1"/>
       <c r="AD562" s="1"/>
     </row>
-    <row r="563" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18550,7 +18534,7 @@
       <c r="AC563" s="1"/>
       <c r="AD563" s="1"/>
     </row>
-    <row r="564" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18582,7 +18566,7 @@
       <c r="AC564" s="1"/>
       <c r="AD564" s="1"/>
     </row>
-    <row r="565" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18614,7 +18598,7 @@
       <c r="AC565" s="1"/>
       <c r="AD565" s="1"/>
     </row>
-    <row r="566" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18646,7 +18630,7 @@
       <c r="AC566" s="1"/>
       <c r="AD566" s="1"/>
     </row>
-    <row r="567" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18678,7 +18662,7 @@
       <c r="AC567" s="1"/>
       <c r="AD567" s="1"/>
     </row>
-    <row r="568" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18710,7 +18694,7 @@
       <c r="AC568" s="1"/>
       <c r="AD568" s="1"/>
     </row>
-    <row r="569" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18742,7 +18726,7 @@
       <c r="AC569" s="1"/>
       <c r="AD569" s="1"/>
     </row>
-    <row r="570" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18774,7 +18758,7 @@
       <c r="AC570" s="1"/>
       <c r="AD570" s="1"/>
     </row>
-    <row r="571" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18806,7 +18790,7 @@
       <c r="AC571" s="1"/>
       <c r="AD571" s="1"/>
     </row>
-    <row r="572" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18838,7 +18822,7 @@
       <c r="AC572" s="1"/>
       <c r="AD572" s="1"/>
     </row>
-    <row r="573" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18870,7 +18854,7 @@
       <c r="AC573" s="1"/>
       <c r="AD573" s="1"/>
     </row>
-    <row r="574" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18902,7 +18886,7 @@
       <c r="AC574" s="1"/>
       <c r="AD574" s="1"/>
     </row>
-    <row r="575" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18934,7 +18918,7 @@
       <c r="AC575" s="1"/>
       <c r="AD575" s="1"/>
     </row>
-    <row r="576" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18966,7 +18950,7 @@
       <c r="AC576" s="1"/>
       <c r="AD576" s="1"/>
     </row>
-    <row r="577" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18998,7 +18982,7 @@
       <c r="AC577" s="1"/>
       <c r="AD577" s="1"/>
     </row>
-    <row r="578" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19030,7 +19014,7 @@
       <c r="AC578" s="1"/>
       <c r="AD578" s="1"/>
     </row>
-    <row r="579" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19062,7 +19046,7 @@
       <c r="AC579" s="1"/>
       <c r="AD579" s="1"/>
     </row>
-    <row r="580" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19094,7 +19078,7 @@
       <c r="AC580" s="1"/>
       <c r="AD580" s="1"/>
     </row>
-    <row r="581" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19126,7 +19110,7 @@
       <c r="AC581" s="1"/>
       <c r="AD581" s="1"/>
     </row>
-    <row r="582" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19158,7 +19142,7 @@
       <c r="AC582" s="1"/>
       <c r="AD582" s="1"/>
     </row>
-    <row r="583" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19190,7 +19174,7 @@
       <c r="AC583" s="1"/>
       <c r="AD583" s="1"/>
     </row>
-    <row r="584" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19222,7 +19206,7 @@
       <c r="AC584" s="1"/>
       <c r="AD584" s="1"/>
     </row>
-    <row r="585" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19254,7 +19238,7 @@
       <c r="AC585" s="1"/>
       <c r="AD585" s="1"/>
     </row>
-    <row r="586" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19286,7 +19270,7 @@
       <c r="AC586" s="1"/>
       <c r="AD586" s="1"/>
     </row>
-    <row r="587" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19318,7 +19302,7 @@
       <c r="AC587" s="1"/>
       <c r="AD587" s="1"/>
     </row>
-    <row r="588" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19350,7 +19334,7 @@
       <c r="AC588" s="1"/>
       <c r="AD588" s="1"/>
     </row>
-    <row r="589" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19382,7 +19366,7 @@
       <c r="AC589" s="1"/>
       <c r="AD589" s="1"/>
     </row>
-    <row r="590" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19414,7 +19398,7 @@
       <c r="AC590" s="1"/>
       <c r="AD590" s="1"/>
     </row>
-    <row r="591" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19446,7 +19430,7 @@
       <c r="AC591" s="1"/>
       <c r="AD591" s="1"/>
     </row>
-    <row r="592" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19478,7 +19462,7 @@
       <c r="AC592" s="1"/>
       <c r="AD592" s="1"/>
     </row>
-    <row r="593" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19510,7 +19494,7 @@
       <c r="AC593" s="1"/>
       <c r="AD593" s="1"/>
     </row>
-    <row r="594" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19542,7 +19526,7 @@
       <c r="AC594" s="1"/>
       <c r="AD594" s="1"/>
     </row>
-    <row r="595" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19574,7 +19558,7 @@
       <c r="AC595" s="1"/>
       <c r="AD595" s="1"/>
     </row>
-    <row r="596" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19606,7 +19590,7 @@
       <c r="AC596" s="1"/>
       <c r="AD596" s="1"/>
     </row>
-    <row r="597" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19638,7 +19622,7 @@
       <c r="AC597" s="1"/>
       <c r="AD597" s="1"/>
     </row>
-    <row r="598" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19670,7 +19654,7 @@
       <c r="AC598" s="1"/>
       <c r="AD598" s="1"/>
     </row>
-    <row r="599" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19702,7 +19686,7 @@
       <c r="AC599" s="1"/>
       <c r="AD599" s="1"/>
     </row>
-    <row r="600" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19734,7 +19718,7 @@
       <c r="AC600" s="1"/>
       <c r="AD600" s="1"/>
     </row>
-    <row r="601" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19766,7 +19750,7 @@
       <c r="AC601" s="1"/>
       <c r="AD601" s="1"/>
     </row>
-    <row r="602" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19798,7 +19782,7 @@
       <c r="AC602" s="1"/>
       <c r="AD602" s="1"/>
     </row>
-    <row r="603" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19830,7 +19814,7 @@
       <c r="AC603" s="1"/>
       <c r="AD603" s="1"/>
     </row>
-    <row r="604" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19862,7 +19846,7 @@
       <c r="AC604" s="1"/>
       <c r="AD604" s="1"/>
     </row>
-    <row r="605" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19894,7 +19878,7 @@
       <c r="AC605" s="1"/>
       <c r="AD605" s="1"/>
     </row>
-    <row r="606" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19926,7 +19910,7 @@
       <c r="AC606" s="1"/>
       <c r="AD606" s="1"/>
     </row>
-    <row r="607" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19958,7 +19942,7 @@
       <c r="AC607" s="1"/>
       <c r="AD607" s="1"/>
     </row>
-    <row r="608" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19990,7 +19974,7 @@
       <c r="AC608" s="1"/>
       <c r="AD608" s="1"/>
     </row>
-    <row r="609" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20022,7 +20006,7 @@
       <c r="AC609" s="1"/>
       <c r="AD609" s="1"/>
     </row>
-    <row r="610" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20054,7 +20038,7 @@
       <c r="AC610" s="1"/>
       <c r="AD610" s="1"/>
     </row>
-    <row r="611" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20086,7 +20070,7 @@
       <c r="AC611" s="1"/>
       <c r="AD611" s="1"/>
     </row>
-    <row r="612" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20118,7 +20102,7 @@
       <c r="AC612" s="1"/>
       <c r="AD612" s="1"/>
     </row>
-    <row r="613" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20150,7 +20134,7 @@
       <c r="AC613" s="1"/>
       <c r="AD613" s="1"/>
     </row>
-    <row r="614" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20182,7 +20166,7 @@
       <c r="AC614" s="1"/>
       <c r="AD614" s="1"/>
     </row>
-    <row r="615" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20214,7 +20198,7 @@
       <c r="AC615" s="1"/>
       <c r="AD615" s="1"/>
     </row>
-    <row r="616" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20246,7 +20230,7 @@
       <c r="AC616" s="1"/>
       <c r="AD616" s="1"/>
     </row>
-    <row r="617" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20278,7 +20262,7 @@
       <c r="AC617" s="1"/>
       <c r="AD617" s="1"/>
     </row>
-    <row r="618" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20310,7 +20294,7 @@
       <c r="AC618" s="1"/>
       <c r="AD618" s="1"/>
     </row>
-    <row r="619" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20342,7 +20326,7 @@
       <c r="AC619" s="1"/>
       <c r="AD619" s="1"/>
     </row>
-    <row r="620" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20374,7 +20358,7 @@
       <c r="AC620" s="1"/>
       <c r="AD620" s="1"/>
     </row>
-    <row r="621" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20406,7 +20390,7 @@
       <c r="AC621" s="1"/>
       <c r="AD621" s="1"/>
     </row>
-    <row r="622" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20438,7 +20422,7 @@
       <c r="AC622" s="1"/>
       <c r="AD622" s="1"/>
     </row>
-    <row r="623" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20470,7 +20454,7 @@
       <c r="AC623" s="1"/>
       <c r="AD623" s="1"/>
     </row>
-    <row r="624" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20502,7 +20486,7 @@
       <c r="AC624" s="1"/>
       <c r="AD624" s="1"/>
     </row>
-    <row r="625" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20534,7 +20518,7 @@
       <c r="AC625" s="1"/>
       <c r="AD625" s="1"/>
     </row>
-    <row r="626" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20566,7 +20550,7 @@
       <c r="AC626" s="1"/>
       <c r="AD626" s="1"/>
     </row>
-    <row r="627" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20598,7 +20582,7 @@
       <c r="AC627" s="1"/>
       <c r="AD627" s="1"/>
     </row>
-    <row r="628" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20630,7 +20614,7 @@
       <c r="AC628" s="1"/>
       <c r="AD628" s="1"/>
     </row>
-    <row r="629" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20662,7 +20646,7 @@
       <c r="AC629" s="1"/>
       <c r="AD629" s="1"/>
     </row>
-    <row r="630" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20694,7 +20678,7 @@
       <c r="AC630" s="1"/>
       <c r="AD630" s="1"/>
     </row>
-    <row r="631" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20726,7 +20710,7 @@
       <c r="AC631" s="1"/>
       <c r="AD631" s="1"/>
     </row>
-    <row r="632" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20758,7 +20742,7 @@
       <c r="AC632" s="1"/>
       <c r="AD632" s="1"/>
     </row>
-    <row r="633" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20790,7 +20774,7 @@
       <c r="AC633" s="1"/>
       <c r="AD633" s="1"/>
     </row>
-    <row r="634" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20822,7 +20806,7 @@
       <c r="AC634" s="1"/>
       <c r="AD634" s="1"/>
     </row>
-    <row r="635" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20854,7 +20838,7 @@
       <c r="AC635" s="1"/>
       <c r="AD635" s="1"/>
     </row>
-    <row r="636" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20886,7 +20870,7 @@
       <c r="AC636" s="1"/>
       <c r="AD636" s="1"/>
     </row>
-    <row r="637" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20918,7 +20902,7 @@
       <c r="AC637" s="1"/>
       <c r="AD637" s="1"/>
     </row>
-    <row r="638" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20950,7 +20934,7 @@
       <c r="AC638" s="1"/>
       <c r="AD638" s="1"/>
     </row>
-    <row r="639" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20982,7 +20966,7 @@
       <c r="AC639" s="1"/>
       <c r="AD639" s="1"/>
     </row>
-    <row r="640" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -21014,7 +20998,7 @@
       <c r="AC640" s="1"/>
       <c r="AD640" s="1"/>
     </row>
-    <row r="641" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21046,7 +21030,7 @@
       <c r="AC641" s="1"/>
       <c r="AD641" s="1"/>
     </row>
-    <row r="642" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21078,7 +21062,7 @@
       <c r="AC642" s="1"/>
       <c r="AD642" s="1"/>
     </row>
-    <row r="643" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21110,7 +21094,7 @@
       <c r="AC643" s="1"/>
       <c r="AD643" s="1"/>
     </row>
-    <row r="644" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21142,7 +21126,7 @@
       <c r="AC644" s="1"/>
       <c r="AD644" s="1"/>
     </row>
-    <row r="645" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21174,7 +21158,7 @@
       <c r="AC645" s="1"/>
       <c r="AD645" s="1"/>
     </row>
-    <row r="646" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21206,7 +21190,7 @@
       <c r="AC646" s="1"/>
       <c r="AD646" s="1"/>
     </row>
-    <row r="647" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21238,7 +21222,7 @@
       <c r="AC647" s="1"/>
       <c r="AD647" s="1"/>
     </row>
-    <row r="648" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21270,7 +21254,7 @@
       <c r="AC648" s="1"/>
       <c r="AD648" s="1"/>
     </row>
-    <row r="649" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21302,7 +21286,7 @@
       <c r="AC649" s="1"/>
       <c r="AD649" s="1"/>
     </row>
-    <row r="650" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21334,7 +21318,7 @@
       <c r="AC650" s="1"/>
       <c r="AD650" s="1"/>
     </row>
-    <row r="651" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21366,7 +21350,7 @@
       <c r="AC651" s="1"/>
       <c r="AD651" s="1"/>
     </row>
-    <row r="652" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21398,7 +21382,7 @@
       <c r="AC652" s="1"/>
       <c r="AD652" s="1"/>
     </row>
-    <row r="653" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21430,7 +21414,7 @@
       <c r="AC653" s="1"/>
       <c r="AD653" s="1"/>
     </row>
-    <row r="654" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21462,7 +21446,7 @@
       <c r="AC654" s="1"/>
       <c r="AD654" s="1"/>
     </row>
-    <row r="655" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21494,7 +21478,7 @@
       <c r="AC655" s="1"/>
       <c r="AD655" s="1"/>
     </row>
-    <row r="656" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21526,7 +21510,7 @@
       <c r="AC656" s="1"/>
       <c r="AD656" s="1"/>
     </row>
-    <row r="657" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21558,7 +21542,7 @@
       <c r="AC657" s="1"/>
       <c r="AD657" s="1"/>
     </row>
-    <row r="658" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21590,7 +21574,7 @@
       <c r="AC658" s="1"/>
       <c r="AD658" s="1"/>
     </row>
-    <row r="659" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21622,7 +21606,7 @@
       <c r="AC659" s="1"/>
       <c r="AD659" s="1"/>
     </row>
-    <row r="660" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21654,7 +21638,7 @@
       <c r="AC660" s="1"/>
       <c r="AD660" s="1"/>
     </row>
-    <row r="661" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21686,7 +21670,7 @@
       <c r="AC661" s="1"/>
       <c r="AD661" s="1"/>
     </row>
-    <row r="662" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21718,7 +21702,7 @@
       <c r="AC662" s="1"/>
       <c r="AD662" s="1"/>
     </row>
-    <row r="663" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21750,7 +21734,7 @@
       <c r="AC663" s="1"/>
       <c r="AD663" s="1"/>
     </row>
-    <row r="664" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21782,7 +21766,7 @@
       <c r="AC664" s="1"/>
       <c r="AD664" s="1"/>
     </row>
-    <row r="665" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21814,7 +21798,7 @@
       <c r="AC665" s="1"/>
       <c r="AD665" s="1"/>
     </row>
-    <row r="666" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21846,7 +21830,7 @@
       <c r="AC666" s="1"/>
       <c r="AD666" s="1"/>
     </row>
-    <row r="667" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21878,7 +21862,7 @@
       <c r="AC667" s="1"/>
       <c r="AD667" s="1"/>
     </row>
-    <row r="668" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21910,7 +21894,7 @@
       <c r="AC668" s="1"/>
       <c r="AD668" s="1"/>
     </row>
-    <row r="669" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21942,7 +21926,7 @@
       <c r="AC669" s="1"/>
       <c r="AD669" s="1"/>
     </row>
-    <row r="670" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21974,7 +21958,7 @@
       <c r="AC670" s="1"/>
       <c r="AD670" s="1"/>
     </row>
-    <row r="671" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -22006,7 +21990,7 @@
       <c r="AC671" s="1"/>
       <c r="AD671" s="1"/>
     </row>
-    <row r="672" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -22038,7 +22022,7 @@
       <c r="AC672" s="1"/>
       <c r="AD672" s="1"/>
     </row>
-    <row r="673" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22070,7 +22054,7 @@
       <c r="AC673" s="1"/>
       <c r="AD673" s="1"/>
     </row>
-    <row r="674" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22102,7 +22086,7 @@
       <c r="AC674" s="1"/>
       <c r="AD674" s="1"/>
     </row>
-    <row r="675" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22134,7 +22118,7 @@
       <c r="AC675" s="1"/>
       <c r="AD675" s="1"/>
     </row>
-    <row r="676" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22166,7 +22150,7 @@
       <c r="AC676" s="1"/>
       <c r="AD676" s="1"/>
     </row>
-    <row r="677" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22198,7 +22182,7 @@
       <c r="AC677" s="1"/>
       <c r="AD677" s="1"/>
     </row>
-    <row r="678" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22230,7 +22214,7 @@
       <c r="AC678" s="1"/>
       <c r="AD678" s="1"/>
     </row>
-    <row r="679" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22262,7 +22246,7 @@
       <c r="AC679" s="1"/>
       <c r="AD679" s="1"/>
     </row>
-    <row r="680" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22294,7 +22278,7 @@
       <c r="AC680" s="1"/>
       <c r="AD680" s="1"/>
     </row>
-    <row r="681" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22326,7 +22310,7 @@
       <c r="AC681" s="1"/>
       <c r="AD681" s="1"/>
     </row>
-    <row r="682" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22358,7 +22342,7 @@
       <c r="AC682" s="1"/>
       <c r="AD682" s="1"/>
     </row>
-    <row r="683" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22390,7 +22374,7 @@
       <c r="AC683" s="1"/>
       <c r="AD683" s="1"/>
     </row>
-    <row r="684" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22422,7 +22406,7 @@
       <c r="AC684" s="1"/>
       <c r="AD684" s="1"/>
     </row>
-    <row r="685" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22454,7 +22438,7 @@
       <c r="AC685" s="1"/>
       <c r="AD685" s="1"/>
     </row>
-    <row r="686" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22486,7 +22470,7 @@
       <c r="AC686" s="1"/>
       <c r="AD686" s="1"/>
     </row>
-    <row r="687" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22518,7 +22502,7 @@
       <c r="AC687" s="1"/>
       <c r="AD687" s="1"/>
     </row>
-    <row r="688" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22550,7 +22534,7 @@
       <c r="AC688" s="1"/>
       <c r="AD688" s="1"/>
     </row>
-    <row r="689" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22582,7 +22566,7 @@
       <c r="AC689" s="1"/>
       <c r="AD689" s="1"/>
     </row>
-    <row r="690" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22614,7 +22598,7 @@
       <c r="AC690" s="1"/>
       <c r="AD690" s="1"/>
     </row>
-    <row r="691" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22646,7 +22630,7 @@
       <c r="AC691" s="1"/>
       <c r="AD691" s="1"/>
     </row>
-    <row r="692" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22678,7 +22662,7 @@
       <c r="AC692" s="1"/>
       <c r="AD692" s="1"/>
     </row>
-    <row r="693" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22710,7 +22694,7 @@
       <c r="AC693" s="1"/>
       <c r="AD693" s="1"/>
     </row>
-    <row r="694" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22742,7 +22726,7 @@
       <c r="AC694" s="1"/>
       <c r="AD694" s="1"/>
     </row>
-    <row r="695" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22774,7 +22758,7 @@
       <c r="AC695" s="1"/>
       <c r="AD695" s="1"/>
     </row>
-    <row r="696" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22806,7 +22790,7 @@
       <c r="AC696" s="1"/>
       <c r="AD696" s="1"/>
     </row>
-    <row r="697" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22838,7 +22822,7 @@
       <c r="AC697" s="1"/>
       <c r="AD697" s="1"/>
     </row>
-    <row r="698" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22870,7 +22854,7 @@
       <c r="AC698" s="1"/>
       <c r="AD698" s="1"/>
     </row>
-    <row r="699" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22902,7 +22886,7 @@
       <c r="AC699" s="1"/>
       <c r="AD699" s="1"/>
     </row>
-    <row r="700" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22934,7 +22918,7 @@
       <c r="AC700" s="1"/>
       <c r="AD700" s="1"/>
     </row>
-    <row r="701" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22966,7 +22950,7 @@
       <c r="AC701" s="1"/>
       <c r="AD701" s="1"/>
     </row>
-    <row r="702" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22998,7 +22982,7 @@
       <c r="AC702" s="1"/>
       <c r="AD702" s="1"/>
     </row>
-    <row r="703" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -23030,7 +23014,7 @@
       <c r="AC703" s="1"/>
       <c r="AD703" s="1"/>
     </row>
-    <row r="704" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -23062,7 +23046,7 @@
       <c r="AC704" s="1"/>
       <c r="AD704" s="1"/>
     </row>
-    <row r="705" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -23094,7 +23078,7 @@
       <c r="AC705" s="1"/>
       <c r="AD705" s="1"/>
     </row>
-    <row r="706" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23126,7 +23110,7 @@
       <c r="AC706" s="1"/>
       <c r="AD706" s="1"/>
     </row>
-    <row r="707" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23158,7 +23142,7 @@
       <c r="AC707" s="1"/>
       <c r="AD707" s="1"/>
     </row>
-    <row r="708" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23190,7 +23174,7 @@
       <c r="AC708" s="1"/>
       <c r="AD708" s="1"/>
     </row>
-    <row r="709" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23222,7 +23206,7 @@
       <c r="AC709" s="1"/>
       <c r="AD709" s="1"/>
     </row>
-    <row r="710" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23254,7 +23238,7 @@
       <c r="AC710" s="1"/>
       <c r="AD710" s="1"/>
     </row>
-    <row r="711" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23286,7 +23270,7 @@
       <c r="AC711" s="1"/>
       <c r="AD711" s="1"/>
     </row>
-    <row r="712" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23318,7 +23302,7 @@
       <c r="AC712" s="1"/>
       <c r="AD712" s="1"/>
     </row>
-    <row r="713" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23350,7 +23334,7 @@
       <c r="AC713" s="1"/>
       <c r="AD713" s="1"/>
     </row>
-    <row r="714" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23382,7 +23366,7 @@
       <c r="AC714" s="1"/>
       <c r="AD714" s="1"/>
     </row>
-    <row r="715" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23414,7 +23398,7 @@
       <c r="AC715" s="1"/>
       <c r="AD715" s="1"/>
     </row>
-    <row r="716" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23446,7 +23430,7 @@
       <c r="AC716" s="1"/>
       <c r="AD716" s="1"/>
     </row>
-    <row r="717" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23478,7 +23462,7 @@
       <c r="AC717" s="1"/>
       <c r="AD717" s="1"/>
     </row>
-    <row r="718" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23510,7 +23494,7 @@
       <c r="AC718" s="1"/>
       <c r="AD718" s="1"/>
     </row>
-    <row r="719" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23542,7 +23526,7 @@
       <c r="AC719" s="1"/>
       <c r="AD719" s="1"/>
     </row>
-    <row r="720" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23574,7 +23558,7 @@
       <c r="AC720" s="1"/>
       <c r="AD720" s="1"/>
     </row>
-    <row r="721" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23606,7 +23590,7 @@
       <c r="AC721" s="1"/>
       <c r="AD721" s="1"/>
     </row>
-    <row r="722" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23638,7 +23622,7 @@
       <c r="AC722" s="1"/>
       <c r="AD722" s="1"/>
     </row>
-    <row r="723" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23670,7 +23654,7 @@
       <c r="AC723" s="1"/>
       <c r="AD723" s="1"/>
     </row>
-    <row r="724" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23702,7 +23686,7 @@
       <c r="AC724" s="1"/>
       <c r="AD724" s="1"/>
     </row>
-    <row r="725" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23734,7 +23718,7 @@
       <c r="AC725" s="1"/>
       <c r="AD725" s="1"/>
     </row>
-    <row r="726" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23766,7 +23750,7 @@
       <c r="AC726" s="1"/>
       <c r="AD726" s="1"/>
     </row>
-    <row r="727" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23798,7 +23782,7 @@
       <c r="AC727" s="1"/>
       <c r="AD727" s="1"/>
     </row>
-    <row r="728" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23830,7 +23814,7 @@
       <c r="AC728" s="1"/>
       <c r="AD728" s="1"/>
     </row>
-    <row r="729" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23862,7 +23846,7 @@
       <c r="AC729" s="1"/>
       <c r="AD729" s="1"/>
     </row>
-    <row r="730" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23894,7 +23878,7 @@
       <c r="AC730" s="1"/>
       <c r="AD730" s="1"/>
     </row>
-    <row r="731" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23926,7 +23910,7 @@
       <c r="AC731" s="1"/>
       <c r="AD731" s="1"/>
     </row>
-    <row r="732" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23958,7 +23942,7 @@
       <c r="AC732" s="1"/>
       <c r="AD732" s="1"/>
     </row>
-    <row r="733" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23990,7 +23974,7 @@
       <c r="AC733" s="1"/>
       <c r="AD733" s="1"/>
     </row>
-    <row r="734" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -24022,7 +24006,7 @@
       <c r="AC734" s="1"/>
       <c r="AD734" s="1"/>
     </row>
-    <row r="735" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -24054,7 +24038,7 @@
       <c r="AC735" s="1"/>
       <c r="AD735" s="1"/>
     </row>
-    <row r="736" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -24086,7 +24070,7 @@
       <c r="AC736" s="1"/>
       <c r="AD736" s="1"/>
     </row>
-    <row r="737" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -24118,7 +24102,7 @@
       <c r="AC737" s="1"/>
       <c r="AD737" s="1"/>
     </row>
-    <row r="738" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24150,7 +24134,7 @@
       <c r="AC738" s="1"/>
       <c r="AD738" s="1"/>
     </row>
-    <row r="739" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24182,7 +24166,7 @@
       <c r="AC739" s="1"/>
       <c r="AD739" s="1"/>
     </row>
-    <row r="740" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24214,7 +24198,7 @@
       <c r="AC740" s="1"/>
       <c r="AD740" s="1"/>
     </row>
-    <row r="741" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24246,7 +24230,7 @@
       <c r="AC741" s="1"/>
       <c r="AD741" s="1"/>
     </row>
-    <row r="742" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24278,7 +24262,7 @@
       <c r="AC742" s="1"/>
       <c r="AD742" s="1"/>
     </row>
-    <row r="743" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24310,7 +24294,7 @@
       <c r="AC743" s="1"/>
       <c r="AD743" s="1"/>
     </row>
-    <row r="744" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24342,7 +24326,7 @@
       <c r="AC744" s="1"/>
       <c r="AD744" s="1"/>
     </row>
-    <row r="745" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24374,7 +24358,7 @@
       <c r="AC745" s="1"/>
       <c r="AD745" s="1"/>
     </row>
-    <row r="746" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24406,7 +24390,7 @@
       <c r="AC746" s="1"/>
       <c r="AD746" s="1"/>
     </row>
-    <row r="747" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24438,7 +24422,7 @@
       <c r="AC747" s="1"/>
       <c r="AD747" s="1"/>
     </row>
-    <row r="748" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24470,7 +24454,7 @@
       <c r="AC748" s="1"/>
       <c r="AD748" s="1"/>
     </row>
-    <row r="749" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24502,7 +24486,7 @@
       <c r="AC749" s="1"/>
       <c r="AD749" s="1"/>
     </row>
-    <row r="750" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24534,7 +24518,7 @@
       <c r="AC750" s="1"/>
       <c r="AD750" s="1"/>
     </row>
-    <row r="751" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24566,7 +24550,7 @@
       <c r="AC751" s="1"/>
       <c r="AD751" s="1"/>
     </row>
-    <row r="752" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24598,7 +24582,7 @@
       <c r="AC752" s="1"/>
       <c r="AD752" s="1"/>
     </row>
-    <row r="753" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24630,7 +24614,7 @@
       <c r="AC753" s="1"/>
       <c r="AD753" s="1"/>
     </row>
-    <row r="754" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24662,7 +24646,7 @@
       <c r="AC754" s="1"/>
       <c r="AD754" s="1"/>
     </row>
-    <row r="755" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24694,7 +24678,7 @@
       <c r="AC755" s="1"/>
       <c r="AD755" s="1"/>
     </row>
-    <row r="756" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24726,7 +24710,7 @@
       <c r="AC756" s="1"/>
       <c r="AD756" s="1"/>
     </row>
-    <row r="757" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24758,7 +24742,7 @@
       <c r="AC757" s="1"/>
       <c r="AD757" s="1"/>
     </row>
-    <row r="758" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24790,7 +24774,7 @@
       <c r="AC758" s="1"/>
       <c r="AD758" s="1"/>
     </row>
-    <row r="759" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24822,7 +24806,7 @@
       <c r="AC759" s="1"/>
       <c r="AD759" s="1"/>
     </row>
-    <row r="760" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24854,7 +24838,7 @@
       <c r="AC760" s="1"/>
       <c r="AD760" s="1"/>
     </row>
-    <row r="761" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24886,7 +24870,7 @@
       <c r="AC761" s="1"/>
       <c r="AD761" s="1"/>
     </row>
-    <row r="762" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24918,7 +24902,7 @@
       <c r="AC762" s="1"/>
       <c r="AD762" s="1"/>
     </row>
-    <row r="763" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24950,7 +24934,7 @@
       <c r="AC763" s="1"/>
       <c r="AD763" s="1"/>
     </row>
-    <row r="764" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24982,7 +24966,7 @@
       <c r="AC764" s="1"/>
       <c r="AD764" s="1"/>
     </row>
-    <row r="765" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -25014,7 +24998,7 @@
       <c r="AC765" s="1"/>
       <c r="AD765" s="1"/>
     </row>
-    <row r="766" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -25046,7 +25030,7 @@
       <c r="AC766" s="1"/>
       <c r="AD766" s="1"/>
     </row>
-    <row r="767" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -25078,7 +25062,7 @@
       <c r="AC767" s="1"/>
       <c r="AD767" s="1"/>
     </row>
-    <row r="768" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -25110,7 +25094,7 @@
       <c r="AC768" s="1"/>
       <c r="AD768" s="1"/>
     </row>
-    <row r="769" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -25142,7 +25126,7 @@
       <c r="AC769" s="1"/>
       <c r="AD769" s="1"/>
     </row>
-    <row r="770" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25174,7 +25158,7 @@
       <c r="AC770" s="1"/>
       <c r="AD770" s="1"/>
     </row>
-    <row r="771" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25206,7 +25190,7 @@
       <c r="AC771" s="1"/>
       <c r="AD771" s="1"/>
     </row>
-    <row r="772" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25238,7 +25222,7 @@
       <c r="AC772" s="1"/>
       <c r="AD772" s="1"/>
     </row>
-    <row r="773" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25270,7 +25254,7 @@
       <c r="AC773" s="1"/>
       <c r="AD773" s="1"/>
     </row>
-    <row r="774" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25302,7 +25286,7 @@
       <c r="AC774" s="1"/>
       <c r="AD774" s="1"/>
     </row>
-    <row r="775" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25334,7 +25318,7 @@
       <c r="AC775" s="1"/>
       <c r="AD775" s="1"/>
     </row>
-    <row r="776" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25366,7 +25350,7 @@
       <c r="AC776" s="1"/>
       <c r="AD776" s="1"/>
     </row>
-    <row r="777" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25398,7 +25382,7 @@
       <c r="AC777" s="1"/>
       <c r="AD777" s="1"/>
     </row>
-    <row r="778" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25430,7 +25414,7 @@
       <c r="AC778" s="1"/>
       <c r="AD778" s="1"/>
     </row>
-    <row r="779" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25462,7 +25446,7 @@
       <c r="AC779" s="1"/>
       <c r="AD779" s="1"/>
     </row>
-    <row r="780" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25494,7 +25478,7 @@
       <c r="AC780" s="1"/>
       <c r="AD780" s="1"/>
     </row>
-    <row r="781" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25526,7 +25510,7 @@
       <c r="AC781" s="1"/>
       <c r="AD781" s="1"/>
     </row>
-    <row r="782" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25558,7 +25542,7 @@
       <c r="AC782" s="1"/>
       <c r="AD782" s="1"/>
     </row>
-    <row r="783" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25590,7 +25574,7 @@
       <c r="AC783" s="1"/>
       <c r="AD783" s="1"/>
     </row>
-    <row r="784" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25622,7 +25606,7 @@
       <c r="AC784" s="1"/>
       <c r="AD784" s="1"/>
     </row>
-    <row r="785" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25654,7 +25638,7 @@
       <c r="AC785" s="1"/>
       <c r="AD785" s="1"/>
     </row>
-    <row r="786" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25686,7 +25670,7 @@
       <c r="AC786" s="1"/>
       <c r="AD786" s="1"/>
     </row>
-    <row r="787" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25718,7 +25702,7 @@
       <c r="AC787" s="1"/>
       <c r="AD787" s="1"/>
     </row>
-    <row r="788" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25750,7 +25734,7 @@
       <c r="AC788" s="1"/>
       <c r="AD788" s="1"/>
     </row>
-    <row r="789" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25782,7 +25766,7 @@
       <c r="AC789" s="1"/>
       <c r="AD789" s="1"/>
     </row>
-    <row r="790" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25814,7 +25798,7 @@
       <c r="AC790" s="1"/>
       <c r="AD790" s="1"/>
     </row>
-    <row r="791" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25846,7 +25830,7 @@
       <c r="AC791" s="1"/>
       <c r="AD791" s="1"/>
     </row>
-    <row r="792" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25878,7 +25862,7 @@
       <c r="AC792" s="1"/>
       <c r="AD792" s="1"/>
     </row>
-    <row r="793" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25910,7 +25894,7 @@
       <c r="AC793" s="1"/>
       <c r="AD793" s="1"/>
     </row>
-    <row r="794" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25942,7 +25926,7 @@
       <c r="AC794" s="1"/>
       <c r="AD794" s="1"/>
     </row>
-    <row r="795" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25974,7 +25958,7 @@
       <c r="AC795" s="1"/>
       <c r="AD795" s="1"/>
     </row>
-    <row r="796" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -26006,7 +25990,7 @@
       <c r="AC796" s="1"/>
       <c r="AD796" s="1"/>
     </row>
-    <row r="797" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -26038,7 +26022,7 @@
       <c r="AC797" s="1"/>
       <c r="AD797" s="1"/>
     </row>
-    <row r="798" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -26070,7 +26054,7 @@
       <c r="AC798" s="1"/>
       <c r="AD798" s="1"/>
     </row>
-    <row r="799" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -26102,7 +26086,7 @@
       <c r="AC799" s="1"/>
       <c r="AD799" s="1"/>
     </row>
-    <row r="800" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -26134,7 +26118,7 @@
       <c r="AC800" s="1"/>
       <c r="AD800" s="1"/>
     </row>
-    <row r="801" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -26166,7 +26150,7 @@
       <c r="AC801" s="1"/>
       <c r="AD801" s="1"/>
     </row>
-    <row r="802" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26198,7 +26182,7 @@
       <c r="AC802" s="1"/>
       <c r="AD802" s="1"/>
     </row>
-    <row r="803" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26230,7 +26214,7 @@
       <c r="AC803" s="1"/>
       <c r="AD803" s="1"/>
     </row>
-    <row r="804" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26262,7 +26246,7 @@
       <c r="AC804" s="1"/>
       <c r="AD804" s="1"/>
     </row>
-    <row r="805" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26294,7 +26278,7 @@
       <c r="AC805" s="1"/>
       <c r="AD805" s="1"/>
     </row>
-    <row r="806" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26326,7 +26310,7 @@
       <c r="AC806" s="1"/>
       <c r="AD806" s="1"/>
     </row>
-    <row r="807" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26358,7 +26342,7 @@
       <c r="AC807" s="1"/>
       <c r="AD807" s="1"/>
     </row>
-    <row r="808" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26390,7 +26374,7 @@
       <c r="AC808" s="1"/>
       <c r="AD808" s="1"/>
     </row>
-    <row r="809" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26422,7 +26406,7 @@
       <c r="AC809" s="1"/>
       <c r="AD809" s="1"/>
     </row>
-    <row r="810" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26454,7 +26438,7 @@
       <c r="AC810" s="1"/>
       <c r="AD810" s="1"/>
     </row>
-    <row r="811" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26486,7 +26470,7 @@
       <c r="AC811" s="1"/>
       <c r="AD811" s="1"/>
     </row>
-    <row r="812" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26518,7 +26502,7 @@
       <c r="AC812" s="1"/>
       <c r="AD812" s="1"/>
     </row>
-    <row r="813" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26550,7 +26534,7 @@
       <c r="AC813" s="1"/>
       <c r="AD813" s="1"/>
     </row>
-    <row r="814" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26582,7 +26566,7 @@
       <c r="AC814" s="1"/>
       <c r="AD814" s="1"/>
     </row>
-    <row r="815" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26614,7 +26598,7 @@
       <c r="AC815" s="1"/>
       <c r="AD815" s="1"/>
     </row>
-    <row r="816" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26646,7 +26630,7 @@
       <c r="AC816" s="1"/>
       <c r="AD816" s="1"/>
     </row>
-    <row r="817" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26678,7 +26662,7 @@
       <c r="AC817" s="1"/>
       <c r="AD817" s="1"/>
     </row>
-    <row r="818" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26710,7 +26694,7 @@
       <c r="AC818" s="1"/>
       <c r="AD818" s="1"/>
     </row>
-    <row r="819" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26742,7 +26726,7 @@
       <c r="AC819" s="1"/>
       <c r="AD819" s="1"/>
     </row>
-    <row r="820" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26774,7 +26758,7 @@
       <c r="AC820" s="1"/>
       <c r="AD820" s="1"/>
     </row>
-    <row r="821" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26806,7 +26790,7 @@
       <c r="AC821" s="1"/>
       <c r="AD821" s="1"/>
     </row>
-    <row r="822" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26838,7 +26822,7 @@
       <c r="AC822" s="1"/>
       <c r="AD822" s="1"/>
     </row>
-    <row r="823" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26870,7 +26854,7 @@
       <c r="AC823" s="1"/>
       <c r="AD823" s="1"/>
     </row>
-    <row r="824" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26902,7 +26886,7 @@
       <c r="AC824" s="1"/>
       <c r="AD824" s="1"/>
     </row>
-    <row r="825" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26934,7 +26918,7 @@
       <c r="AC825" s="1"/>
       <c r="AD825" s="1"/>
     </row>
-    <row r="826" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26966,7 +26950,7 @@
       <c r="AC826" s="1"/>
       <c r="AD826" s="1"/>
     </row>
-    <row r="827" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26998,7 +26982,7 @@
       <c r="AC827" s="1"/>
       <c r="AD827" s="1"/>
     </row>
-    <row r="828" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -27030,7 +27014,7 @@
       <c r="AC828" s="1"/>
       <c r="AD828" s="1"/>
     </row>
-    <row r="829" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -27062,7 +27046,7 @@
       <c r="AC829" s="1"/>
       <c r="AD829" s="1"/>
     </row>
-    <row r="830" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -27094,7 +27078,7 @@
       <c r="AC830" s="1"/>
       <c r="AD830" s="1"/>
     </row>
-    <row r="831" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -27126,7 +27110,7 @@
       <c r="AC831" s="1"/>
       <c r="AD831" s="1"/>
     </row>
-    <row r="832" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -27158,7 +27142,7 @@
       <c r="AC832" s="1"/>
       <c r="AD832" s="1"/>
     </row>
-    <row r="833" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -27190,7 +27174,7 @@
       <c r="AC833" s="1"/>
       <c r="AD833" s="1"/>
     </row>
-    <row r="834" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -27222,7 +27206,7 @@
       <c r="AC834" s="1"/>
       <c r="AD834" s="1"/>
     </row>
-    <row r="835" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27254,7 +27238,7 @@
       <c r="AC835" s="1"/>
       <c r="AD835" s="1"/>
     </row>
-    <row r="836" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27286,7 +27270,7 @@
       <c r="AC836" s="1"/>
       <c r="AD836" s="1"/>
     </row>
-    <row r="837" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27318,7 +27302,7 @@
       <c r="AC837" s="1"/>
       <c r="AD837" s="1"/>
     </row>
-    <row r="838" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27350,7 +27334,7 @@
       <c r="AC838" s="1"/>
       <c r="AD838" s="1"/>
     </row>
-    <row r="839" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27382,7 +27366,7 @@
       <c r="AC839" s="1"/>
       <c r="AD839" s="1"/>
     </row>
-    <row r="840" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27414,7 +27398,7 @@
       <c r="AC840" s="1"/>
       <c r="AD840" s="1"/>
     </row>
-    <row r="841" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27446,7 +27430,7 @@
       <c r="AC841" s="1"/>
       <c r="AD841" s="1"/>
     </row>
-    <row r="842" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27478,7 +27462,7 @@
       <c r="AC842" s="1"/>
       <c r="AD842" s="1"/>
     </row>
-    <row r="843" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27510,7 +27494,7 @@
       <c r="AC843" s="1"/>
       <c r="AD843" s="1"/>
     </row>
-    <row r="844" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27542,7 +27526,7 @@
       <c r="AC844" s="1"/>
       <c r="AD844" s="1"/>
     </row>
-    <row r="845" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27574,7 +27558,7 @@
       <c r="AC845" s="1"/>
       <c r="AD845" s="1"/>
     </row>
-    <row r="846" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27606,7 +27590,7 @@
       <c r="AC846" s="1"/>
       <c r="AD846" s="1"/>
     </row>
-    <row r="847" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27638,7 +27622,7 @@
       <c r="AC847" s="1"/>
       <c r="AD847" s="1"/>
     </row>
-    <row r="848" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27670,7 +27654,7 @@
       <c r="AC848" s="1"/>
       <c r="AD848" s="1"/>
     </row>
-    <row r="849" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27702,7 +27686,7 @@
       <c r="AC849" s="1"/>
       <c r="AD849" s="1"/>
     </row>
-    <row r="850" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27734,7 +27718,7 @@
       <c r="AC850" s="1"/>
       <c r="AD850" s="1"/>
     </row>
-    <row r="851" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27766,7 +27750,7 @@
       <c r="AC851" s="1"/>
       <c r="AD851" s="1"/>
     </row>
-    <row r="852" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27798,7 +27782,7 @@
       <c r="AC852" s="1"/>
       <c r="AD852" s="1"/>
     </row>
-    <row r="853" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27830,7 +27814,7 @@
       <c r="AC853" s="1"/>
       <c r="AD853" s="1"/>
     </row>
-    <row r="854" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27862,7 +27846,7 @@
       <c r="AC854" s="1"/>
       <c r="AD854" s="1"/>
     </row>
-    <row r="855" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27894,7 +27878,7 @@
       <c r="AC855" s="1"/>
       <c r="AD855" s="1"/>
     </row>
-    <row r="856" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27926,7 +27910,7 @@
       <c r="AC856" s="1"/>
       <c r="AD856" s="1"/>
     </row>
-    <row r="857" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27958,7 +27942,7 @@
       <c r="AC857" s="1"/>
       <c r="AD857" s="1"/>
     </row>
-    <row r="858" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27990,7 +27974,7 @@
       <c r="AC858" s="1"/>
       <c r="AD858" s="1"/>
     </row>
-    <row r="859" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -28022,7 +28006,7 @@
       <c r="AC859" s="1"/>
       <c r="AD859" s="1"/>
     </row>
-    <row r="860" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -28054,7 +28038,7 @@
       <c r="AC860" s="1"/>
       <c r="AD860" s="1"/>
     </row>
-    <row r="861" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -28086,7 +28070,7 @@
       <c r="AC861" s="1"/>
       <c r="AD861" s="1"/>
     </row>
-    <row r="862" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -28118,7 +28102,7 @@
       <c r="AC862" s="1"/>
       <c r="AD862" s="1"/>
     </row>
-    <row r="863" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -28150,7 +28134,7 @@
       <c r="AC863" s="1"/>
       <c r="AD863" s="1"/>
     </row>
-    <row r="864" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -28182,7 +28166,7 @@
       <c r="AC864" s="1"/>
       <c r="AD864" s="1"/>
     </row>
-    <row r="865" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -28214,7 +28198,7 @@
       <c r="AC865" s="1"/>
       <c r="AD865" s="1"/>
     </row>
-    <row r="866" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -28246,7 +28230,7 @@
       <c r="AC866" s="1"/>
       <c r="AD866" s="1"/>
     </row>
-    <row r="867" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28278,7 +28262,7 @@
       <c r="AC867" s="1"/>
       <c r="AD867" s="1"/>
     </row>
-    <row r="868" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28310,7 +28294,7 @@
       <c r="AC868" s="1"/>
       <c r="AD868" s="1"/>
     </row>
-    <row r="869" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28342,7 +28326,7 @@
       <c r="AC869" s="1"/>
       <c r="AD869" s="1"/>
     </row>
-    <row r="870" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28374,7 +28358,7 @@
       <c r="AC870" s="1"/>
       <c r="AD870" s="1"/>
     </row>
-    <row r="871" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28406,7 +28390,7 @@
       <c r="AC871" s="1"/>
       <c r="AD871" s="1"/>
     </row>
-    <row r="872" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28438,7 +28422,7 @@
       <c r="AC872" s="1"/>
       <c r="AD872" s="1"/>
     </row>
-    <row r="873" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28470,7 +28454,7 @@
       <c r="AC873" s="1"/>
       <c r="AD873" s="1"/>
     </row>
-    <row r="874" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28502,7 +28486,7 @@
       <c r="AC874" s="1"/>
       <c r="AD874" s="1"/>
     </row>
-    <row r="875" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28534,7 +28518,7 @@
       <c r="AC875" s="1"/>
       <c r="AD875" s="1"/>
     </row>
-    <row r="876" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28566,7 +28550,7 @@
       <c r="AC876" s="1"/>
       <c r="AD876" s="1"/>
     </row>
-    <row r="877" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28598,7 +28582,7 @@
       <c r="AC877" s="1"/>
       <c r="AD877" s="1"/>
     </row>
-    <row r="878" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28630,7 +28614,7 @@
       <c r="AC878" s="1"/>
       <c r="AD878" s="1"/>
     </row>
-    <row r="879" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28662,7 +28646,7 @@
       <c r="AC879" s="1"/>
       <c r="AD879" s="1"/>
     </row>
-    <row r="880" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28694,7 +28678,7 @@
       <c r="AC880" s="1"/>
       <c r="AD880" s="1"/>
     </row>
-    <row r="881" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28726,7 +28710,7 @@
       <c r="AC881" s="1"/>
       <c r="AD881" s="1"/>
     </row>
-    <row r="882" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28758,7 +28742,7 @@
       <c r="AC882" s="1"/>
       <c r="AD882" s="1"/>
     </row>
-    <row r="883" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28790,7 +28774,7 @@
       <c r="AC883" s="1"/>
       <c r="AD883" s="1"/>
     </row>
-    <row r="884" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28822,7 +28806,7 @@
       <c r="AC884" s="1"/>
       <c r="AD884" s="1"/>
     </row>
-    <row r="885" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28854,7 +28838,7 @@
       <c r="AC885" s="1"/>
       <c r="AD885" s="1"/>
     </row>
-    <row r="886" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28886,7 +28870,7 @@
       <c r="AC886" s="1"/>
       <c r="AD886" s="1"/>
     </row>
-    <row r="887" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28918,7 +28902,7 @@
       <c r="AC887" s="1"/>
       <c r="AD887" s="1"/>
     </row>
-    <row r="888" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28950,7 +28934,7 @@
       <c r="AC888" s="1"/>
       <c r="AD888" s="1"/>
     </row>
-    <row r="889" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28982,7 +28966,7 @@
       <c r="AC889" s="1"/>
       <c r="AD889" s="1"/>
     </row>
-    <row r="890" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -29014,7 +28998,7 @@
       <c r="AC890" s="1"/>
       <c r="AD890" s="1"/>
     </row>
-    <row r="891" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -29046,7 +29030,7 @@
       <c r="AC891" s="1"/>
       <c r="AD891" s="1"/>
     </row>
-    <row r="892" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -29078,7 +29062,7 @@
       <c r="AC892" s="1"/>
       <c r="AD892" s="1"/>
     </row>
-    <row r="893" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -29110,7 +29094,7 @@
       <c r="AC893" s="1"/>
       <c r="AD893" s="1"/>
     </row>
-    <row r="894" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -29142,7 +29126,7 @@
       <c r="AC894" s="1"/>
       <c r="AD894" s="1"/>
     </row>
-    <row r="895" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -29174,7 +29158,7 @@
       <c r="AC895" s="1"/>
       <c r="AD895" s="1"/>
     </row>
-    <row r="896" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -29206,7 +29190,7 @@
       <c r="AC896" s="1"/>
       <c r="AD896" s="1"/>
     </row>
-    <row r="897" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -29238,7 +29222,7 @@
       <c r="AC897" s="1"/>
       <c r="AD897" s="1"/>
     </row>
-    <row r="898" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -29270,7 +29254,7 @@
       <c r="AC898" s="1"/>
       <c r="AD898" s="1"/>
     </row>
-    <row r="899" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29302,7 +29286,7 @@
       <c r="AC899" s="1"/>
       <c r="AD899" s="1"/>
     </row>
-    <row r="900" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29334,7 +29318,7 @@
       <c r="AC900" s="1"/>
       <c r="AD900" s="1"/>
     </row>
-    <row r="901" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29366,7 +29350,7 @@
       <c r="AC901" s="1"/>
       <c r="AD901" s="1"/>
     </row>
-    <row r="902" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29398,7 +29382,7 @@
       <c r="AC902" s="1"/>
       <c r="AD902" s="1"/>
     </row>
-    <row r="903" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29430,7 +29414,7 @@
       <c r="AC903" s="1"/>
       <c r="AD903" s="1"/>
     </row>
-    <row r="904" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29462,7 +29446,7 @@
       <c r="AC904" s="1"/>
       <c r="AD904" s="1"/>
     </row>
-    <row r="905" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29494,7 +29478,7 @@
       <c r="AC905" s="1"/>
       <c r="AD905" s="1"/>
     </row>
-    <row r="906" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29526,7 +29510,7 @@
       <c r="AC906" s="1"/>
       <c r="AD906" s="1"/>
     </row>
-    <row r="907" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29558,7 +29542,7 @@
       <c r="AC907" s="1"/>
       <c r="AD907" s="1"/>
     </row>
-    <row r="908" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29590,7 +29574,7 @@
       <c r="AC908" s="1"/>
       <c r="AD908" s="1"/>
     </row>
-    <row r="909" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29622,7 +29606,7 @@
       <c r="AC909" s="1"/>
       <c r="AD909" s="1"/>
     </row>
-    <row r="910" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29654,7 +29638,7 @@
       <c r="AC910" s="1"/>
       <c r="AD910" s="1"/>
     </row>
-    <row r="911" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29686,7 +29670,7 @@
       <c r="AC911" s="1"/>
       <c r="AD911" s="1"/>
     </row>
-    <row r="912" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29718,7 +29702,7 @@
       <c r="AC912" s="1"/>
       <c r="AD912" s="1"/>
     </row>
-    <row r="913" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29750,7 +29734,7 @@
       <c r="AC913" s="1"/>
       <c r="AD913" s="1"/>
     </row>
-    <row r="914" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29782,7 +29766,7 @@
       <c r="AC914" s="1"/>
       <c r="AD914" s="1"/>
     </row>
-    <row r="915" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29814,7 +29798,7 @@
       <c r="AC915" s="1"/>
       <c r="AD915" s="1"/>
     </row>
-    <row r="916" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29846,7 +29830,7 @@
       <c r="AC916" s="1"/>
       <c r="AD916" s="1"/>
     </row>
-    <row r="917" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29878,7 +29862,7 @@
       <c r="AC917" s="1"/>
       <c r="AD917" s="1"/>
     </row>
-    <row r="918" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29910,7 +29894,7 @@
       <c r="AC918" s="1"/>
       <c r="AD918" s="1"/>
     </row>
-    <row r="919" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29942,7 +29926,7 @@
       <c r="AC919" s="1"/>
       <c r="AD919" s="1"/>
     </row>
-    <row r="920" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29974,7 +29958,7 @@
       <c r="AC920" s="1"/>
       <c r="AD920" s="1"/>
     </row>
-    <row r="921" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -30006,7 +29990,7 @@
       <c r="AC921" s="1"/>
       <c r="AD921" s="1"/>
     </row>
-    <row r="922" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -30038,7 +30022,7 @@
       <c r="AC922" s="1"/>
       <c r="AD922" s="1"/>
     </row>
-    <row r="923" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -30070,7 +30054,7 @@
       <c r="AC923" s="1"/>
       <c r="AD923" s="1"/>
     </row>
-    <row r="924" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -30102,7 +30086,7 @@
       <c r="AC924" s="1"/>
       <c r="AD924" s="1"/>
     </row>
-    <row r="925" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -30134,7 +30118,7 @@
       <c r="AC925" s="1"/>
       <c r="AD925" s="1"/>
     </row>
-    <row r="926" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -30166,7 +30150,7 @@
       <c r="AC926" s="1"/>
       <c r="AD926" s="1"/>
     </row>
-    <row r="927" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -30198,7 +30182,7 @@
       <c r="AC927" s="1"/>
       <c r="AD927" s="1"/>
     </row>
-    <row r="928" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -30230,7 +30214,7 @@
       <c r="AC928" s="1"/>
       <c r="AD928" s="1"/>
     </row>
-    <row r="929" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -30262,7 +30246,7 @@
       <c r="AC929" s="1"/>
       <c r="AD929" s="1"/>
     </row>
-    <row r="930" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -30294,7 +30278,7 @@
       <c r="AC930" s="1"/>
       <c r="AD930" s="1"/>
     </row>
-    <row r="931" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30326,7 +30310,7 @@
       <c r="AC931" s="1"/>
       <c r="AD931" s="1"/>
     </row>
-    <row r="932" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30358,7 +30342,7 @@
       <c r="AC932" s="1"/>
       <c r="AD932" s="1"/>
     </row>
-    <row r="933" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30390,7 +30374,7 @@
       <c r="AC933" s="1"/>
       <c r="AD933" s="1"/>
     </row>
-    <row r="934" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30422,7 +30406,7 @@
       <c r="AC934" s="1"/>
       <c r="AD934" s="1"/>
     </row>
-    <row r="935" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30454,7 +30438,7 @@
       <c r="AC935" s="1"/>
       <c r="AD935" s="1"/>
     </row>
-    <row r="936" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30486,7 +30470,7 @@
       <c r="AC936" s="1"/>
       <c r="AD936" s="1"/>
     </row>
-    <row r="937" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30518,7 +30502,7 @@
       <c r="AC937" s="1"/>
       <c r="AD937" s="1"/>
     </row>
-    <row r="938" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30550,7 +30534,7 @@
       <c r="AC938" s="1"/>
       <c r="AD938" s="1"/>
     </row>
-    <row r="939" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30582,7 +30566,7 @@
       <c r="AC939" s="1"/>
       <c r="AD939" s="1"/>
     </row>
-    <row r="940" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30614,7 +30598,7 @@
       <c r="AC940" s="1"/>
       <c r="AD940" s="1"/>
     </row>
-    <row r="941" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30646,7 +30630,7 @@
       <c r="AC941" s="1"/>
       <c r="AD941" s="1"/>
     </row>
-    <row r="942" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30678,7 +30662,7 @@
       <c r="AC942" s="1"/>
       <c r="AD942" s="1"/>
     </row>
-    <row r="943" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30710,7 +30694,7 @@
       <c r="AC943" s="1"/>
       <c r="AD943" s="1"/>
     </row>
-    <row r="944" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30742,7 +30726,7 @@
       <c r="AC944" s="1"/>
       <c r="AD944" s="1"/>
     </row>
-    <row r="945" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30774,7 +30758,7 @@
       <c r="AC945" s="1"/>
       <c r="AD945" s="1"/>
     </row>
-    <row r="946" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30806,7 +30790,7 @@
       <c r="AC946" s="1"/>
       <c r="AD946" s="1"/>
     </row>
-    <row r="947" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30838,7 +30822,7 @@
       <c r="AC947" s="1"/>
       <c r="AD947" s="1"/>
     </row>
-    <row r="948" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30870,7 +30854,7 @@
       <c r="AC948" s="1"/>
       <c r="AD948" s="1"/>
     </row>
-    <row r="949" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30902,7 +30886,7 @@
       <c r="AC949" s="1"/>
       <c r="AD949" s="1"/>
     </row>
-    <row r="950" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30934,7 +30918,7 @@
       <c r="AC950" s="1"/>
       <c r="AD950" s="1"/>
     </row>
-    <row r="951" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30966,7 +30950,7 @@
       <c r="AC951" s="1"/>
       <c r="AD951" s="1"/>
     </row>
-    <row r="952" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30998,7 +30982,7 @@
       <c r="AC952" s="1"/>
       <c r="AD952" s="1"/>
     </row>
-    <row r="953" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -31030,7 +31014,7 @@
       <c r="AC953" s="1"/>
       <c r="AD953" s="1"/>
     </row>
-    <row r="954" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -31062,7 +31046,7 @@
       <c r="AC954" s="1"/>
       <c r="AD954" s="1"/>
     </row>
-    <row r="955" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -31094,7 +31078,7 @@
       <c r="AC955" s="1"/>
       <c r="AD955" s="1"/>
     </row>
-    <row r="956" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -31126,7 +31110,7 @@
       <c r="AC956" s="1"/>
       <c r="AD956" s="1"/>
     </row>
-    <row r="957" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -31158,7 +31142,7 @@
       <c r="AC957" s="1"/>
       <c r="AD957" s="1"/>
     </row>
-    <row r="958" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -31190,7 +31174,7 @@
       <c r="AC958" s="1"/>
       <c r="AD958" s="1"/>
     </row>
-    <row r="959" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -31222,7 +31206,7 @@
       <c r="AC959" s="1"/>
       <c r="AD959" s="1"/>
     </row>
-    <row r="960" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -31254,7 +31238,7 @@
       <c r="AC960" s="1"/>
       <c r="AD960" s="1"/>
     </row>
-    <row r="961" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -31286,7 +31270,7 @@
       <c r="AC961" s="1"/>
       <c r="AD961" s="1"/>
     </row>
-    <row r="962" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -31318,7 +31302,7 @@
       <c r="AC962" s="1"/>
       <c r="AD962" s="1"/>
     </row>
-    <row r="963" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -31350,7 +31334,7 @@
       <c r="AC963" s="1"/>
       <c r="AD963" s="1"/>
     </row>
-    <row r="964" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31382,7 +31366,7 @@
       <c r="AC964" s="1"/>
       <c r="AD964" s="1"/>
     </row>
-    <row r="965" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31414,7 +31398,7 @@
       <c r="AC965" s="1"/>
       <c r="AD965" s="1"/>
     </row>
-    <row r="966" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31446,7 +31430,7 @@
       <c r="AC966" s="1"/>
       <c r="AD966" s="1"/>
     </row>
-    <row r="967" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31478,7 +31462,7 @@
       <c r="AC967" s="1"/>
       <c r="AD967" s="1"/>
     </row>
-    <row r="968" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31510,7 +31494,7 @@
       <c r="AC968" s="1"/>
       <c r="AD968" s="1"/>
     </row>
-    <row r="969" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31542,7 +31526,7 @@
       <c r="AC969" s="1"/>
       <c r="AD969" s="1"/>
     </row>
-    <row r="970" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31574,7 +31558,7 @@
       <c r="AC970" s="1"/>
       <c r="AD970" s="1"/>
     </row>
-    <row r="971" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31606,7 +31590,7 @@
       <c r="AC971" s="1"/>
       <c r="AD971" s="1"/>
     </row>
-    <row r="972" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31638,7 +31622,7 @@
       <c r="AC972" s="1"/>
       <c r="AD972" s="1"/>
     </row>
-    <row r="973" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31670,7 +31654,7 @@
       <c r="AC973" s="1"/>
       <c r="AD973" s="1"/>
     </row>
-    <row r="974" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31702,7 +31686,7 @@
       <c r="AC974" s="1"/>
       <c r="AD974" s="1"/>
     </row>
-    <row r="975" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31734,7 +31718,7 @@
       <c r="AC975" s="1"/>
       <c r="AD975" s="1"/>
     </row>
-    <row r="976" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31766,7 +31750,7 @@
       <c r="AC976" s="1"/>
       <c r="AD976" s="1"/>
     </row>
-    <row r="977" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31798,7 +31782,7 @@
       <c r="AC977" s="1"/>
       <c r="AD977" s="1"/>
     </row>
-    <row r="978" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31830,7 +31814,7 @@
       <c r="AC978" s="1"/>
       <c r="AD978" s="1"/>
     </row>
-    <row r="979" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31862,7 +31846,7 @@
       <c r="AC979" s="1"/>
       <c r="AD979" s="1"/>
     </row>
-    <row r="980" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31894,7 +31878,7 @@
       <c r="AC980" s="1"/>
       <c r="AD980" s="1"/>
     </row>
-    <row r="981" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31926,7 +31910,7 @@
       <c r="AC981" s="1"/>
       <c r="AD981" s="1"/>
     </row>
-    <row r="982" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31958,7 +31942,7 @@
       <c r="AC982" s="1"/>
       <c r="AD982" s="1"/>
     </row>
-    <row r="983" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31990,7 +31974,7 @@
       <c r="AC983" s="1"/>
       <c r="AD983" s="1"/>
     </row>
-    <row r="984" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -32022,7 +32006,7 @@
       <c r="AC984" s="1"/>
       <c r="AD984" s="1"/>
     </row>
-    <row r="985" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -32054,7 +32038,7 @@
       <c r="AC985" s="1"/>
       <c r="AD985" s="1"/>
     </row>
-    <row r="986" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -32086,7 +32070,7 @@
       <c r="AC986" s="1"/>
       <c r="AD986" s="1"/>
     </row>
-    <row r="987" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -32118,7 +32102,7 @@
       <c r="AC987" s="1"/>
       <c r="AD987" s="1"/>
     </row>
-    <row r="988" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -32150,7 +32134,7 @@
       <c r="AC988" s="1"/>
       <c r="AD988" s="1"/>
     </row>
-    <row r="989" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -32182,7 +32166,7 @@
       <c r="AC989" s="1"/>
       <c r="AD989" s="1"/>
     </row>
-    <row r="990" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -32214,7 +32198,7 @@
       <c r="AC990" s="1"/>
       <c r="AD990" s="1"/>
     </row>
-    <row r="991" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -32246,7 +32230,7 @@
       <c r="AC991" s="1"/>
       <c r="AD991" s="1"/>
     </row>
-    <row r="992" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -32278,7 +32262,7 @@
       <c r="AC992" s="1"/>
       <c r="AD992" s="1"/>
     </row>
-    <row r="993" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -32310,7 +32294,7 @@
       <c r="AC993" s="1"/>
       <c r="AD993" s="1"/>
     </row>
-    <row r="994" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -32342,7 +32326,7 @@
       <c r="AC994" s="1"/>
       <c r="AD994" s="1"/>
     </row>
-    <row r="995" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -32374,7 +32358,7 @@
       <c r="AC995" s="1"/>
       <c r="AD995" s="1"/>
     </row>
-    <row r="996" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32406,7 +32390,7 @@
       <c r="AC996" s="1"/>
       <c r="AD996" s="1"/>
     </row>
-    <row r="997" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32438,7 +32422,7 @@
       <c r="AC997" s="1"/>
       <c r="AD997" s="1"/>
     </row>
-    <row r="998" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32470,7 +32454,7 @@
       <c r="AC998" s="1"/>
       <c r="AD998" s="1"/>
     </row>
-    <row r="999" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32502,7 +32486,7 @@
       <c r="AC999" s="1"/>
       <c r="AD999" s="1"/>
     </row>
-    <row r="1000" spans="1:30" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32536,6 +32520,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="K9:O9"/>
     <mergeCell ref="K10:O10"/>
     <mergeCell ref="G16:I16"/>
@@ -32547,17 +32536,12 @@
     <mergeCell ref="K25:O25"/>
     <mergeCell ref="G4:I14"/>
     <mergeCell ref="K8:O8"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="Q2:W2"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G16:I16" r:id="rId2" display="SIMULAÇÃO - Transistor  (print)" xr:uid="{125647E5-AE4D-428E-91F7-FD2605979EE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/a_CI/APS_A.xlsx
+++ b/a_CI/APS_A.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C562F8B0-EC42-4CDC-8E65-FA31EDE3CFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D7787B-5230-4B0F-9051-1F18DAA8109F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentacao" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -130,19 +135,19 @@
     <t>D = ¬(A+D)BC+AD¬(B+C)</t>
   </si>
   <si>
-    <t xml:space="preserve">1) https://youtu.be/ubGuFvksfBw
-2) https://youtu.be/-N40jEYFJDQ
-3) https://youtu.be/t2BxfgsAuno </t>
+    <t>V = ¬ABD + B¬CD + AC¬D + A¬BC</t>
   </si>
   <si>
-    <t>V = ¬ABD + B¬CD + AC¬D + A¬BC</t>
+    <t>1) https://youtu.be/ubGuFvksfBw
+2) https://youtu.be/-N40jEYFJDQ
+3) https://youtu.be/oHvft_JwQmQ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -178,6 +183,14 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -383,7 +396,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -466,17 +479,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
@@ -484,17 +508,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -796,25 +810,25 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AD1000"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" customWidth="1"/>
-    <col min="5" max="5" width="63.44140625" customWidth="1"/>
+    <col min="5" max="5" width="63.46484375" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" customWidth="1"/>
     <col min="10" max="10" width="2.6640625" customWidth="1"/>
-    <col min="11" max="15" width="6.77734375" customWidth="1"/>
-    <col min="16" max="16" width="3.109375" customWidth="1"/>
-    <col min="17" max="17" width="2.21875" customWidth="1"/>
-    <col min="18" max="18" width="2.109375" customWidth="1"/>
-    <col min="19" max="21" width="2.21875" customWidth="1"/>
-    <col min="22" max="22" width="2.109375" customWidth="1"/>
-    <col min="23" max="23" width="2.21875" customWidth="1"/>
-    <col min="24" max="29" width="6.77734375" customWidth="1"/>
+    <col min="11" max="15" width="6.796875" customWidth="1"/>
+    <col min="16" max="16" width="3.1328125" customWidth="1"/>
+    <col min="17" max="17" width="2.19921875" customWidth="1"/>
+    <col min="18" max="18" width="2.1328125" customWidth="1"/>
+    <col min="19" max="21" width="2.19921875" customWidth="1"/>
+    <col min="22" max="22" width="2.1328125" customWidth="1"/>
+    <col min="23" max="23" width="2.19921875" customWidth="1"/>
+    <col min="24" max="29" width="6.796875" customWidth="1"/>
     <col min="30" max="30" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="D1" s="1"/>
       <c r="F1" s="1"/>
@@ -829,43 +843,43 @@
       <c r="R1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="1"/>
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="2"/>
       <c r="K2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="31"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="31"/>
       <c r="AD2" s="1"/>
     </row>
-    <row r="3" spans="1:30" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="38.25" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -875,10 +889,10 @@
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="34" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="35"/>
@@ -922,7 +936,7 @@
       </c>
       <c r="AD3" s="1"/>
     </row>
-    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="15" t="s">
         <v>13</v>
@@ -932,7 +946,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="34"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="35"/>
       <c r="I4" s="36"/>
       <c r="K4" s="17" t="s">
@@ -974,7 +988,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -983,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="37"/>
+      <c r="G5" s="42"/>
       <c r="H5" s="35"/>
       <c r="I5" s="36"/>
       <c r="K5" s="17" t="s">
@@ -1025,7 +1039,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1033,7 +1047,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="37"/>
+      <c r="G6" s="42"/>
       <c r="H6" s="35"/>
       <c r="I6" s="36"/>
       <c r="K6" s="17" t="s">
@@ -1075,7 +1089,7 @@
       </c>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1084,7 +1098,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="37"/>
+      <c r="G7" s="42"/>
       <c r="H7" s="35"/>
       <c r="I7" s="36"/>
       <c r="K7" s="23" t="s">
@@ -1124,9 +1138,10 @@
       <c r="W7" s="20" t="s">
         <v>17</v>
       </c>
+      <c r="AB7" s="47"/>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1135,16 +1150,16 @@
         <v>21</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="37"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="35"/>
       <c r="I8" s="36"/>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="19" t="s">
         <v>17</v>
@@ -1169,23 +1184,23 @@
       </c>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="22"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="37"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="35"/>
       <c r="I9" s="36"/>
-      <c r="K9" s="30" t="s">
+      <c r="K9" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="31"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="12">
         <v>0</v>
@@ -1210,7 +1225,7 @@
       </c>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1219,16 +1234,16 @@
         <v>24</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="37"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="35"/>
       <c r="I10" s="36"/>
-      <c r="K10" s="30" t="s">
+      <c r="K10" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="19" t="s">
         <v>17</v>
@@ -1253,7 +1268,7 @@
       </c>
       <c r="AD10" s="1"/>
     </row>
-    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1262,7 +1277,7 @@
         <v>26</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="37"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="35"/>
       <c r="I11" s="36"/>
       <c r="K11" s="8" t="s">
@@ -1304,14 +1319,14 @@
       </c>
       <c r="AD11" s="1"/>
     </row>
-    <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="22"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="37"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="35"/>
       <c r="I12" s="36"/>
       <c r="K12" s="17" t="s">
@@ -1353,7 +1368,7 @@
       </c>
       <c r="AD12" s="1"/>
     </row>
-    <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1362,7 +1377,7 @@
         <v>27</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="37"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36"/>
       <c r="K13" s="17" t="s">
@@ -1404,7 +1419,7 @@
       </c>
       <c r="AD13" s="1"/>
     </row>
-    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1413,9 +1428,9 @@
         <v>28</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="45"/>
       <c r="K14" s="17" t="s">
         <v>11</v>
       </c>
@@ -1455,7 +1470,7 @@
       </c>
       <c r="AD14" s="1"/>
     </row>
-    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1503,7 +1518,7 @@
       </c>
       <c r="AD15" s="1"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1512,18 +1527,18 @@
         <v>30</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="46"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
       <c r="K16" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="31"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="19" t="s">
         <v>18</v>
@@ -1548,23 +1563,23 @@
       </c>
       <c r="AD16" s="1"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="28"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="34"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="35"/>
       <c r="I17" s="36"/>
       <c r="K17" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="31"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="19" t="s">
         <v>18</v>
@@ -1589,22 +1604,22 @@
       </c>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="37"/>
+      <c r="G18" s="42"/>
       <c r="H18" s="35"/>
       <c r="I18" s="36"/>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="31"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="19" t="s">
         <v>18</v>
@@ -1629,13 +1644,13 @@
       </c>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="37"/>
+      <c r="G19" s="42"/>
       <c r="H19" s="35"/>
       <c r="I19" s="36"/>
       <c r="K19" s="8" t="s">
@@ -1677,13 +1692,13 @@
       </c>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="37"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="35"/>
       <c r="I20" s="36"/>
       <c r="K20" s="17" t="s">
@@ -1711,13 +1726,13 @@
       <c r="W20" s="11"/>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="37"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="35"/>
       <c r="I21" s="36"/>
       <c r="K21" s="17" t="s">
@@ -1740,13 +1755,13 @@
       <c r="R21" s="1"/>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="37"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="35"/>
       <c r="I22" s="36"/>
       <c r="K22" s="17" t="s">
@@ -1769,13 +1784,13 @@
       <c r="R22" s="1"/>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="37"/>
+      <c r="G23" s="42"/>
       <c r="H23" s="35"/>
       <c r="I23" s="36"/>
       <c r="K23" s="23" t="s">
@@ -1798,55 +1813,56 @@
       <c r="R23" s="1"/>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="37"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="35"/>
       <c r="I24" s="36"/>
       <c r="K24" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="31"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
+      <c r="AA24" s="47"/>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="37"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="35"/>
       <c r="I25" s="36"/>
-      <c r="K25" s="41" t="s">
+      <c r="K25" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="31"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="37"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="35"/>
       <c r="I26" s="36"/>
       <c r="K26" s="1"/>
@@ -1859,19 +1875,19 @@
       <c r="R26" s="1"/>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
       <c r="R27" s="1"/>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1884,7 +1900,7 @@
       <c r="R28" s="1"/>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1897,7 +1913,7 @@
       <c r="R29" s="1"/>
       <c r="AD29" s="1"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1910,7 +1926,7 @@
       <c r="R30" s="1"/>
       <c r="AD30" s="1"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1923,7 +1939,7 @@
       <c r="R31" s="1"/>
       <c r="AD31" s="1"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1936,7 +1952,7 @@
       <c r="R32" s="1"/>
       <c r="AD32" s="1"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1949,7 +1965,7 @@
       <c r="R33" s="1"/>
       <c r="AD33" s="1"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1962,7 +1978,7 @@
       <c r="R34" s="1"/>
       <c r="AD34" s="1"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1975,7 +1991,7 @@
       <c r="R35" s="1"/>
       <c r="AD35" s="1"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1988,7 +2004,7 @@
       <c r="R36" s="1"/>
       <c r="AD36" s="1"/>
     </row>
-    <row r="37" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2001,7 +2017,7 @@
       <c r="R37" s="1"/>
       <c r="AD37" s="1"/>
     </row>
-    <row r="38" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2014,7 +2030,7 @@
       <c r="R38" s="1"/>
       <c r="AD38" s="1"/>
     </row>
-    <row r="39" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2027,7 +2043,7 @@
       <c r="R39" s="1"/>
       <c r="AD39" s="1"/>
     </row>
-    <row r="40" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2040,7 +2056,7 @@
       <c r="R40" s="1"/>
       <c r="AD40" s="1"/>
     </row>
-    <row r="41" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2050,7 +2066,7 @@
       <c r="R41" s="1"/>
       <c r="AD41" s="1"/>
     </row>
-    <row r="42" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2060,7 +2076,7 @@
       <c r="R42" s="1"/>
       <c r="AD42" s="1"/>
     </row>
-    <row r="43" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2070,7 +2086,7 @@
       <c r="R43" s="1"/>
       <c r="AD43" s="1"/>
     </row>
-    <row r="44" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2080,7 +2096,7 @@
       <c r="R44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
-    <row r="45" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2090,7 +2106,7 @@
       <c r="R45" s="1"/>
       <c r="AD45" s="1"/>
     </row>
-    <row r="46" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2100,7 +2116,7 @@
       <c r="R46" s="1"/>
       <c r="AD46" s="1"/>
     </row>
-    <row r="47" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2110,7 +2126,7 @@
       <c r="R47" s="1"/>
       <c r="AD47" s="1"/>
     </row>
-    <row r="48" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2120,7 +2136,7 @@
       <c r="R48" s="1"/>
       <c r="AD48" s="1"/>
     </row>
-    <row r="49" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2130,7 +2146,7 @@
       <c r="R49" s="1"/>
       <c r="AD49" s="1"/>
     </row>
-    <row r="50" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2140,7 +2156,7 @@
       <c r="R50" s="1"/>
       <c r="AD50" s="1"/>
     </row>
-    <row r="51" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2150,7 +2166,7 @@
       <c r="R51" s="1"/>
       <c r="AD51" s="1"/>
     </row>
-    <row r="52" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2182,7 +2198,7 @@
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
     </row>
-    <row r="53" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2214,7 +2230,7 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
     </row>
-    <row r="54" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2246,7 +2262,7 @@
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
     </row>
-    <row r="55" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2278,7 +2294,7 @@
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
     </row>
-    <row r="56" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2310,7 +2326,7 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
     </row>
-    <row r="57" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2342,7 +2358,7 @@
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
     </row>
-    <row r="58" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2374,7 +2390,7 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
     </row>
-    <row r="59" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2406,7 +2422,7 @@
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
     </row>
-    <row r="60" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2438,7 +2454,7 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
     </row>
-    <row r="61" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2470,7 +2486,7 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
     </row>
-    <row r="62" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2502,7 +2518,7 @@
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
     </row>
-    <row r="63" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2534,7 +2550,7 @@
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
     </row>
-    <row r="64" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2566,7 +2582,7 @@
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
     </row>
-    <row r="65" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2598,7 +2614,7 @@
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
     </row>
-    <row r="66" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2630,7 +2646,7 @@
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
     </row>
-    <row r="67" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2662,7 +2678,7 @@
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
     </row>
-    <row r="68" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2694,7 +2710,7 @@
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
     </row>
-    <row r="69" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2726,7 +2742,7 @@
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
     </row>
-    <row r="70" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2758,7 +2774,7 @@
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
     </row>
-    <row r="71" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2790,7 +2806,7 @@
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
     </row>
-    <row r="72" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2822,7 +2838,7 @@
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
     </row>
-    <row r="73" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2854,7 +2870,7 @@
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
     </row>
-    <row r="74" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2886,7 +2902,7 @@
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
     </row>
-    <row r="75" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2918,7 +2934,7 @@
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
     </row>
-    <row r="76" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2950,7 +2966,7 @@
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
     </row>
-    <row r="77" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2982,7 +2998,7 @@
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
     </row>
-    <row r="78" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3014,7 +3030,7 @@
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
     </row>
-    <row r="79" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3046,7 +3062,7 @@
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
     </row>
-    <row r="80" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3078,7 +3094,7 @@
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
     </row>
-    <row r="81" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3110,7 +3126,7 @@
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
     </row>
-    <row r="82" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3142,7 +3158,7 @@
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
     </row>
-    <row r="83" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3174,7 +3190,7 @@
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
     </row>
-    <row r="84" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3206,7 +3222,7 @@
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
     </row>
-    <row r="85" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3238,7 +3254,7 @@
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
     </row>
-    <row r="86" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3270,7 +3286,7 @@
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
     </row>
-    <row r="87" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3302,7 +3318,7 @@
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
     </row>
-    <row r="88" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3334,7 +3350,7 @@
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
     </row>
-    <row r="89" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3366,7 +3382,7 @@
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
     </row>
-    <row r="90" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3398,7 +3414,7 @@
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
     </row>
-    <row r="91" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3430,7 +3446,7 @@
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
     </row>
-    <row r="92" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3462,7 +3478,7 @@
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
     </row>
-    <row r="93" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3494,7 +3510,7 @@
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
     </row>
-    <row r="94" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3526,7 +3542,7 @@
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
     </row>
-    <row r="95" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3558,7 +3574,7 @@
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
     </row>
-    <row r="96" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3590,7 +3606,7 @@
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
     </row>
-    <row r="97" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3622,7 +3638,7 @@
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
     </row>
-    <row r="98" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3654,7 +3670,7 @@
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
     </row>
-    <row r="99" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3686,7 +3702,7 @@
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
     </row>
-    <row r="100" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3718,7 +3734,7 @@
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
     </row>
-    <row r="101" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3750,7 +3766,7 @@
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
     </row>
-    <row r="102" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3782,7 +3798,7 @@
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
     </row>
-    <row r="103" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3814,7 +3830,7 @@
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
     </row>
-    <row r="104" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3846,7 +3862,7 @@
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
     </row>
-    <row r="105" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3878,7 +3894,7 @@
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
     </row>
-    <row r="106" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3910,7 +3926,7 @@
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
     </row>
-    <row r="107" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3942,7 +3958,7 @@
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
     </row>
-    <row r="108" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3974,7 +3990,7 @@
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
     </row>
-    <row r="109" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4006,7 +4022,7 @@
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
     </row>
-    <row r="110" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4038,7 +4054,7 @@
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
     </row>
-    <row r="111" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4070,7 +4086,7 @@
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
     </row>
-    <row r="112" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4102,7 +4118,7 @@
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
     </row>
-    <row r="113" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4134,7 +4150,7 @@
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
     </row>
-    <row r="114" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4166,7 +4182,7 @@
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
     </row>
-    <row r="115" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4198,7 +4214,7 @@
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
     </row>
-    <row r="116" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4230,7 +4246,7 @@
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
     </row>
-    <row r="117" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4262,7 +4278,7 @@
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
     </row>
-    <row r="118" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4294,7 +4310,7 @@
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
     </row>
-    <row r="119" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4326,7 +4342,7 @@
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
     </row>
-    <row r="120" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4358,7 +4374,7 @@
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
     </row>
-    <row r="121" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4390,7 +4406,7 @@
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
     </row>
-    <row r="122" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4422,7 +4438,7 @@
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
     </row>
-    <row r="123" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4454,7 +4470,7 @@
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
     </row>
-    <row r="124" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4486,7 +4502,7 @@
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
     </row>
-    <row r="125" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4518,7 +4534,7 @@
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
     </row>
-    <row r="126" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4550,7 +4566,7 @@
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
     </row>
-    <row r="127" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4582,7 +4598,7 @@
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
     </row>
-    <row r="128" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4614,7 +4630,7 @@
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
     </row>
-    <row r="129" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4646,7 +4662,7 @@
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
     </row>
-    <row r="130" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4678,7 +4694,7 @@
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
     </row>
-    <row r="131" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4710,7 +4726,7 @@
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
     </row>
-    <row r="132" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4742,7 +4758,7 @@
       <c r="AC132" s="1"/>
       <c r="AD132" s="1"/>
     </row>
-    <row r="133" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4774,7 +4790,7 @@
       <c r="AC133" s="1"/>
       <c r="AD133" s="1"/>
     </row>
-    <row r="134" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4806,7 +4822,7 @@
       <c r="AC134" s="1"/>
       <c r="AD134" s="1"/>
     </row>
-    <row r="135" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4838,7 +4854,7 @@
       <c r="AC135" s="1"/>
       <c r="AD135" s="1"/>
     </row>
-    <row r="136" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4870,7 +4886,7 @@
       <c r="AC136" s="1"/>
       <c r="AD136" s="1"/>
     </row>
-    <row r="137" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4902,7 +4918,7 @@
       <c r="AC137" s="1"/>
       <c r="AD137" s="1"/>
     </row>
-    <row r="138" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4934,7 +4950,7 @@
       <c r="AC138" s="1"/>
       <c r="AD138" s="1"/>
     </row>
-    <row r="139" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4966,7 +4982,7 @@
       <c r="AC139" s="1"/>
       <c r="AD139" s="1"/>
     </row>
-    <row r="140" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4998,7 +5014,7 @@
       <c r="AC140" s="1"/>
       <c r="AD140" s="1"/>
     </row>
-    <row r="141" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5030,7 +5046,7 @@
       <c r="AC141" s="1"/>
       <c r="AD141" s="1"/>
     </row>
-    <row r="142" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5062,7 +5078,7 @@
       <c r="AC142" s="1"/>
       <c r="AD142" s="1"/>
     </row>
-    <row r="143" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5094,7 +5110,7 @@
       <c r="AC143" s="1"/>
       <c r="AD143" s="1"/>
     </row>
-    <row r="144" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5126,7 +5142,7 @@
       <c r="AC144" s="1"/>
       <c r="AD144" s="1"/>
     </row>
-    <row r="145" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5158,7 +5174,7 @@
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
     </row>
-    <row r="146" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5190,7 +5206,7 @@
       <c r="AC146" s="1"/>
       <c r="AD146" s="1"/>
     </row>
-    <row r="147" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5222,7 +5238,7 @@
       <c r="AC147" s="1"/>
       <c r="AD147" s="1"/>
     </row>
-    <row r="148" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5254,7 +5270,7 @@
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
     </row>
-    <row r="149" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5286,7 +5302,7 @@
       <c r="AC149" s="1"/>
       <c r="AD149" s="1"/>
     </row>
-    <row r="150" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5318,7 +5334,7 @@
       <c r="AC150" s="1"/>
       <c r="AD150" s="1"/>
     </row>
-    <row r="151" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5350,7 +5366,7 @@
       <c r="AC151" s="1"/>
       <c r="AD151" s="1"/>
     </row>
-    <row r="152" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5382,7 +5398,7 @@
       <c r="AC152" s="1"/>
       <c r="AD152" s="1"/>
     </row>
-    <row r="153" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5414,7 +5430,7 @@
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
     </row>
-    <row r="154" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5446,7 +5462,7 @@
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
     </row>
-    <row r="155" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5478,7 +5494,7 @@
       <c r="AC155" s="1"/>
       <c r="AD155" s="1"/>
     </row>
-    <row r="156" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5510,7 +5526,7 @@
       <c r="AC156" s="1"/>
       <c r="AD156" s="1"/>
     </row>
-    <row r="157" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5542,7 +5558,7 @@
       <c r="AC157" s="1"/>
       <c r="AD157" s="1"/>
     </row>
-    <row r="158" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5574,7 +5590,7 @@
       <c r="AC158" s="1"/>
       <c r="AD158" s="1"/>
     </row>
-    <row r="159" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5606,7 +5622,7 @@
       <c r="AC159" s="1"/>
       <c r="AD159" s="1"/>
     </row>
-    <row r="160" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5638,7 +5654,7 @@
       <c r="AC160" s="1"/>
       <c r="AD160" s="1"/>
     </row>
-    <row r="161" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5670,7 +5686,7 @@
       <c r="AC161" s="1"/>
       <c r="AD161" s="1"/>
     </row>
-    <row r="162" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5702,7 +5718,7 @@
       <c r="AC162" s="1"/>
       <c r="AD162" s="1"/>
     </row>
-    <row r="163" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5734,7 +5750,7 @@
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
     </row>
-    <row r="164" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5766,7 +5782,7 @@
       <c r="AC164" s="1"/>
       <c r="AD164" s="1"/>
     </row>
-    <row r="165" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5798,7 +5814,7 @@
       <c r="AC165" s="1"/>
       <c r="AD165" s="1"/>
     </row>
-    <row r="166" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5830,7 +5846,7 @@
       <c r="AC166" s="1"/>
       <c r="AD166" s="1"/>
     </row>
-    <row r="167" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5862,7 +5878,7 @@
       <c r="AC167" s="1"/>
       <c r="AD167" s="1"/>
     </row>
-    <row r="168" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5894,7 +5910,7 @@
       <c r="AC168" s="1"/>
       <c r="AD168" s="1"/>
     </row>
-    <row r="169" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5926,7 +5942,7 @@
       <c r="AC169" s="1"/>
       <c r="AD169" s="1"/>
     </row>
-    <row r="170" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5958,7 +5974,7 @@
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
     </row>
-    <row r="171" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5990,7 +6006,7 @@
       <c r="AC171" s="1"/>
       <c r="AD171" s="1"/>
     </row>
-    <row r="172" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6022,7 +6038,7 @@
       <c r="AC172" s="1"/>
       <c r="AD172" s="1"/>
     </row>
-    <row r="173" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6054,7 +6070,7 @@
       <c r="AC173" s="1"/>
       <c r="AD173" s="1"/>
     </row>
-    <row r="174" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6086,7 +6102,7 @@
       <c r="AC174" s="1"/>
       <c r="AD174" s="1"/>
     </row>
-    <row r="175" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6118,7 +6134,7 @@
       <c r="AC175" s="1"/>
       <c r="AD175" s="1"/>
     </row>
-    <row r="176" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6150,7 +6166,7 @@
       <c r="AC176" s="1"/>
       <c r="AD176" s="1"/>
     </row>
-    <row r="177" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6182,7 +6198,7 @@
       <c r="AC177" s="1"/>
       <c r="AD177" s="1"/>
     </row>
-    <row r="178" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6214,7 +6230,7 @@
       <c r="AC178" s="1"/>
       <c r="AD178" s="1"/>
     </row>
-    <row r="179" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6246,7 +6262,7 @@
       <c r="AC179" s="1"/>
       <c r="AD179" s="1"/>
     </row>
-    <row r="180" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6278,7 +6294,7 @@
       <c r="AC180" s="1"/>
       <c r="AD180" s="1"/>
     </row>
-    <row r="181" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6310,7 +6326,7 @@
       <c r="AC181" s="1"/>
       <c r="AD181" s="1"/>
     </row>
-    <row r="182" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6342,7 +6358,7 @@
       <c r="AC182" s="1"/>
       <c r="AD182" s="1"/>
     </row>
-    <row r="183" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6374,7 +6390,7 @@
       <c r="AC183" s="1"/>
       <c r="AD183" s="1"/>
     </row>
-    <row r="184" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6406,7 +6422,7 @@
       <c r="AC184" s="1"/>
       <c r="AD184" s="1"/>
     </row>
-    <row r="185" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6438,7 +6454,7 @@
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
     </row>
-    <row r="186" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6470,7 +6486,7 @@
       <c r="AC186" s="1"/>
       <c r="AD186" s="1"/>
     </row>
-    <row r="187" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6502,7 +6518,7 @@
       <c r="AC187" s="1"/>
       <c r="AD187" s="1"/>
     </row>
-    <row r="188" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6534,7 +6550,7 @@
       <c r="AC188" s="1"/>
       <c r="AD188" s="1"/>
     </row>
-    <row r="189" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6566,7 +6582,7 @@
       <c r="AC189" s="1"/>
       <c r="AD189" s="1"/>
     </row>
-    <row r="190" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6598,7 +6614,7 @@
       <c r="AC190" s="1"/>
       <c r="AD190" s="1"/>
     </row>
-    <row r="191" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6630,7 +6646,7 @@
       <c r="AC191" s="1"/>
       <c r="AD191" s="1"/>
     </row>
-    <row r="192" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6662,7 +6678,7 @@
       <c r="AC192" s="1"/>
       <c r="AD192" s="1"/>
     </row>
-    <row r="193" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6694,7 +6710,7 @@
       <c r="AC193" s="1"/>
       <c r="AD193" s="1"/>
     </row>
-    <row r="194" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6726,7 +6742,7 @@
       <c r="AC194" s="1"/>
       <c r="AD194" s="1"/>
     </row>
-    <row r="195" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6758,7 +6774,7 @@
       <c r="AC195" s="1"/>
       <c r="AD195" s="1"/>
     </row>
-    <row r="196" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6790,7 +6806,7 @@
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
     </row>
-    <row r="197" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6822,7 +6838,7 @@
       <c r="AC197" s="1"/>
       <c r="AD197" s="1"/>
     </row>
-    <row r="198" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6854,7 +6870,7 @@
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
     </row>
-    <row r="199" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6886,7 +6902,7 @@
       <c r="AC199" s="1"/>
       <c r="AD199" s="1"/>
     </row>
-    <row r="200" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6918,7 +6934,7 @@
       <c r="AC200" s="1"/>
       <c r="AD200" s="1"/>
     </row>
-    <row r="201" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6950,7 +6966,7 @@
       <c r="AC201" s="1"/>
       <c r="AD201" s="1"/>
     </row>
-    <row r="202" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6982,7 +6998,7 @@
       <c r="AC202" s="1"/>
       <c r="AD202" s="1"/>
     </row>
-    <row r="203" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7014,7 +7030,7 @@
       <c r="AC203" s="1"/>
       <c r="AD203" s="1"/>
     </row>
-    <row r="204" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7046,7 +7062,7 @@
       <c r="AC204" s="1"/>
       <c r="AD204" s="1"/>
     </row>
-    <row r="205" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7078,7 +7094,7 @@
       <c r="AC205" s="1"/>
       <c r="AD205" s="1"/>
     </row>
-    <row r="206" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7110,7 +7126,7 @@
       <c r="AC206" s="1"/>
       <c r="AD206" s="1"/>
     </row>
-    <row r="207" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7142,7 +7158,7 @@
       <c r="AC207" s="1"/>
       <c r="AD207" s="1"/>
     </row>
-    <row r="208" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7174,7 +7190,7 @@
       <c r="AC208" s="1"/>
       <c r="AD208" s="1"/>
     </row>
-    <row r="209" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7206,7 +7222,7 @@
       <c r="AC209" s="1"/>
       <c r="AD209" s="1"/>
     </row>
-    <row r="210" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7238,7 +7254,7 @@
       <c r="AC210" s="1"/>
       <c r="AD210" s="1"/>
     </row>
-    <row r="211" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7270,7 +7286,7 @@
       <c r="AC211" s="1"/>
       <c r="AD211" s="1"/>
     </row>
-    <row r="212" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7302,7 +7318,7 @@
       <c r="AC212" s="1"/>
       <c r="AD212" s="1"/>
     </row>
-    <row r="213" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7334,7 +7350,7 @@
       <c r="AC213" s="1"/>
       <c r="AD213" s="1"/>
     </row>
-    <row r="214" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7366,7 +7382,7 @@
       <c r="AC214" s="1"/>
       <c r="AD214" s="1"/>
     </row>
-    <row r="215" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7398,7 +7414,7 @@
       <c r="AC215" s="1"/>
       <c r="AD215" s="1"/>
     </row>
-    <row r="216" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7430,7 +7446,7 @@
       <c r="AC216" s="1"/>
       <c r="AD216" s="1"/>
     </row>
-    <row r="217" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7462,7 +7478,7 @@
       <c r="AC217" s="1"/>
       <c r="AD217" s="1"/>
     </row>
-    <row r="218" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7494,7 +7510,7 @@
       <c r="AC218" s="1"/>
       <c r="AD218" s="1"/>
     </row>
-    <row r="219" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7526,7 +7542,7 @@
       <c r="AC219" s="1"/>
       <c r="AD219" s="1"/>
     </row>
-    <row r="220" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7558,7 +7574,7 @@
       <c r="AC220" s="1"/>
       <c r="AD220" s="1"/>
     </row>
-    <row r="221" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7590,7 +7606,7 @@
       <c r="AC221" s="1"/>
       <c r="AD221" s="1"/>
     </row>
-    <row r="222" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7622,7 +7638,7 @@
       <c r="AC222" s="1"/>
       <c r="AD222" s="1"/>
     </row>
-    <row r="223" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7654,7 +7670,7 @@
       <c r="AC223" s="1"/>
       <c r="AD223" s="1"/>
     </row>
-    <row r="224" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7686,7 +7702,7 @@
       <c r="AC224" s="1"/>
       <c r="AD224" s="1"/>
     </row>
-    <row r="225" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7718,7 +7734,7 @@
       <c r="AC225" s="1"/>
       <c r="AD225" s="1"/>
     </row>
-    <row r="226" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7750,7 +7766,7 @@
       <c r="AC226" s="1"/>
       <c r="AD226" s="1"/>
     </row>
-    <row r="227" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7782,7 +7798,7 @@
       <c r="AC227" s="1"/>
       <c r="AD227" s="1"/>
     </row>
-    <row r="228" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7814,7 +7830,7 @@
       <c r="AC228" s="1"/>
       <c r="AD228" s="1"/>
     </row>
-    <row r="229" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7846,7 +7862,7 @@
       <c r="AC229" s="1"/>
       <c r="AD229" s="1"/>
     </row>
-    <row r="230" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7878,7 +7894,7 @@
       <c r="AC230" s="1"/>
       <c r="AD230" s="1"/>
     </row>
-    <row r="231" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7910,7 +7926,7 @@
       <c r="AC231" s="1"/>
       <c r="AD231" s="1"/>
     </row>
-    <row r="232" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7942,7 +7958,7 @@
       <c r="AC232" s="1"/>
       <c r="AD232" s="1"/>
     </row>
-    <row r="233" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7974,7 +7990,7 @@
       <c r="AC233" s="1"/>
       <c r="AD233" s="1"/>
     </row>
-    <row r="234" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8006,7 +8022,7 @@
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
     </row>
-    <row r="235" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8038,7 +8054,7 @@
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
     </row>
-    <row r="236" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8070,7 +8086,7 @@
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
     </row>
-    <row r="237" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8102,7 +8118,7 @@
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
     </row>
-    <row r="238" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8134,7 +8150,7 @@
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
     </row>
-    <row r="239" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8166,7 +8182,7 @@
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
     </row>
-    <row r="240" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8198,7 +8214,7 @@
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
     </row>
-    <row r="241" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8230,7 +8246,7 @@
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
     </row>
-    <row r="242" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8262,7 +8278,7 @@
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
     </row>
-    <row r="243" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8294,7 +8310,7 @@
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
     </row>
-    <row r="244" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8326,7 +8342,7 @@
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
     </row>
-    <row r="245" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8358,7 +8374,7 @@
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
     </row>
-    <row r="246" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8390,7 +8406,7 @@
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
     </row>
-    <row r="247" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8422,7 +8438,7 @@
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
     </row>
-    <row r="248" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8454,7 +8470,7 @@
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
     </row>
-    <row r="249" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8486,7 +8502,7 @@
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
     </row>
-    <row r="250" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8518,7 +8534,7 @@
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
     </row>
-    <row r="251" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8550,7 +8566,7 @@
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
     </row>
-    <row r="252" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8582,7 +8598,7 @@
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
     </row>
-    <row r="253" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8614,7 +8630,7 @@
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
     </row>
-    <row r="254" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8646,7 +8662,7 @@
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
     </row>
-    <row r="255" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8678,7 +8694,7 @@
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
     </row>
-    <row r="256" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8710,7 +8726,7 @@
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
     </row>
-    <row r="257" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8742,7 +8758,7 @@
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
     </row>
-    <row r="258" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8774,7 +8790,7 @@
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
     </row>
-    <row r="259" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8806,7 +8822,7 @@
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
     </row>
-    <row r="260" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8838,7 +8854,7 @@
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
     </row>
-    <row r="261" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8870,7 +8886,7 @@
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
     </row>
-    <row r="262" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8902,7 +8918,7 @@
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
     </row>
-    <row r="263" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8934,7 +8950,7 @@
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
     </row>
-    <row r="264" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8966,7 +8982,7 @@
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
     </row>
-    <row r="265" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -8998,7 +9014,7 @@
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
     </row>
-    <row r="266" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9030,7 +9046,7 @@
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
     </row>
-    <row r="267" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9062,7 +9078,7 @@
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
     </row>
-    <row r="268" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9094,7 +9110,7 @@
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
     </row>
-    <row r="269" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9126,7 +9142,7 @@
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
     </row>
-    <row r="270" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9158,7 +9174,7 @@
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
     </row>
-    <row r="271" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9190,7 +9206,7 @@
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
     </row>
-    <row r="272" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9222,7 +9238,7 @@
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
     </row>
-    <row r="273" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9254,7 +9270,7 @@
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
     </row>
-    <row r="274" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9286,7 +9302,7 @@
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
     </row>
-    <row r="275" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9318,7 +9334,7 @@
       <c r="AC275" s="1"/>
       <c r="AD275" s="1"/>
     </row>
-    <row r="276" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9350,7 +9366,7 @@
       <c r="AC276" s="1"/>
       <c r="AD276" s="1"/>
     </row>
-    <row r="277" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9382,7 +9398,7 @@
       <c r="AC277" s="1"/>
       <c r="AD277" s="1"/>
     </row>
-    <row r="278" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9414,7 +9430,7 @@
       <c r="AC278" s="1"/>
       <c r="AD278" s="1"/>
     </row>
-    <row r="279" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9446,7 +9462,7 @@
       <c r="AC279" s="1"/>
       <c r="AD279" s="1"/>
     </row>
-    <row r="280" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9478,7 +9494,7 @@
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
     </row>
-    <row r="281" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9510,7 +9526,7 @@
       <c r="AC281" s="1"/>
       <c r="AD281" s="1"/>
     </row>
-    <row r="282" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9542,7 +9558,7 @@
       <c r="AC282" s="1"/>
       <c r="AD282" s="1"/>
     </row>
-    <row r="283" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9574,7 +9590,7 @@
       <c r="AC283" s="1"/>
       <c r="AD283" s="1"/>
     </row>
-    <row r="284" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9606,7 +9622,7 @@
       <c r="AC284" s="1"/>
       <c r="AD284" s="1"/>
     </row>
-    <row r="285" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9638,7 +9654,7 @@
       <c r="AC285" s="1"/>
       <c r="AD285" s="1"/>
     </row>
-    <row r="286" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9670,7 +9686,7 @@
       <c r="AC286" s="1"/>
       <c r="AD286" s="1"/>
     </row>
-    <row r="287" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9702,7 +9718,7 @@
       <c r="AC287" s="1"/>
       <c r="AD287" s="1"/>
     </row>
-    <row r="288" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9734,7 +9750,7 @@
       <c r="AC288" s="1"/>
       <c r="AD288" s="1"/>
     </row>
-    <row r="289" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9766,7 +9782,7 @@
       <c r="AC289" s="1"/>
       <c r="AD289" s="1"/>
     </row>
-    <row r="290" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9798,7 +9814,7 @@
       <c r="AC290" s="1"/>
       <c r="AD290" s="1"/>
     </row>
-    <row r="291" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9830,7 +9846,7 @@
       <c r="AC291" s="1"/>
       <c r="AD291" s="1"/>
     </row>
-    <row r="292" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9862,7 +9878,7 @@
       <c r="AC292" s="1"/>
       <c r="AD292" s="1"/>
     </row>
-    <row r="293" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9894,7 +9910,7 @@
       <c r="AC293" s="1"/>
       <c r="AD293" s="1"/>
     </row>
-    <row r="294" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9926,7 +9942,7 @@
       <c r="AC294" s="1"/>
       <c r="AD294" s="1"/>
     </row>
-    <row r="295" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9958,7 +9974,7 @@
       <c r="AC295" s="1"/>
       <c r="AD295" s="1"/>
     </row>
-    <row r="296" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -9990,7 +10006,7 @@
       <c r="AC296" s="1"/>
       <c r="AD296" s="1"/>
     </row>
-    <row r="297" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10022,7 +10038,7 @@
       <c r="AC297" s="1"/>
       <c r="AD297" s="1"/>
     </row>
-    <row r="298" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10054,7 +10070,7 @@
       <c r="AC298" s="1"/>
       <c r="AD298" s="1"/>
     </row>
-    <row r="299" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10086,7 +10102,7 @@
       <c r="AC299" s="1"/>
       <c r="AD299" s="1"/>
     </row>
-    <row r="300" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10118,7 +10134,7 @@
       <c r="AC300" s="1"/>
       <c r="AD300" s="1"/>
     </row>
-    <row r="301" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10150,7 +10166,7 @@
       <c r="AC301" s="1"/>
       <c r="AD301" s="1"/>
     </row>
-    <row r="302" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10182,7 +10198,7 @@
       <c r="AC302" s="1"/>
       <c r="AD302" s="1"/>
     </row>
-    <row r="303" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10214,7 +10230,7 @@
       <c r="AC303" s="1"/>
       <c r="AD303" s="1"/>
     </row>
-    <row r="304" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10246,7 +10262,7 @@
       <c r="AC304" s="1"/>
       <c r="AD304" s="1"/>
     </row>
-    <row r="305" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10278,7 +10294,7 @@
       <c r="AC305" s="1"/>
       <c r="AD305" s="1"/>
     </row>
-    <row r="306" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10310,7 +10326,7 @@
       <c r="AC306" s="1"/>
       <c r="AD306" s="1"/>
     </row>
-    <row r="307" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10342,7 +10358,7 @@
       <c r="AC307" s="1"/>
       <c r="AD307" s="1"/>
     </row>
-    <row r="308" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10374,7 +10390,7 @@
       <c r="AC308" s="1"/>
       <c r="AD308" s="1"/>
     </row>
-    <row r="309" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10406,7 +10422,7 @@
       <c r="AC309" s="1"/>
       <c r="AD309" s="1"/>
     </row>
-    <row r="310" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10438,7 +10454,7 @@
       <c r="AC310" s="1"/>
       <c r="AD310" s="1"/>
     </row>
-    <row r="311" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10470,7 +10486,7 @@
       <c r="AC311" s="1"/>
       <c r="AD311" s="1"/>
     </row>
-    <row r="312" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10502,7 +10518,7 @@
       <c r="AC312" s="1"/>
       <c r="AD312" s="1"/>
     </row>
-    <row r="313" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10534,7 +10550,7 @@
       <c r="AC313" s="1"/>
       <c r="AD313" s="1"/>
     </row>
-    <row r="314" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10566,7 +10582,7 @@
       <c r="AC314" s="1"/>
       <c r="AD314" s="1"/>
     </row>
-    <row r="315" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10598,7 +10614,7 @@
       <c r="AC315" s="1"/>
       <c r="AD315" s="1"/>
     </row>
-    <row r="316" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10630,7 +10646,7 @@
       <c r="AC316" s="1"/>
       <c r="AD316" s="1"/>
     </row>
-    <row r="317" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10662,7 +10678,7 @@
       <c r="AC317" s="1"/>
       <c r="AD317" s="1"/>
     </row>
-    <row r="318" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10694,7 +10710,7 @@
       <c r="AC318" s="1"/>
       <c r="AD318" s="1"/>
     </row>
-    <row r="319" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10726,7 +10742,7 @@
       <c r="AC319" s="1"/>
       <c r="AD319" s="1"/>
     </row>
-    <row r="320" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10758,7 +10774,7 @@
       <c r="AC320" s="1"/>
       <c r="AD320" s="1"/>
     </row>
-    <row r="321" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10790,7 +10806,7 @@
       <c r="AC321" s="1"/>
       <c r="AD321" s="1"/>
     </row>
-    <row r="322" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10822,7 +10838,7 @@
       <c r="AC322" s="1"/>
       <c r="AD322" s="1"/>
     </row>
-    <row r="323" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10854,7 +10870,7 @@
       <c r="AC323" s="1"/>
       <c r="AD323" s="1"/>
     </row>
-    <row r="324" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10886,7 +10902,7 @@
       <c r="AC324" s="1"/>
       <c r="AD324" s="1"/>
     </row>
-    <row r="325" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10918,7 +10934,7 @@
       <c r="AC325" s="1"/>
       <c r="AD325" s="1"/>
     </row>
-    <row r="326" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10950,7 +10966,7 @@
       <c r="AC326" s="1"/>
       <c r="AD326" s="1"/>
     </row>
-    <row r="327" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10982,7 +10998,7 @@
       <c r="AC327" s="1"/>
       <c r="AD327" s="1"/>
     </row>
-    <row r="328" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11014,7 +11030,7 @@
       <c r="AC328" s="1"/>
       <c r="AD328" s="1"/>
     </row>
-    <row r="329" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11046,7 +11062,7 @@
       <c r="AC329" s="1"/>
       <c r="AD329" s="1"/>
     </row>
-    <row r="330" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11078,7 +11094,7 @@
       <c r="AC330" s="1"/>
       <c r="AD330" s="1"/>
     </row>
-    <row r="331" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11110,7 +11126,7 @@
       <c r="AC331" s="1"/>
       <c r="AD331" s="1"/>
     </row>
-    <row r="332" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11142,7 +11158,7 @@
       <c r="AC332" s="1"/>
       <c r="AD332" s="1"/>
     </row>
-    <row r="333" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11174,7 +11190,7 @@
       <c r="AC333" s="1"/>
       <c r="AD333" s="1"/>
     </row>
-    <row r="334" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11206,7 +11222,7 @@
       <c r="AC334" s="1"/>
       <c r="AD334" s="1"/>
     </row>
-    <row r="335" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11238,7 +11254,7 @@
       <c r="AC335" s="1"/>
       <c r="AD335" s="1"/>
     </row>
-    <row r="336" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11270,7 +11286,7 @@
       <c r="AC336" s="1"/>
       <c r="AD336" s="1"/>
     </row>
-    <row r="337" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11302,7 +11318,7 @@
       <c r="AC337" s="1"/>
       <c r="AD337" s="1"/>
     </row>
-    <row r="338" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11334,7 +11350,7 @@
       <c r="AC338" s="1"/>
       <c r="AD338" s="1"/>
     </row>
-    <row r="339" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11366,7 +11382,7 @@
       <c r="AC339" s="1"/>
       <c r="AD339" s="1"/>
     </row>
-    <row r="340" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11398,7 +11414,7 @@
       <c r="AC340" s="1"/>
       <c r="AD340" s="1"/>
     </row>
-    <row r="341" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11430,7 +11446,7 @@
       <c r="AC341" s="1"/>
       <c r="AD341" s="1"/>
     </row>
-    <row r="342" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11462,7 +11478,7 @@
       <c r="AC342" s="1"/>
       <c r="AD342" s="1"/>
     </row>
-    <row r="343" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11494,7 +11510,7 @@
       <c r="AC343" s="1"/>
       <c r="AD343" s="1"/>
     </row>
-    <row r="344" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11526,7 +11542,7 @@
       <c r="AC344" s="1"/>
       <c r="AD344" s="1"/>
     </row>
-    <row r="345" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11558,7 +11574,7 @@
       <c r="AC345" s="1"/>
       <c r="AD345" s="1"/>
     </row>
-    <row r="346" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11590,7 +11606,7 @@
       <c r="AC346" s="1"/>
       <c r="AD346" s="1"/>
     </row>
-    <row r="347" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11622,7 +11638,7 @@
       <c r="AC347" s="1"/>
       <c r="AD347" s="1"/>
     </row>
-    <row r="348" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11654,7 +11670,7 @@
       <c r="AC348" s="1"/>
       <c r="AD348" s="1"/>
     </row>
-    <row r="349" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11686,7 +11702,7 @@
       <c r="AC349" s="1"/>
       <c r="AD349" s="1"/>
     </row>
-    <row r="350" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11718,7 +11734,7 @@
       <c r="AC350" s="1"/>
       <c r="AD350" s="1"/>
     </row>
-    <row r="351" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11750,7 +11766,7 @@
       <c r="AC351" s="1"/>
       <c r="AD351" s="1"/>
     </row>
-    <row r="352" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11782,7 +11798,7 @@
       <c r="AC352" s="1"/>
       <c r="AD352" s="1"/>
     </row>
-    <row r="353" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11814,7 +11830,7 @@
       <c r="AC353" s="1"/>
       <c r="AD353" s="1"/>
     </row>
-    <row r="354" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11846,7 +11862,7 @@
       <c r="AC354" s="1"/>
       <c r="AD354" s="1"/>
     </row>
-    <row r="355" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11878,7 +11894,7 @@
       <c r="AC355" s="1"/>
       <c r="AD355" s="1"/>
     </row>
-    <row r="356" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11910,7 +11926,7 @@
       <c r="AC356" s="1"/>
       <c r="AD356" s="1"/>
     </row>
-    <row r="357" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11942,7 +11958,7 @@
       <c r="AC357" s="1"/>
       <c r="AD357" s="1"/>
     </row>
-    <row r="358" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11974,7 +11990,7 @@
       <c r="AC358" s="1"/>
       <c r="AD358" s="1"/>
     </row>
-    <row r="359" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12006,7 +12022,7 @@
       <c r="AC359" s="1"/>
       <c r="AD359" s="1"/>
     </row>
-    <row r="360" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12038,7 +12054,7 @@
       <c r="AC360" s="1"/>
       <c r="AD360" s="1"/>
     </row>
-    <row r="361" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12070,7 +12086,7 @@
       <c r="AC361" s="1"/>
       <c r="AD361" s="1"/>
     </row>
-    <row r="362" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12102,7 +12118,7 @@
       <c r="AC362" s="1"/>
       <c r="AD362" s="1"/>
     </row>
-    <row r="363" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12134,7 +12150,7 @@
       <c r="AC363" s="1"/>
       <c r="AD363" s="1"/>
     </row>
-    <row r="364" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12166,7 +12182,7 @@
       <c r="AC364" s="1"/>
       <c r="AD364" s="1"/>
     </row>
-    <row r="365" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12198,7 +12214,7 @@
       <c r="AC365" s="1"/>
       <c r="AD365" s="1"/>
     </row>
-    <row r="366" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12230,7 +12246,7 @@
       <c r="AC366" s="1"/>
       <c r="AD366" s="1"/>
     </row>
-    <row r="367" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12262,7 +12278,7 @@
       <c r="AC367" s="1"/>
       <c r="AD367" s="1"/>
     </row>
-    <row r="368" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12294,7 +12310,7 @@
       <c r="AC368" s="1"/>
       <c r="AD368" s="1"/>
     </row>
-    <row r="369" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12326,7 +12342,7 @@
       <c r="AC369" s="1"/>
       <c r="AD369" s="1"/>
     </row>
-    <row r="370" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12358,7 +12374,7 @@
       <c r="AC370" s="1"/>
       <c r="AD370" s="1"/>
     </row>
-    <row r="371" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12390,7 +12406,7 @@
       <c r="AC371" s="1"/>
       <c r="AD371" s="1"/>
     </row>
-    <row r="372" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12422,7 +12438,7 @@
       <c r="AC372" s="1"/>
       <c r="AD372" s="1"/>
     </row>
-    <row r="373" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12454,7 +12470,7 @@
       <c r="AC373" s="1"/>
       <c r="AD373" s="1"/>
     </row>
-    <row r="374" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12486,7 +12502,7 @@
       <c r="AC374" s="1"/>
       <c r="AD374" s="1"/>
     </row>
-    <row r="375" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12518,7 +12534,7 @@
       <c r="AC375" s="1"/>
       <c r="AD375" s="1"/>
     </row>
-    <row r="376" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12550,7 +12566,7 @@
       <c r="AC376" s="1"/>
       <c r="AD376" s="1"/>
     </row>
-    <row r="377" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12582,7 +12598,7 @@
       <c r="AC377" s="1"/>
       <c r="AD377" s="1"/>
     </row>
-    <row r="378" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12614,7 +12630,7 @@
       <c r="AC378" s="1"/>
       <c r="AD378" s="1"/>
     </row>
-    <row r="379" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12646,7 +12662,7 @@
       <c r="AC379" s="1"/>
       <c r="AD379" s="1"/>
     </row>
-    <row r="380" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12678,7 +12694,7 @@
       <c r="AC380" s="1"/>
       <c r="AD380" s="1"/>
     </row>
-    <row r="381" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12710,7 +12726,7 @@
       <c r="AC381" s="1"/>
       <c r="AD381" s="1"/>
     </row>
-    <row r="382" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12742,7 +12758,7 @@
       <c r="AC382" s="1"/>
       <c r="AD382" s="1"/>
     </row>
-    <row r="383" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12774,7 +12790,7 @@
       <c r="AC383" s="1"/>
       <c r="AD383" s="1"/>
     </row>
-    <row r="384" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12806,7 +12822,7 @@
       <c r="AC384" s="1"/>
       <c r="AD384" s="1"/>
     </row>
-    <row r="385" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12838,7 +12854,7 @@
       <c r="AC385" s="1"/>
       <c r="AD385" s="1"/>
     </row>
-    <row r="386" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12870,7 +12886,7 @@
       <c r="AC386" s="1"/>
       <c r="AD386" s="1"/>
     </row>
-    <row r="387" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12902,7 +12918,7 @@
       <c r="AC387" s="1"/>
       <c r="AD387" s="1"/>
     </row>
-    <row r="388" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12934,7 +12950,7 @@
       <c r="AC388" s="1"/>
       <c r="AD388" s="1"/>
     </row>
-    <row r="389" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12966,7 +12982,7 @@
       <c r="AC389" s="1"/>
       <c r="AD389" s="1"/>
     </row>
-    <row r="390" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -12998,7 +13014,7 @@
       <c r="AC390" s="1"/>
       <c r="AD390" s="1"/>
     </row>
-    <row r="391" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13030,7 +13046,7 @@
       <c r="AC391" s="1"/>
       <c r="AD391" s="1"/>
     </row>
-    <row r="392" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13062,7 +13078,7 @@
       <c r="AC392" s="1"/>
       <c r="AD392" s="1"/>
     </row>
-    <row r="393" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13094,7 +13110,7 @@
       <c r="AC393" s="1"/>
       <c r="AD393" s="1"/>
     </row>
-    <row r="394" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13126,7 +13142,7 @@
       <c r="AC394" s="1"/>
       <c r="AD394" s="1"/>
     </row>
-    <row r="395" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13158,7 +13174,7 @@
       <c r="AC395" s="1"/>
       <c r="AD395" s="1"/>
     </row>
-    <row r="396" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13190,7 +13206,7 @@
       <c r="AC396" s="1"/>
       <c r="AD396" s="1"/>
     </row>
-    <row r="397" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13222,7 +13238,7 @@
       <c r="AC397" s="1"/>
       <c r="AD397" s="1"/>
     </row>
-    <row r="398" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13254,7 +13270,7 @@
       <c r="AC398" s="1"/>
       <c r="AD398" s="1"/>
     </row>
-    <row r="399" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13286,7 +13302,7 @@
       <c r="AC399" s="1"/>
       <c r="AD399" s="1"/>
     </row>
-    <row r="400" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13318,7 +13334,7 @@
       <c r="AC400" s="1"/>
       <c r="AD400" s="1"/>
     </row>
-    <row r="401" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13350,7 +13366,7 @@
       <c r="AC401" s="1"/>
       <c r="AD401" s="1"/>
     </row>
-    <row r="402" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13382,7 +13398,7 @@
       <c r="AC402" s="1"/>
       <c r="AD402" s="1"/>
     </row>
-    <row r="403" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13414,7 +13430,7 @@
       <c r="AC403" s="1"/>
       <c r="AD403" s="1"/>
     </row>
-    <row r="404" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13446,7 +13462,7 @@
       <c r="AC404" s="1"/>
       <c r="AD404" s="1"/>
     </row>
-    <row r="405" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13478,7 +13494,7 @@
       <c r="AC405" s="1"/>
       <c r="AD405" s="1"/>
     </row>
-    <row r="406" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13510,7 +13526,7 @@
       <c r="AC406" s="1"/>
       <c r="AD406" s="1"/>
     </row>
-    <row r="407" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13542,7 +13558,7 @@
       <c r="AC407" s="1"/>
       <c r="AD407" s="1"/>
     </row>
-    <row r="408" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13574,7 +13590,7 @@
       <c r="AC408" s="1"/>
       <c r="AD408" s="1"/>
     </row>
-    <row r="409" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13606,7 +13622,7 @@
       <c r="AC409" s="1"/>
       <c r="AD409" s="1"/>
     </row>
-    <row r="410" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13638,7 +13654,7 @@
       <c r="AC410" s="1"/>
       <c r="AD410" s="1"/>
     </row>
-    <row r="411" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13670,7 +13686,7 @@
       <c r="AC411" s="1"/>
       <c r="AD411" s="1"/>
     </row>
-    <row r="412" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13702,7 +13718,7 @@
       <c r="AC412" s="1"/>
       <c r="AD412" s="1"/>
     </row>
-    <row r="413" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13734,7 +13750,7 @@
       <c r="AC413" s="1"/>
       <c r="AD413" s="1"/>
     </row>
-    <row r="414" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13766,7 +13782,7 @@
       <c r="AC414" s="1"/>
       <c r="AD414" s="1"/>
     </row>
-    <row r="415" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13798,7 +13814,7 @@
       <c r="AC415" s="1"/>
       <c r="AD415" s="1"/>
     </row>
-    <row r="416" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13830,7 +13846,7 @@
       <c r="AC416" s="1"/>
       <c r="AD416" s="1"/>
     </row>
-    <row r="417" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13862,7 +13878,7 @@
       <c r="AC417" s="1"/>
       <c r="AD417" s="1"/>
     </row>
-    <row r="418" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13894,7 +13910,7 @@
       <c r="AC418" s="1"/>
       <c r="AD418" s="1"/>
     </row>
-    <row r="419" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13926,7 +13942,7 @@
       <c r="AC419" s="1"/>
       <c r="AD419" s="1"/>
     </row>
-    <row r="420" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13958,7 +13974,7 @@
       <c r="AC420" s="1"/>
       <c r="AD420" s="1"/>
     </row>
-    <row r="421" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13990,7 +14006,7 @@
       <c r="AC421" s="1"/>
       <c r="AD421" s="1"/>
     </row>
-    <row r="422" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14022,7 +14038,7 @@
       <c r="AC422" s="1"/>
       <c r="AD422" s="1"/>
     </row>
-    <row r="423" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14054,7 +14070,7 @@
       <c r="AC423" s="1"/>
       <c r="AD423" s="1"/>
     </row>
-    <row r="424" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14086,7 +14102,7 @@
       <c r="AC424" s="1"/>
       <c r="AD424" s="1"/>
     </row>
-    <row r="425" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14118,7 +14134,7 @@
       <c r="AC425" s="1"/>
       <c r="AD425" s="1"/>
     </row>
-    <row r="426" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14150,7 +14166,7 @@
       <c r="AC426" s="1"/>
       <c r="AD426" s="1"/>
     </row>
-    <row r="427" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14182,7 +14198,7 @@
       <c r="AC427" s="1"/>
       <c r="AD427" s="1"/>
     </row>
-    <row r="428" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14214,7 +14230,7 @@
       <c r="AC428" s="1"/>
       <c r="AD428" s="1"/>
     </row>
-    <row r="429" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14246,7 +14262,7 @@
       <c r="AC429" s="1"/>
       <c r="AD429" s="1"/>
     </row>
-    <row r="430" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14278,7 +14294,7 @@
       <c r="AC430" s="1"/>
       <c r="AD430" s="1"/>
     </row>
-    <row r="431" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14310,7 +14326,7 @@
       <c r="AC431" s="1"/>
       <c r="AD431" s="1"/>
     </row>
-    <row r="432" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14342,7 +14358,7 @@
       <c r="AC432" s="1"/>
       <c r="AD432" s="1"/>
     </row>
-    <row r="433" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14374,7 +14390,7 @@
       <c r="AC433" s="1"/>
       <c r="AD433" s="1"/>
     </row>
-    <row r="434" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14406,7 +14422,7 @@
       <c r="AC434" s="1"/>
       <c r="AD434" s="1"/>
     </row>
-    <row r="435" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14438,7 +14454,7 @@
       <c r="AC435" s="1"/>
       <c r="AD435" s="1"/>
     </row>
-    <row r="436" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14470,7 +14486,7 @@
       <c r="AC436" s="1"/>
       <c r="AD436" s="1"/>
     </row>
-    <row r="437" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14502,7 +14518,7 @@
       <c r="AC437" s="1"/>
       <c r="AD437" s="1"/>
     </row>
-    <row r="438" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14534,7 +14550,7 @@
       <c r="AC438" s="1"/>
       <c r="AD438" s="1"/>
     </row>
-    <row r="439" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14566,7 +14582,7 @@
       <c r="AC439" s="1"/>
       <c r="AD439" s="1"/>
     </row>
-    <row r="440" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14598,7 +14614,7 @@
       <c r="AC440" s="1"/>
       <c r="AD440" s="1"/>
     </row>
-    <row r="441" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14630,7 +14646,7 @@
       <c r="AC441" s="1"/>
       <c r="AD441" s="1"/>
     </row>
-    <row r="442" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14662,7 +14678,7 @@
       <c r="AC442" s="1"/>
       <c r="AD442" s="1"/>
     </row>
-    <row r="443" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14694,7 +14710,7 @@
       <c r="AC443" s="1"/>
       <c r="AD443" s="1"/>
     </row>
-    <row r="444" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14726,7 +14742,7 @@
       <c r="AC444" s="1"/>
       <c r="AD444" s="1"/>
     </row>
-    <row r="445" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14758,7 +14774,7 @@
       <c r="AC445" s="1"/>
       <c r="AD445" s="1"/>
     </row>
-    <row r="446" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14790,7 +14806,7 @@
       <c r="AC446" s="1"/>
       <c r="AD446" s="1"/>
     </row>
-    <row r="447" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14822,7 +14838,7 @@
       <c r="AC447" s="1"/>
       <c r="AD447" s="1"/>
     </row>
-    <row r="448" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14854,7 +14870,7 @@
       <c r="AC448" s="1"/>
       <c r="AD448" s="1"/>
     </row>
-    <row r="449" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14886,7 +14902,7 @@
       <c r="AC449" s="1"/>
       <c r="AD449" s="1"/>
     </row>
-    <row r="450" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14918,7 +14934,7 @@
       <c r="AC450" s="1"/>
       <c r="AD450" s="1"/>
     </row>
-    <row r="451" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14950,7 +14966,7 @@
       <c r="AC451" s="1"/>
       <c r="AD451" s="1"/>
     </row>
-    <row r="452" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14982,7 +14998,7 @@
       <c r="AC452" s="1"/>
       <c r="AD452" s="1"/>
     </row>
-    <row r="453" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15014,7 +15030,7 @@
       <c r="AC453" s="1"/>
       <c r="AD453" s="1"/>
     </row>
-    <row r="454" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15046,7 +15062,7 @@
       <c r="AC454" s="1"/>
       <c r="AD454" s="1"/>
     </row>
-    <row r="455" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15078,7 +15094,7 @@
       <c r="AC455" s="1"/>
       <c r="AD455" s="1"/>
     </row>
-    <row r="456" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15110,7 +15126,7 @@
       <c r="AC456" s="1"/>
       <c r="AD456" s="1"/>
     </row>
-    <row r="457" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15142,7 +15158,7 @@
       <c r="AC457" s="1"/>
       <c r="AD457" s="1"/>
     </row>
-    <row r="458" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15174,7 +15190,7 @@
       <c r="AC458" s="1"/>
       <c r="AD458" s="1"/>
     </row>
-    <row r="459" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15206,7 +15222,7 @@
       <c r="AC459" s="1"/>
       <c r="AD459" s="1"/>
     </row>
-    <row r="460" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15238,7 +15254,7 @@
       <c r="AC460" s="1"/>
       <c r="AD460" s="1"/>
     </row>
-    <row r="461" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15270,7 +15286,7 @@
       <c r="AC461" s="1"/>
       <c r="AD461" s="1"/>
     </row>
-    <row r="462" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15302,7 +15318,7 @@
       <c r="AC462" s="1"/>
       <c r="AD462" s="1"/>
     </row>
-    <row r="463" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15334,7 +15350,7 @@
       <c r="AC463" s="1"/>
       <c r="AD463" s="1"/>
     </row>
-    <row r="464" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15366,7 +15382,7 @@
       <c r="AC464" s="1"/>
       <c r="AD464" s="1"/>
     </row>
-    <row r="465" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15398,7 +15414,7 @@
       <c r="AC465" s="1"/>
       <c r="AD465" s="1"/>
     </row>
-    <row r="466" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15430,7 +15446,7 @@
       <c r="AC466" s="1"/>
       <c r="AD466" s="1"/>
     </row>
-    <row r="467" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15462,7 +15478,7 @@
       <c r="AC467" s="1"/>
       <c r="AD467" s="1"/>
     </row>
-    <row r="468" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15494,7 +15510,7 @@
       <c r="AC468" s="1"/>
       <c r="AD468" s="1"/>
     </row>
-    <row r="469" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15526,7 +15542,7 @@
       <c r="AC469" s="1"/>
       <c r="AD469" s="1"/>
     </row>
-    <row r="470" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15558,7 +15574,7 @@
       <c r="AC470" s="1"/>
       <c r="AD470" s="1"/>
     </row>
-    <row r="471" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15590,7 +15606,7 @@
       <c r="AC471" s="1"/>
       <c r="AD471" s="1"/>
     </row>
-    <row r="472" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15622,7 +15638,7 @@
       <c r="AC472" s="1"/>
       <c r="AD472" s="1"/>
     </row>
-    <row r="473" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15654,7 +15670,7 @@
       <c r="AC473" s="1"/>
       <c r="AD473" s="1"/>
     </row>
-    <row r="474" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15686,7 +15702,7 @@
       <c r="AC474" s="1"/>
       <c r="AD474" s="1"/>
     </row>
-    <row r="475" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15718,7 +15734,7 @@
       <c r="AC475" s="1"/>
       <c r="AD475" s="1"/>
     </row>
-    <row r="476" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15750,7 +15766,7 @@
       <c r="AC476" s="1"/>
       <c r="AD476" s="1"/>
     </row>
-    <row r="477" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15782,7 +15798,7 @@
       <c r="AC477" s="1"/>
       <c r="AD477" s="1"/>
     </row>
-    <row r="478" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15814,7 +15830,7 @@
       <c r="AC478" s="1"/>
       <c r="AD478" s="1"/>
     </row>
-    <row r="479" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15846,7 +15862,7 @@
       <c r="AC479" s="1"/>
       <c r="AD479" s="1"/>
     </row>
-    <row r="480" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15878,7 +15894,7 @@
       <c r="AC480" s="1"/>
       <c r="AD480" s="1"/>
     </row>
-    <row r="481" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15910,7 +15926,7 @@
       <c r="AC481" s="1"/>
       <c r="AD481" s="1"/>
     </row>
-    <row r="482" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15942,7 +15958,7 @@
       <c r="AC482" s="1"/>
       <c r="AD482" s="1"/>
     </row>
-    <row r="483" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15974,7 +15990,7 @@
       <c r="AC483" s="1"/>
       <c r="AD483" s="1"/>
     </row>
-    <row r="484" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16006,7 +16022,7 @@
       <c r="AC484" s="1"/>
       <c r="AD484" s="1"/>
     </row>
-    <row r="485" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16038,7 +16054,7 @@
       <c r="AC485" s="1"/>
       <c r="AD485" s="1"/>
     </row>
-    <row r="486" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16070,7 +16086,7 @@
       <c r="AC486" s="1"/>
       <c r="AD486" s="1"/>
     </row>
-    <row r="487" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16102,7 +16118,7 @@
       <c r="AC487" s="1"/>
       <c r="AD487" s="1"/>
     </row>
-    <row r="488" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16134,7 +16150,7 @@
       <c r="AC488" s="1"/>
       <c r="AD488" s="1"/>
     </row>
-    <row r="489" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16166,7 +16182,7 @@
       <c r="AC489" s="1"/>
       <c r="AD489" s="1"/>
     </row>
-    <row r="490" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16198,7 +16214,7 @@
       <c r="AC490" s="1"/>
       <c r="AD490" s="1"/>
     </row>
-    <row r="491" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16230,7 +16246,7 @@
       <c r="AC491" s="1"/>
       <c r="AD491" s="1"/>
     </row>
-    <row r="492" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16262,7 +16278,7 @@
       <c r="AC492" s="1"/>
       <c r="AD492" s="1"/>
     </row>
-    <row r="493" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16294,7 +16310,7 @@
       <c r="AC493" s="1"/>
       <c r="AD493" s="1"/>
     </row>
-    <row r="494" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16326,7 +16342,7 @@
       <c r="AC494" s="1"/>
       <c r="AD494" s="1"/>
     </row>
-    <row r="495" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16358,7 +16374,7 @@
       <c r="AC495" s="1"/>
       <c r="AD495" s="1"/>
     </row>
-    <row r="496" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16390,7 +16406,7 @@
       <c r="AC496" s="1"/>
       <c r="AD496" s="1"/>
     </row>
-    <row r="497" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16422,7 +16438,7 @@
       <c r="AC497" s="1"/>
       <c r="AD497" s="1"/>
     </row>
-    <row r="498" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16454,7 +16470,7 @@
       <c r="AC498" s="1"/>
       <c r="AD498" s="1"/>
     </row>
-    <row r="499" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16486,7 +16502,7 @@
       <c r="AC499" s="1"/>
       <c r="AD499" s="1"/>
     </row>
-    <row r="500" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16518,7 +16534,7 @@
       <c r="AC500" s="1"/>
       <c r="AD500" s="1"/>
     </row>
-    <row r="501" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16550,7 +16566,7 @@
       <c r="AC501" s="1"/>
       <c r="AD501" s="1"/>
     </row>
-    <row r="502" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16582,7 +16598,7 @@
       <c r="AC502" s="1"/>
       <c r="AD502" s="1"/>
     </row>
-    <row r="503" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16614,7 +16630,7 @@
       <c r="AC503" s="1"/>
       <c r="AD503" s="1"/>
     </row>
-    <row r="504" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16646,7 +16662,7 @@
       <c r="AC504" s="1"/>
       <c r="AD504" s="1"/>
     </row>
-    <row r="505" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16678,7 +16694,7 @@
       <c r="AC505" s="1"/>
       <c r="AD505" s="1"/>
     </row>
-    <row r="506" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16710,7 +16726,7 @@
       <c r="AC506" s="1"/>
       <c r="AD506" s="1"/>
     </row>
-    <row r="507" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16742,7 +16758,7 @@
       <c r="AC507" s="1"/>
       <c r="AD507" s="1"/>
     </row>
-    <row r="508" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16774,7 +16790,7 @@
       <c r="AC508" s="1"/>
       <c r="AD508" s="1"/>
     </row>
-    <row r="509" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16806,7 +16822,7 @@
       <c r="AC509" s="1"/>
       <c r="AD509" s="1"/>
     </row>
-    <row r="510" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16838,7 +16854,7 @@
       <c r="AC510" s="1"/>
       <c r="AD510" s="1"/>
     </row>
-    <row r="511" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16870,7 +16886,7 @@
       <c r="AC511" s="1"/>
       <c r="AD511" s="1"/>
     </row>
-    <row r="512" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16902,7 +16918,7 @@
       <c r="AC512" s="1"/>
       <c r="AD512" s="1"/>
     </row>
-    <row r="513" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16934,7 +16950,7 @@
       <c r="AC513" s="1"/>
       <c r="AD513" s="1"/>
     </row>
-    <row r="514" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16966,7 +16982,7 @@
       <c r="AC514" s="1"/>
       <c r="AD514" s="1"/>
     </row>
-    <row r="515" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16998,7 +17014,7 @@
       <c r="AC515" s="1"/>
       <c r="AD515" s="1"/>
     </row>
-    <row r="516" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17030,7 +17046,7 @@
       <c r="AC516" s="1"/>
       <c r="AD516" s="1"/>
     </row>
-    <row r="517" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17062,7 +17078,7 @@
       <c r="AC517" s="1"/>
       <c r="AD517" s="1"/>
     </row>
-    <row r="518" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17094,7 +17110,7 @@
       <c r="AC518" s="1"/>
       <c r="AD518" s="1"/>
     </row>
-    <row r="519" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17126,7 +17142,7 @@
       <c r="AC519" s="1"/>
       <c r="AD519" s="1"/>
     </row>
-    <row r="520" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17158,7 +17174,7 @@
       <c r="AC520" s="1"/>
       <c r="AD520" s="1"/>
     </row>
-    <row r="521" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17190,7 +17206,7 @@
       <c r="AC521" s="1"/>
       <c r="AD521" s="1"/>
     </row>
-    <row r="522" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17222,7 +17238,7 @@
       <c r="AC522" s="1"/>
       <c r="AD522" s="1"/>
     </row>
-    <row r="523" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17254,7 +17270,7 @@
       <c r="AC523" s="1"/>
       <c r="AD523" s="1"/>
     </row>
-    <row r="524" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17286,7 +17302,7 @@
       <c r="AC524" s="1"/>
       <c r="AD524" s="1"/>
     </row>
-    <row r="525" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17318,7 +17334,7 @@
       <c r="AC525" s="1"/>
       <c r="AD525" s="1"/>
     </row>
-    <row r="526" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17350,7 +17366,7 @@
       <c r="AC526" s="1"/>
       <c r="AD526" s="1"/>
     </row>
-    <row r="527" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17382,7 +17398,7 @@
       <c r="AC527" s="1"/>
       <c r="AD527" s="1"/>
     </row>
-    <row r="528" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17414,7 +17430,7 @@
       <c r="AC528" s="1"/>
       <c r="AD528" s="1"/>
     </row>
-    <row r="529" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17446,7 +17462,7 @@
       <c r="AC529" s="1"/>
       <c r="AD529" s="1"/>
     </row>
-    <row r="530" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17478,7 +17494,7 @@
       <c r="AC530" s="1"/>
       <c r="AD530" s="1"/>
     </row>
-    <row r="531" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17510,7 +17526,7 @@
       <c r="AC531" s="1"/>
       <c r="AD531" s="1"/>
     </row>
-    <row r="532" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17542,7 +17558,7 @@
       <c r="AC532" s="1"/>
       <c r="AD532" s="1"/>
     </row>
-    <row r="533" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17574,7 +17590,7 @@
       <c r="AC533" s="1"/>
       <c r="AD533" s="1"/>
     </row>
-    <row r="534" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17606,7 +17622,7 @@
       <c r="AC534" s="1"/>
       <c r="AD534" s="1"/>
     </row>
-    <row r="535" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17638,7 +17654,7 @@
       <c r="AC535" s="1"/>
       <c r="AD535" s="1"/>
     </row>
-    <row r="536" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17670,7 +17686,7 @@
       <c r="AC536" s="1"/>
       <c r="AD536" s="1"/>
     </row>
-    <row r="537" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17702,7 +17718,7 @@
       <c r="AC537" s="1"/>
       <c r="AD537" s="1"/>
     </row>
-    <row r="538" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17734,7 +17750,7 @@
       <c r="AC538" s="1"/>
       <c r="AD538" s="1"/>
     </row>
-    <row r="539" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17766,7 +17782,7 @@
       <c r="AC539" s="1"/>
       <c r="AD539" s="1"/>
     </row>
-    <row r="540" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17798,7 +17814,7 @@
       <c r="AC540" s="1"/>
       <c r="AD540" s="1"/>
     </row>
-    <row r="541" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17830,7 +17846,7 @@
       <c r="AC541" s="1"/>
       <c r="AD541" s="1"/>
     </row>
-    <row r="542" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17862,7 +17878,7 @@
       <c r="AC542" s="1"/>
       <c r="AD542" s="1"/>
     </row>
-    <row r="543" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17894,7 +17910,7 @@
       <c r="AC543" s="1"/>
       <c r="AD543" s="1"/>
     </row>
-    <row r="544" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17926,7 +17942,7 @@
       <c r="AC544" s="1"/>
       <c r="AD544" s="1"/>
     </row>
-    <row r="545" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17958,7 +17974,7 @@
       <c r="AC545" s="1"/>
       <c r="AD545" s="1"/>
     </row>
-    <row r="546" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17990,7 +18006,7 @@
       <c r="AC546" s="1"/>
       <c r="AD546" s="1"/>
     </row>
-    <row r="547" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18022,7 +18038,7 @@
       <c r="AC547" s="1"/>
       <c r="AD547" s="1"/>
     </row>
-    <row r="548" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18054,7 +18070,7 @@
       <c r="AC548" s="1"/>
       <c r="AD548" s="1"/>
     </row>
-    <row r="549" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18086,7 +18102,7 @@
       <c r="AC549" s="1"/>
       <c r="AD549" s="1"/>
     </row>
-    <row r="550" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18118,7 +18134,7 @@
       <c r="AC550" s="1"/>
       <c r="AD550" s="1"/>
     </row>
-    <row r="551" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18150,7 +18166,7 @@
       <c r="AC551" s="1"/>
       <c r="AD551" s="1"/>
     </row>
-    <row r="552" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18182,7 +18198,7 @@
       <c r="AC552" s="1"/>
       <c r="AD552" s="1"/>
     </row>
-    <row r="553" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18214,7 +18230,7 @@
       <c r="AC553" s="1"/>
       <c r="AD553" s="1"/>
     </row>
-    <row r="554" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18246,7 +18262,7 @@
       <c r="AC554" s="1"/>
       <c r="AD554" s="1"/>
     </row>
-    <row r="555" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18278,7 +18294,7 @@
       <c r="AC555" s="1"/>
       <c r="AD555" s="1"/>
     </row>
-    <row r="556" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18310,7 +18326,7 @@
       <c r="AC556" s="1"/>
       <c r="AD556" s="1"/>
     </row>
-    <row r="557" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18342,7 +18358,7 @@
       <c r="AC557" s="1"/>
       <c r="AD557" s="1"/>
     </row>
-    <row r="558" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18374,7 +18390,7 @@
       <c r="AC558" s="1"/>
       <c r="AD558" s="1"/>
     </row>
-    <row r="559" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18406,7 +18422,7 @@
       <c r="AC559" s="1"/>
       <c r="AD559" s="1"/>
     </row>
-    <row r="560" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18438,7 +18454,7 @@
       <c r="AC560" s="1"/>
       <c r="AD560" s="1"/>
     </row>
-    <row r="561" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18470,7 +18486,7 @@
       <c r="AC561" s="1"/>
       <c r="AD561" s="1"/>
     </row>
-    <row r="562" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18502,7 +18518,7 @@
       <c r="AC562" s="1"/>
       <c r="AD562" s="1"/>
     </row>
-    <row r="563" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18534,7 +18550,7 @@
       <c r="AC563" s="1"/>
       <c r="AD563" s="1"/>
     </row>
-    <row r="564" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18566,7 +18582,7 @@
       <c r="AC564" s="1"/>
       <c r="AD564" s="1"/>
     </row>
-    <row r="565" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18598,7 +18614,7 @@
       <c r="AC565" s="1"/>
       <c r="AD565" s="1"/>
     </row>
-    <row r="566" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18630,7 +18646,7 @@
       <c r="AC566" s="1"/>
       <c r="AD566" s="1"/>
     </row>
-    <row r="567" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18662,7 +18678,7 @@
       <c r="AC567" s="1"/>
       <c r="AD567" s="1"/>
     </row>
-    <row r="568" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18694,7 +18710,7 @@
       <c r="AC568" s="1"/>
       <c r="AD568" s="1"/>
     </row>
-    <row r="569" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18726,7 +18742,7 @@
       <c r="AC569" s="1"/>
       <c r="AD569" s="1"/>
     </row>
-    <row r="570" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18758,7 +18774,7 @@
       <c r="AC570" s="1"/>
       <c r="AD570" s="1"/>
     </row>
-    <row r="571" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18790,7 +18806,7 @@
       <c r="AC571" s="1"/>
       <c r="AD571" s="1"/>
     </row>
-    <row r="572" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18822,7 +18838,7 @@
       <c r="AC572" s="1"/>
       <c r="AD572" s="1"/>
     </row>
-    <row r="573" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18854,7 +18870,7 @@
       <c r="AC573" s="1"/>
       <c r="AD573" s="1"/>
     </row>
-    <row r="574" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18886,7 +18902,7 @@
       <c r="AC574" s="1"/>
       <c r="AD574" s="1"/>
     </row>
-    <row r="575" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18918,7 +18934,7 @@
       <c r="AC575" s="1"/>
       <c r="AD575" s="1"/>
     </row>
-    <row r="576" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18950,7 +18966,7 @@
       <c r="AC576" s="1"/>
       <c r="AD576" s="1"/>
     </row>
-    <row r="577" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18982,7 +18998,7 @@
       <c r="AC577" s="1"/>
       <c r="AD577" s="1"/>
     </row>
-    <row r="578" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19014,7 +19030,7 @@
       <c r="AC578" s="1"/>
       <c r="AD578" s="1"/>
     </row>
-    <row r="579" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19046,7 +19062,7 @@
       <c r="AC579" s="1"/>
       <c r="AD579" s="1"/>
     </row>
-    <row r="580" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19078,7 +19094,7 @@
       <c r="AC580" s="1"/>
       <c r="AD580" s="1"/>
     </row>
-    <row r="581" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19110,7 +19126,7 @@
       <c r="AC581" s="1"/>
       <c r="AD581" s="1"/>
     </row>
-    <row r="582" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19142,7 +19158,7 @@
       <c r="AC582" s="1"/>
       <c r="AD582" s="1"/>
     </row>
-    <row r="583" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19174,7 +19190,7 @@
       <c r="AC583" s="1"/>
       <c r="AD583" s="1"/>
     </row>
-    <row r="584" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19206,7 +19222,7 @@
       <c r="AC584" s="1"/>
       <c r="AD584" s="1"/>
     </row>
-    <row r="585" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19238,7 +19254,7 @@
       <c r="AC585" s="1"/>
       <c r="AD585" s="1"/>
     </row>
-    <row r="586" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19270,7 +19286,7 @@
       <c r="AC586" s="1"/>
       <c r="AD586" s="1"/>
     </row>
-    <row r="587" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19302,7 +19318,7 @@
       <c r="AC587" s="1"/>
       <c r="AD587" s="1"/>
     </row>
-    <row r="588" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19334,7 +19350,7 @@
       <c r="AC588" s="1"/>
       <c r="AD588" s="1"/>
     </row>
-    <row r="589" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19366,7 +19382,7 @@
       <c r="AC589" s="1"/>
       <c r="AD589" s="1"/>
     </row>
-    <row r="590" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19398,7 +19414,7 @@
       <c r="AC590" s="1"/>
       <c r="AD590" s="1"/>
     </row>
-    <row r="591" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19430,7 +19446,7 @@
       <c r="AC591" s="1"/>
       <c r="AD591" s="1"/>
     </row>
-    <row r="592" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19462,7 +19478,7 @@
       <c r="AC592" s="1"/>
       <c r="AD592" s="1"/>
     </row>
-    <row r="593" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19494,7 +19510,7 @@
       <c r="AC593" s="1"/>
       <c r="AD593" s="1"/>
     </row>
-    <row r="594" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19526,7 +19542,7 @@
       <c r="AC594" s="1"/>
       <c r="AD594" s="1"/>
     </row>
-    <row r="595" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19558,7 +19574,7 @@
       <c r="AC595" s="1"/>
       <c r="AD595" s="1"/>
     </row>
-    <row r="596" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19590,7 +19606,7 @@
       <c r="AC596" s="1"/>
       <c r="AD596" s="1"/>
     </row>
-    <row r="597" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19622,7 +19638,7 @@
       <c r="AC597" s="1"/>
       <c r="AD597" s="1"/>
     </row>
-    <row r="598" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19654,7 +19670,7 @@
       <c r="AC598" s="1"/>
       <c r="AD598" s="1"/>
     </row>
-    <row r="599" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19686,7 +19702,7 @@
       <c r="AC599" s="1"/>
       <c r="AD599" s="1"/>
     </row>
-    <row r="600" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19718,7 +19734,7 @@
       <c r="AC600" s="1"/>
       <c r="AD600" s="1"/>
     </row>
-    <row r="601" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19750,7 +19766,7 @@
       <c r="AC601" s="1"/>
       <c r="AD601" s="1"/>
     </row>
-    <row r="602" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19782,7 +19798,7 @@
       <c r="AC602" s="1"/>
       <c r="AD602" s="1"/>
     </row>
-    <row r="603" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19814,7 +19830,7 @@
       <c r="AC603" s="1"/>
       <c r="AD603" s="1"/>
     </row>
-    <row r="604" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19846,7 +19862,7 @@
       <c r="AC604" s="1"/>
       <c r="AD604" s="1"/>
     </row>
-    <row r="605" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19878,7 +19894,7 @@
       <c r="AC605" s="1"/>
       <c r="AD605" s="1"/>
     </row>
-    <row r="606" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19910,7 +19926,7 @@
       <c r="AC606" s="1"/>
       <c r="AD606" s="1"/>
     </row>
-    <row r="607" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19942,7 +19958,7 @@
       <c r="AC607" s="1"/>
       <c r="AD607" s="1"/>
     </row>
-    <row r="608" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19974,7 +19990,7 @@
       <c r="AC608" s="1"/>
       <c r="AD608" s="1"/>
     </row>
-    <row r="609" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20006,7 +20022,7 @@
       <c r="AC609" s="1"/>
       <c r="AD609" s="1"/>
     </row>
-    <row r="610" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20038,7 +20054,7 @@
       <c r="AC610" s="1"/>
       <c r="AD610" s="1"/>
     </row>
-    <row r="611" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20070,7 +20086,7 @@
       <c r="AC611" s="1"/>
       <c r="AD611" s="1"/>
     </row>
-    <row r="612" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20102,7 +20118,7 @@
       <c r="AC612" s="1"/>
       <c r="AD612" s="1"/>
     </row>
-    <row r="613" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20134,7 +20150,7 @@
       <c r="AC613" s="1"/>
       <c r="AD613" s="1"/>
     </row>
-    <row r="614" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20166,7 +20182,7 @@
       <c r="AC614" s="1"/>
       <c r="AD614" s="1"/>
     </row>
-    <row r="615" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20198,7 +20214,7 @@
       <c r="AC615" s="1"/>
       <c r="AD615" s="1"/>
     </row>
-    <row r="616" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20230,7 +20246,7 @@
       <c r="AC616" s="1"/>
       <c r="AD616" s="1"/>
     </row>
-    <row r="617" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20262,7 +20278,7 @@
       <c r="AC617" s="1"/>
       <c r="AD617" s="1"/>
     </row>
-    <row r="618" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20294,7 +20310,7 @@
       <c r="AC618" s="1"/>
       <c r="AD618" s="1"/>
     </row>
-    <row r="619" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20326,7 +20342,7 @@
       <c r="AC619" s="1"/>
       <c r="AD619" s="1"/>
     </row>
-    <row r="620" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20358,7 +20374,7 @@
       <c r="AC620" s="1"/>
       <c r="AD620" s="1"/>
     </row>
-    <row r="621" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20390,7 +20406,7 @@
       <c r="AC621" s="1"/>
       <c r="AD621" s="1"/>
     </row>
-    <row r="622" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20422,7 +20438,7 @@
       <c r="AC622" s="1"/>
       <c r="AD622" s="1"/>
     </row>
-    <row r="623" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20454,7 +20470,7 @@
       <c r="AC623" s="1"/>
       <c r="AD623" s="1"/>
     </row>
-    <row r="624" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20486,7 +20502,7 @@
       <c r="AC624" s="1"/>
       <c r="AD624" s="1"/>
     </row>
-    <row r="625" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20518,7 +20534,7 @@
       <c r="AC625" s="1"/>
       <c r="AD625" s="1"/>
     </row>
-    <row r="626" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20550,7 +20566,7 @@
       <c r="AC626" s="1"/>
       <c r="AD626" s="1"/>
     </row>
-    <row r="627" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20582,7 +20598,7 @@
       <c r="AC627" s="1"/>
       <c r="AD627" s="1"/>
     </row>
-    <row r="628" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20614,7 +20630,7 @@
       <c r="AC628" s="1"/>
       <c r="AD628" s="1"/>
     </row>
-    <row r="629" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20646,7 +20662,7 @@
       <c r="AC629" s="1"/>
       <c r="AD629" s="1"/>
     </row>
-    <row r="630" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20678,7 +20694,7 @@
       <c r="AC630" s="1"/>
       <c r="AD630" s="1"/>
     </row>
-    <row r="631" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20710,7 +20726,7 @@
       <c r="AC631" s="1"/>
       <c r="AD631" s="1"/>
     </row>
-    <row r="632" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20742,7 +20758,7 @@
       <c r="AC632" s="1"/>
       <c r="AD632" s="1"/>
     </row>
-    <row r="633" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20774,7 +20790,7 @@
       <c r="AC633" s="1"/>
       <c r="AD633" s="1"/>
     </row>
-    <row r="634" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20806,7 +20822,7 @@
       <c r="AC634" s="1"/>
       <c r="AD634" s="1"/>
     </row>
-    <row r="635" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20838,7 +20854,7 @@
       <c r="AC635" s="1"/>
       <c r="AD635" s="1"/>
     </row>
-    <row r="636" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20870,7 +20886,7 @@
       <c r="AC636" s="1"/>
       <c r="AD636" s="1"/>
     </row>
-    <row r="637" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20902,7 +20918,7 @@
       <c r="AC637" s="1"/>
       <c r="AD637" s="1"/>
     </row>
-    <row r="638" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20934,7 +20950,7 @@
       <c r="AC638" s="1"/>
       <c r="AD638" s="1"/>
     </row>
-    <row r="639" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20966,7 +20982,7 @@
       <c r="AC639" s="1"/>
       <c r="AD639" s="1"/>
     </row>
-    <row r="640" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20998,7 +21014,7 @@
       <c r="AC640" s="1"/>
       <c r="AD640" s="1"/>
     </row>
-    <row r="641" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21030,7 +21046,7 @@
       <c r="AC641" s="1"/>
       <c r="AD641" s="1"/>
     </row>
-    <row r="642" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21062,7 +21078,7 @@
       <c r="AC642" s="1"/>
       <c r="AD642" s="1"/>
     </row>
-    <row r="643" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21094,7 +21110,7 @@
       <c r="AC643" s="1"/>
       <c r="AD643" s="1"/>
     </row>
-    <row r="644" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21126,7 +21142,7 @@
       <c r="AC644" s="1"/>
       <c r="AD644" s="1"/>
     </row>
-    <row r="645" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21158,7 +21174,7 @@
       <c r="AC645" s="1"/>
       <c r="AD645" s="1"/>
     </row>
-    <row r="646" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21190,7 +21206,7 @@
       <c r="AC646" s="1"/>
       <c r="AD646" s="1"/>
     </row>
-    <row r="647" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21222,7 +21238,7 @@
       <c r="AC647" s="1"/>
       <c r="AD647" s="1"/>
     </row>
-    <row r="648" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21254,7 +21270,7 @@
       <c r="AC648" s="1"/>
       <c r="AD648" s="1"/>
     </row>
-    <row r="649" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21286,7 +21302,7 @@
       <c r="AC649" s="1"/>
       <c r="AD649" s="1"/>
     </row>
-    <row r="650" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21318,7 +21334,7 @@
       <c r="AC650" s="1"/>
       <c r="AD650" s="1"/>
     </row>
-    <row r="651" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21350,7 +21366,7 @@
       <c r="AC651" s="1"/>
       <c r="AD651" s="1"/>
     </row>
-    <row r="652" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21382,7 +21398,7 @@
       <c r="AC652" s="1"/>
       <c r="AD652" s="1"/>
     </row>
-    <row r="653" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21414,7 +21430,7 @@
       <c r="AC653" s="1"/>
       <c r="AD653" s="1"/>
     </row>
-    <row r="654" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21446,7 +21462,7 @@
       <c r="AC654" s="1"/>
       <c r="AD654" s="1"/>
     </row>
-    <row r="655" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21478,7 +21494,7 @@
       <c r="AC655" s="1"/>
       <c r="AD655" s="1"/>
     </row>
-    <row r="656" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21510,7 +21526,7 @@
       <c r="AC656" s="1"/>
       <c r="AD656" s="1"/>
     </row>
-    <row r="657" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21542,7 +21558,7 @@
       <c r="AC657" s="1"/>
       <c r="AD657" s="1"/>
     </row>
-    <row r="658" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21574,7 +21590,7 @@
       <c r="AC658" s="1"/>
       <c r="AD658" s="1"/>
     </row>
-    <row r="659" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21606,7 +21622,7 @@
       <c r="AC659" s="1"/>
       <c r="AD659" s="1"/>
     </row>
-    <row r="660" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21638,7 +21654,7 @@
       <c r="AC660" s="1"/>
       <c r="AD660" s="1"/>
     </row>
-    <row r="661" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21670,7 +21686,7 @@
       <c r="AC661" s="1"/>
       <c r="AD661" s="1"/>
     </row>
-    <row r="662" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21702,7 +21718,7 @@
       <c r="AC662" s="1"/>
       <c r="AD662" s="1"/>
     </row>
-    <row r="663" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21734,7 +21750,7 @@
       <c r="AC663" s="1"/>
       <c r="AD663" s="1"/>
     </row>
-    <row r="664" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21766,7 +21782,7 @@
       <c r="AC664" s="1"/>
       <c r="AD664" s="1"/>
     </row>
-    <row r="665" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21798,7 +21814,7 @@
       <c r="AC665" s="1"/>
       <c r="AD665" s="1"/>
     </row>
-    <row r="666" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21830,7 +21846,7 @@
       <c r="AC666" s="1"/>
       <c r="AD666" s="1"/>
     </row>
-    <row r="667" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21862,7 +21878,7 @@
       <c r="AC667" s="1"/>
       <c r="AD667" s="1"/>
     </row>
-    <row r="668" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21894,7 +21910,7 @@
       <c r="AC668" s="1"/>
       <c r="AD668" s="1"/>
     </row>
-    <row r="669" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21926,7 +21942,7 @@
       <c r="AC669" s="1"/>
       <c r="AD669" s="1"/>
     </row>
-    <row r="670" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21958,7 +21974,7 @@
       <c r="AC670" s="1"/>
       <c r="AD670" s="1"/>
     </row>
-    <row r="671" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21990,7 +22006,7 @@
       <c r="AC671" s="1"/>
       <c r="AD671" s="1"/>
     </row>
-    <row r="672" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -22022,7 +22038,7 @@
       <c r="AC672" s="1"/>
       <c r="AD672" s="1"/>
     </row>
-    <row r="673" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22054,7 +22070,7 @@
       <c r="AC673" s="1"/>
       <c r="AD673" s="1"/>
     </row>
-    <row r="674" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22086,7 +22102,7 @@
       <c r="AC674" s="1"/>
       <c r="AD674" s="1"/>
     </row>
-    <row r="675" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22118,7 +22134,7 @@
       <c r="AC675" s="1"/>
       <c r="AD675" s="1"/>
     </row>
-    <row r="676" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22150,7 +22166,7 @@
       <c r="AC676" s="1"/>
       <c r="AD676" s="1"/>
     </row>
-    <row r="677" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22182,7 +22198,7 @@
       <c r="AC677" s="1"/>
       <c r="AD677" s="1"/>
     </row>
-    <row r="678" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22214,7 +22230,7 @@
       <c r="AC678" s="1"/>
       <c r="AD678" s="1"/>
     </row>
-    <row r="679" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22246,7 +22262,7 @@
       <c r="AC679" s="1"/>
       <c r="AD679" s="1"/>
     </row>
-    <row r="680" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22278,7 +22294,7 @@
       <c r="AC680" s="1"/>
       <c r="AD680" s="1"/>
     </row>
-    <row r="681" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22310,7 +22326,7 @@
       <c r="AC681" s="1"/>
       <c r="AD681" s="1"/>
     </row>
-    <row r="682" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22342,7 +22358,7 @@
       <c r="AC682" s="1"/>
       <c r="AD682" s="1"/>
     </row>
-    <row r="683" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22374,7 +22390,7 @@
       <c r="AC683" s="1"/>
       <c r="AD683" s="1"/>
     </row>
-    <row r="684" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22406,7 +22422,7 @@
       <c r="AC684" s="1"/>
       <c r="AD684" s="1"/>
     </row>
-    <row r="685" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22438,7 +22454,7 @@
       <c r="AC685" s="1"/>
       <c r="AD685" s="1"/>
     </row>
-    <row r="686" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22470,7 +22486,7 @@
       <c r="AC686" s="1"/>
       <c r="AD686" s="1"/>
     </row>
-    <row r="687" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22502,7 +22518,7 @@
       <c r="AC687" s="1"/>
       <c r="AD687" s="1"/>
     </row>
-    <row r="688" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22534,7 +22550,7 @@
       <c r="AC688" s="1"/>
       <c r="AD688" s="1"/>
     </row>
-    <row r="689" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22566,7 +22582,7 @@
       <c r="AC689" s="1"/>
       <c r="AD689" s="1"/>
     </row>
-    <row r="690" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22598,7 +22614,7 @@
       <c r="AC690" s="1"/>
       <c r="AD690" s="1"/>
     </row>
-    <row r="691" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22630,7 +22646,7 @@
       <c r="AC691" s="1"/>
       <c r="AD691" s="1"/>
     </row>
-    <row r="692" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22662,7 +22678,7 @@
       <c r="AC692" s="1"/>
       <c r="AD692" s="1"/>
     </row>
-    <row r="693" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22694,7 +22710,7 @@
       <c r="AC693" s="1"/>
       <c r="AD693" s="1"/>
     </row>
-    <row r="694" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22726,7 +22742,7 @@
       <c r="AC694" s="1"/>
       <c r="AD694" s="1"/>
     </row>
-    <row r="695" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22758,7 +22774,7 @@
       <c r="AC695" s="1"/>
       <c r="AD695" s="1"/>
     </row>
-    <row r="696" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22790,7 +22806,7 @@
       <c r="AC696" s="1"/>
       <c r="AD696" s="1"/>
     </row>
-    <row r="697" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22822,7 +22838,7 @@
       <c r="AC697" s="1"/>
       <c r="AD697" s="1"/>
     </row>
-    <row r="698" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22854,7 +22870,7 @@
       <c r="AC698" s="1"/>
       <c r="AD698" s="1"/>
     </row>
-    <row r="699" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22886,7 +22902,7 @@
       <c r="AC699" s="1"/>
       <c r="AD699" s="1"/>
     </row>
-    <row r="700" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22918,7 +22934,7 @@
       <c r="AC700" s="1"/>
       <c r="AD700" s="1"/>
     </row>
-    <row r="701" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22950,7 +22966,7 @@
       <c r="AC701" s="1"/>
       <c r="AD701" s="1"/>
     </row>
-    <row r="702" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22982,7 +22998,7 @@
       <c r="AC702" s="1"/>
       <c r="AD702" s="1"/>
     </row>
-    <row r="703" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -23014,7 +23030,7 @@
       <c r="AC703" s="1"/>
       <c r="AD703" s="1"/>
     </row>
-    <row r="704" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -23046,7 +23062,7 @@
       <c r="AC704" s="1"/>
       <c r="AD704" s="1"/>
     </row>
-    <row r="705" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -23078,7 +23094,7 @@
       <c r="AC705" s="1"/>
       <c r="AD705" s="1"/>
     </row>
-    <row r="706" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23110,7 +23126,7 @@
       <c r="AC706" s="1"/>
       <c r="AD706" s="1"/>
     </row>
-    <row r="707" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23142,7 +23158,7 @@
       <c r="AC707" s="1"/>
       <c r="AD707" s="1"/>
     </row>
-    <row r="708" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23174,7 +23190,7 @@
       <c r="AC708" s="1"/>
       <c r="AD708" s="1"/>
     </row>
-    <row r="709" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23206,7 +23222,7 @@
       <c r="AC709" s="1"/>
       <c r="AD709" s="1"/>
     </row>
-    <row r="710" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23238,7 +23254,7 @@
       <c r="AC710" s="1"/>
       <c r="AD710" s="1"/>
     </row>
-    <row r="711" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23270,7 +23286,7 @@
       <c r="AC711" s="1"/>
       <c r="AD711" s="1"/>
     </row>
-    <row r="712" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23302,7 +23318,7 @@
       <c r="AC712" s="1"/>
       <c r="AD712" s="1"/>
     </row>
-    <row r="713" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23334,7 +23350,7 @@
       <c r="AC713" s="1"/>
       <c r="AD713" s="1"/>
     </row>
-    <row r="714" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23366,7 +23382,7 @@
       <c r="AC714" s="1"/>
       <c r="AD714" s="1"/>
     </row>
-    <row r="715" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23398,7 +23414,7 @@
       <c r="AC715" s="1"/>
       <c r="AD715" s="1"/>
     </row>
-    <row r="716" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23430,7 +23446,7 @@
       <c r="AC716" s="1"/>
       <c r="AD716" s="1"/>
     </row>
-    <row r="717" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23462,7 +23478,7 @@
       <c r="AC717" s="1"/>
       <c r="AD717" s="1"/>
     </row>
-    <row r="718" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23494,7 +23510,7 @@
       <c r="AC718" s="1"/>
       <c r="AD718" s="1"/>
     </row>
-    <row r="719" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23526,7 +23542,7 @@
       <c r="AC719" s="1"/>
       <c r="AD719" s="1"/>
     </row>
-    <row r="720" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23558,7 +23574,7 @@
       <c r="AC720" s="1"/>
       <c r="AD720" s="1"/>
     </row>
-    <row r="721" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23590,7 +23606,7 @@
       <c r="AC721" s="1"/>
       <c r="AD721" s="1"/>
     </row>
-    <row r="722" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23622,7 +23638,7 @@
       <c r="AC722" s="1"/>
       <c r="AD722" s="1"/>
     </row>
-    <row r="723" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23654,7 +23670,7 @@
       <c r="AC723" s="1"/>
       <c r="AD723" s="1"/>
     </row>
-    <row r="724" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23686,7 +23702,7 @@
       <c r="AC724" s="1"/>
       <c r="AD724" s="1"/>
     </row>
-    <row r="725" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23718,7 +23734,7 @@
       <c r="AC725" s="1"/>
       <c r="AD725" s="1"/>
     </row>
-    <row r="726" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23750,7 +23766,7 @@
       <c r="AC726" s="1"/>
       <c r="AD726" s="1"/>
     </row>
-    <row r="727" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23782,7 +23798,7 @@
       <c r="AC727" s="1"/>
       <c r="AD727" s="1"/>
     </row>
-    <row r="728" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23814,7 +23830,7 @@
       <c r="AC728" s="1"/>
       <c r="AD728" s="1"/>
     </row>
-    <row r="729" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23846,7 +23862,7 @@
       <c r="AC729" s="1"/>
       <c r="AD729" s="1"/>
     </row>
-    <row r="730" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23878,7 +23894,7 @@
       <c r="AC730" s="1"/>
       <c r="AD730" s="1"/>
     </row>
-    <row r="731" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23910,7 +23926,7 @@
       <c r="AC731" s="1"/>
       <c r="AD731" s="1"/>
     </row>
-    <row r="732" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23942,7 +23958,7 @@
       <c r="AC732" s="1"/>
       <c r="AD732" s="1"/>
     </row>
-    <row r="733" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23974,7 +23990,7 @@
       <c r="AC733" s="1"/>
       <c r="AD733" s="1"/>
     </row>
-    <row r="734" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -24006,7 +24022,7 @@
       <c r="AC734" s="1"/>
       <c r="AD734" s="1"/>
     </row>
-    <row r="735" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -24038,7 +24054,7 @@
       <c r="AC735" s="1"/>
       <c r="AD735" s="1"/>
     </row>
-    <row r="736" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -24070,7 +24086,7 @@
       <c r="AC736" s="1"/>
       <c r="AD736" s="1"/>
     </row>
-    <row r="737" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -24102,7 +24118,7 @@
       <c r="AC737" s="1"/>
       <c r="AD737" s="1"/>
     </row>
-    <row r="738" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24134,7 +24150,7 @@
       <c r="AC738" s="1"/>
       <c r="AD738" s="1"/>
     </row>
-    <row r="739" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24166,7 +24182,7 @@
       <c r="AC739" s="1"/>
       <c r="AD739" s="1"/>
     </row>
-    <row r="740" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24198,7 +24214,7 @@
       <c r="AC740" s="1"/>
       <c r="AD740" s="1"/>
     </row>
-    <row r="741" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24230,7 +24246,7 @@
       <c r="AC741" s="1"/>
       <c r="AD741" s="1"/>
     </row>
-    <row r="742" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24262,7 +24278,7 @@
       <c r="AC742" s="1"/>
       <c r="AD742" s="1"/>
     </row>
-    <row r="743" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24294,7 +24310,7 @@
       <c r="AC743" s="1"/>
       <c r="AD743" s="1"/>
     </row>
-    <row r="744" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24326,7 +24342,7 @@
       <c r="AC744" s="1"/>
       <c r="AD744" s="1"/>
     </row>
-    <row r="745" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24358,7 +24374,7 @@
       <c r="AC745" s="1"/>
       <c r="AD745" s="1"/>
     </row>
-    <row r="746" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24390,7 +24406,7 @@
       <c r="AC746" s="1"/>
       <c r="AD746" s="1"/>
     </row>
-    <row r="747" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24422,7 +24438,7 @@
       <c r="AC747" s="1"/>
       <c r="AD747" s="1"/>
     </row>
-    <row r="748" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24454,7 +24470,7 @@
       <c r="AC748" s="1"/>
       <c r="AD748" s="1"/>
     </row>
-    <row r="749" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24486,7 +24502,7 @@
       <c r="AC749" s="1"/>
       <c r="AD749" s="1"/>
     </row>
-    <row r="750" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24518,7 +24534,7 @@
       <c r="AC750" s="1"/>
       <c r="AD750" s="1"/>
     </row>
-    <row r="751" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24550,7 +24566,7 @@
       <c r="AC751" s="1"/>
       <c r="AD751" s="1"/>
     </row>
-    <row r="752" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24582,7 +24598,7 @@
       <c r="AC752" s="1"/>
       <c r="AD752" s="1"/>
     </row>
-    <row r="753" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24614,7 +24630,7 @@
       <c r="AC753" s="1"/>
       <c r="AD753" s="1"/>
     </row>
-    <row r="754" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24646,7 +24662,7 @@
       <c r="AC754" s="1"/>
       <c r="AD754" s="1"/>
     </row>
-    <row r="755" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24678,7 +24694,7 @@
       <c r="AC755" s="1"/>
       <c r="AD755" s="1"/>
     </row>
-    <row r="756" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24710,7 +24726,7 @@
       <c r="AC756" s="1"/>
       <c r="AD756" s="1"/>
     </row>
-    <row r="757" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24742,7 +24758,7 @@
       <c r="AC757" s="1"/>
       <c r="AD757" s="1"/>
     </row>
-    <row r="758" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24774,7 +24790,7 @@
       <c r="AC758" s="1"/>
       <c r="AD758" s="1"/>
     </row>
-    <row r="759" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24806,7 +24822,7 @@
       <c r="AC759" s="1"/>
       <c r="AD759" s="1"/>
     </row>
-    <row r="760" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24838,7 +24854,7 @@
       <c r="AC760" s="1"/>
       <c r="AD760" s="1"/>
     </row>
-    <row r="761" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24870,7 +24886,7 @@
       <c r="AC761" s="1"/>
       <c r="AD761" s="1"/>
     </row>
-    <row r="762" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24902,7 +24918,7 @@
       <c r="AC762" s="1"/>
       <c r="AD762" s="1"/>
     </row>
-    <row r="763" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24934,7 +24950,7 @@
       <c r="AC763" s="1"/>
       <c r="AD763" s="1"/>
     </row>
-    <row r="764" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24966,7 +24982,7 @@
       <c r="AC764" s="1"/>
       <c r="AD764" s="1"/>
     </row>
-    <row r="765" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -24998,7 +25014,7 @@
       <c r="AC765" s="1"/>
       <c r="AD765" s="1"/>
     </row>
-    <row r="766" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -25030,7 +25046,7 @@
       <c r="AC766" s="1"/>
       <c r="AD766" s="1"/>
     </row>
-    <row r="767" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -25062,7 +25078,7 @@
       <c r="AC767" s="1"/>
       <c r="AD767" s="1"/>
     </row>
-    <row r="768" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -25094,7 +25110,7 @@
       <c r="AC768" s="1"/>
       <c r="AD768" s="1"/>
     </row>
-    <row r="769" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -25126,7 +25142,7 @@
       <c r="AC769" s="1"/>
       <c r="AD769" s="1"/>
     </row>
-    <row r="770" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25158,7 +25174,7 @@
       <c r="AC770" s="1"/>
       <c r="AD770" s="1"/>
     </row>
-    <row r="771" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25190,7 +25206,7 @@
       <c r="AC771" s="1"/>
       <c r="AD771" s="1"/>
     </row>
-    <row r="772" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25222,7 +25238,7 @@
       <c r="AC772" s="1"/>
       <c r="AD772" s="1"/>
     </row>
-    <row r="773" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25254,7 +25270,7 @@
       <c r="AC773" s="1"/>
       <c r="AD773" s="1"/>
     </row>
-    <row r="774" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25286,7 +25302,7 @@
       <c r="AC774" s="1"/>
       <c r="AD774" s="1"/>
     </row>
-    <row r="775" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25318,7 +25334,7 @@
       <c r="AC775" s="1"/>
       <c r="AD775" s="1"/>
     </row>
-    <row r="776" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25350,7 +25366,7 @@
       <c r="AC776" s="1"/>
       <c r="AD776" s="1"/>
     </row>
-    <row r="777" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25382,7 +25398,7 @@
       <c r="AC777" s="1"/>
       <c r="AD777" s="1"/>
     </row>
-    <row r="778" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25414,7 +25430,7 @@
       <c r="AC778" s="1"/>
       <c r="AD778" s="1"/>
     </row>
-    <row r="779" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25446,7 +25462,7 @@
       <c r="AC779" s="1"/>
       <c r="AD779" s="1"/>
     </row>
-    <row r="780" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25478,7 +25494,7 @@
       <c r="AC780" s="1"/>
       <c r="AD780" s="1"/>
     </row>
-    <row r="781" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25510,7 +25526,7 @@
       <c r="AC781" s="1"/>
       <c r="AD781" s="1"/>
     </row>
-    <row r="782" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25542,7 +25558,7 @@
       <c r="AC782" s="1"/>
       <c r="AD782" s="1"/>
     </row>
-    <row r="783" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25574,7 +25590,7 @@
       <c r="AC783" s="1"/>
       <c r="AD783" s="1"/>
     </row>
-    <row r="784" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25606,7 +25622,7 @@
       <c r="AC784" s="1"/>
       <c r="AD784" s="1"/>
     </row>
-    <row r="785" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25638,7 +25654,7 @@
       <c r="AC785" s="1"/>
       <c r="AD785" s="1"/>
     </row>
-    <row r="786" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25670,7 +25686,7 @@
       <c r="AC786" s="1"/>
       <c r="AD786" s="1"/>
     </row>
-    <row r="787" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25702,7 +25718,7 @@
       <c r="AC787" s="1"/>
       <c r="AD787" s="1"/>
     </row>
-    <row r="788" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25734,7 +25750,7 @@
       <c r="AC788" s="1"/>
       <c r="AD788" s="1"/>
     </row>
-    <row r="789" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25766,7 +25782,7 @@
       <c r="AC789" s="1"/>
       <c r="AD789" s="1"/>
     </row>
-    <row r="790" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25798,7 +25814,7 @@
       <c r="AC790" s="1"/>
       <c r="AD790" s="1"/>
     </row>
-    <row r="791" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25830,7 +25846,7 @@
       <c r="AC791" s="1"/>
       <c r="AD791" s="1"/>
     </row>
-    <row r="792" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25862,7 +25878,7 @@
       <c r="AC792" s="1"/>
       <c r="AD792" s="1"/>
     </row>
-    <row r="793" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25894,7 +25910,7 @@
       <c r="AC793" s="1"/>
       <c r="AD793" s="1"/>
     </row>
-    <row r="794" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25926,7 +25942,7 @@
       <c r="AC794" s="1"/>
       <c r="AD794" s="1"/>
     </row>
-    <row r="795" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25958,7 +25974,7 @@
       <c r="AC795" s="1"/>
       <c r="AD795" s="1"/>
     </row>
-    <row r="796" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -25990,7 +26006,7 @@
       <c r="AC796" s="1"/>
       <c r="AD796" s="1"/>
     </row>
-    <row r="797" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -26022,7 +26038,7 @@
       <c r="AC797" s="1"/>
       <c r="AD797" s="1"/>
     </row>
-    <row r="798" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -26054,7 +26070,7 @@
       <c r="AC798" s="1"/>
       <c r="AD798" s="1"/>
     </row>
-    <row r="799" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -26086,7 +26102,7 @@
       <c r="AC799" s="1"/>
       <c r="AD799" s="1"/>
     </row>
-    <row r="800" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -26118,7 +26134,7 @@
       <c r="AC800" s="1"/>
       <c r="AD800" s="1"/>
     </row>
-    <row r="801" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -26150,7 +26166,7 @@
       <c r="AC801" s="1"/>
       <c r="AD801" s="1"/>
     </row>
-    <row r="802" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26182,7 +26198,7 @@
       <c r="AC802" s="1"/>
       <c r="AD802" s="1"/>
     </row>
-    <row r="803" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26214,7 +26230,7 @@
       <c r="AC803" s="1"/>
       <c r="AD803" s="1"/>
     </row>
-    <row r="804" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26246,7 +26262,7 @@
       <c r="AC804" s="1"/>
       <c r="AD804" s="1"/>
     </row>
-    <row r="805" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26278,7 +26294,7 @@
       <c r="AC805" s="1"/>
       <c r="AD805" s="1"/>
     </row>
-    <row r="806" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26310,7 +26326,7 @@
       <c r="AC806" s="1"/>
       <c r="AD806" s="1"/>
     </row>
-    <row r="807" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26342,7 +26358,7 @@
       <c r="AC807" s="1"/>
       <c r="AD807" s="1"/>
     </row>
-    <row r="808" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26374,7 +26390,7 @@
       <c r="AC808" s="1"/>
       <c r="AD808" s="1"/>
     </row>
-    <row r="809" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26406,7 +26422,7 @@
       <c r="AC809" s="1"/>
       <c r="AD809" s="1"/>
     </row>
-    <row r="810" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26438,7 +26454,7 @@
       <c r="AC810" s="1"/>
       <c r="AD810" s="1"/>
     </row>
-    <row r="811" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26470,7 +26486,7 @@
       <c r="AC811" s="1"/>
       <c r="AD811" s="1"/>
     </row>
-    <row r="812" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26502,7 +26518,7 @@
       <c r="AC812" s="1"/>
       <c r="AD812" s="1"/>
     </row>
-    <row r="813" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26534,7 +26550,7 @@
       <c r="AC813" s="1"/>
       <c r="AD813" s="1"/>
     </row>
-    <row r="814" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26566,7 +26582,7 @@
       <c r="AC814" s="1"/>
       <c r="AD814" s="1"/>
     </row>
-    <row r="815" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26598,7 +26614,7 @@
       <c r="AC815" s="1"/>
       <c r="AD815" s="1"/>
     </row>
-    <row r="816" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26630,7 +26646,7 @@
       <c r="AC816" s="1"/>
       <c r="AD816" s="1"/>
     </row>
-    <row r="817" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26662,7 +26678,7 @@
       <c r="AC817" s="1"/>
       <c r="AD817" s="1"/>
     </row>
-    <row r="818" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26694,7 +26710,7 @@
       <c r="AC818" s="1"/>
       <c r="AD818" s="1"/>
     </row>
-    <row r="819" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26726,7 +26742,7 @@
       <c r="AC819" s="1"/>
       <c r="AD819" s="1"/>
     </row>
-    <row r="820" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26758,7 +26774,7 @@
       <c r="AC820" s="1"/>
       <c r="AD820" s="1"/>
     </row>
-    <row r="821" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26790,7 +26806,7 @@
       <c r="AC821" s="1"/>
       <c r="AD821" s="1"/>
     </row>
-    <row r="822" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26822,7 +26838,7 @@
       <c r="AC822" s="1"/>
       <c r="AD822" s="1"/>
     </row>
-    <row r="823" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26854,7 +26870,7 @@
       <c r="AC823" s="1"/>
       <c r="AD823" s="1"/>
     </row>
-    <row r="824" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26886,7 +26902,7 @@
       <c r="AC824" s="1"/>
       <c r="AD824" s="1"/>
     </row>
-    <row r="825" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26918,7 +26934,7 @@
       <c r="AC825" s="1"/>
       <c r="AD825" s="1"/>
     </row>
-    <row r="826" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26950,7 +26966,7 @@
       <c r="AC826" s="1"/>
       <c r="AD826" s="1"/>
     </row>
-    <row r="827" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26982,7 +26998,7 @@
       <c r="AC827" s="1"/>
       <c r="AD827" s="1"/>
     </row>
-    <row r="828" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -27014,7 +27030,7 @@
       <c r="AC828" s="1"/>
       <c r="AD828" s="1"/>
     </row>
-    <row r="829" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -27046,7 +27062,7 @@
       <c r="AC829" s="1"/>
       <c r="AD829" s="1"/>
     </row>
-    <row r="830" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -27078,7 +27094,7 @@
       <c r="AC830" s="1"/>
       <c r="AD830" s="1"/>
     </row>
-    <row r="831" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -27110,7 +27126,7 @@
       <c r="AC831" s="1"/>
       <c r="AD831" s="1"/>
     </row>
-    <row r="832" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -27142,7 +27158,7 @@
       <c r="AC832" s="1"/>
       <c r="AD832" s="1"/>
     </row>
-    <row r="833" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -27174,7 +27190,7 @@
       <c r="AC833" s="1"/>
       <c r="AD833" s="1"/>
     </row>
-    <row r="834" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -27206,7 +27222,7 @@
       <c r="AC834" s="1"/>
       <c r="AD834" s="1"/>
     </row>
-    <row r="835" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27238,7 +27254,7 @@
       <c r="AC835" s="1"/>
       <c r="AD835" s="1"/>
     </row>
-    <row r="836" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27270,7 +27286,7 @@
       <c r="AC836" s="1"/>
       <c r="AD836" s="1"/>
     </row>
-    <row r="837" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27302,7 +27318,7 @@
       <c r="AC837" s="1"/>
       <c r="AD837" s="1"/>
     </row>
-    <row r="838" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27334,7 +27350,7 @@
       <c r="AC838" s="1"/>
       <c r="AD838" s="1"/>
     </row>
-    <row r="839" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27366,7 +27382,7 @@
       <c r="AC839" s="1"/>
       <c r="AD839" s="1"/>
     </row>
-    <row r="840" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27398,7 +27414,7 @@
       <c r="AC840" s="1"/>
       <c r="AD840" s="1"/>
     </row>
-    <row r="841" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27430,7 +27446,7 @@
       <c r="AC841" s="1"/>
       <c r="AD841" s="1"/>
     </row>
-    <row r="842" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27462,7 +27478,7 @@
       <c r="AC842" s="1"/>
       <c r="AD842" s="1"/>
     </row>
-    <row r="843" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27494,7 +27510,7 @@
       <c r="AC843" s="1"/>
       <c r="AD843" s="1"/>
     </row>
-    <row r="844" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27526,7 +27542,7 @@
       <c r="AC844" s="1"/>
       <c r="AD844" s="1"/>
     </row>
-    <row r="845" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27558,7 +27574,7 @@
       <c r="AC845" s="1"/>
       <c r="AD845" s="1"/>
     </row>
-    <row r="846" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27590,7 +27606,7 @@
       <c r="AC846" s="1"/>
       <c r="AD846" s="1"/>
     </row>
-    <row r="847" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27622,7 +27638,7 @@
       <c r="AC847" s="1"/>
       <c r="AD847" s="1"/>
     </row>
-    <row r="848" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27654,7 +27670,7 @@
       <c r="AC848" s="1"/>
       <c r="AD848" s="1"/>
     </row>
-    <row r="849" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27686,7 +27702,7 @@
       <c r="AC849" s="1"/>
       <c r="AD849" s="1"/>
     </row>
-    <row r="850" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27718,7 +27734,7 @@
       <c r="AC850" s="1"/>
       <c r="AD850" s="1"/>
     </row>
-    <row r="851" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27750,7 +27766,7 @@
       <c r="AC851" s="1"/>
       <c r="AD851" s="1"/>
     </row>
-    <row r="852" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27782,7 +27798,7 @@
       <c r="AC852" s="1"/>
       <c r="AD852" s="1"/>
     </row>
-    <row r="853" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27814,7 +27830,7 @@
       <c r="AC853" s="1"/>
       <c r="AD853" s="1"/>
     </row>
-    <row r="854" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27846,7 +27862,7 @@
       <c r="AC854" s="1"/>
       <c r="AD854" s="1"/>
     </row>
-    <row r="855" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27878,7 +27894,7 @@
       <c r="AC855" s="1"/>
       <c r="AD855" s="1"/>
     </row>
-    <row r="856" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27910,7 +27926,7 @@
       <c r="AC856" s="1"/>
       <c r="AD856" s="1"/>
     </row>
-    <row r="857" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27942,7 +27958,7 @@
       <c r="AC857" s="1"/>
       <c r="AD857" s="1"/>
     </row>
-    <row r="858" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27974,7 +27990,7 @@
       <c r="AC858" s="1"/>
       <c r="AD858" s="1"/>
     </row>
-    <row r="859" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -28006,7 +28022,7 @@
       <c r="AC859" s="1"/>
       <c r="AD859" s="1"/>
     </row>
-    <row r="860" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -28038,7 +28054,7 @@
       <c r="AC860" s="1"/>
       <c r="AD860" s="1"/>
     </row>
-    <row r="861" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -28070,7 +28086,7 @@
       <c r="AC861" s="1"/>
       <c r="AD861" s="1"/>
     </row>
-    <row r="862" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -28102,7 +28118,7 @@
       <c r="AC862" s="1"/>
       <c r="AD862" s="1"/>
     </row>
-    <row r="863" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -28134,7 +28150,7 @@
       <c r="AC863" s="1"/>
       <c r="AD863" s="1"/>
     </row>
-    <row r="864" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -28166,7 +28182,7 @@
       <c r="AC864" s="1"/>
       <c r="AD864" s="1"/>
     </row>
-    <row r="865" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -28198,7 +28214,7 @@
       <c r="AC865" s="1"/>
       <c r="AD865" s="1"/>
     </row>
-    <row r="866" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -28230,7 +28246,7 @@
       <c r="AC866" s="1"/>
       <c r="AD866" s="1"/>
     </row>
-    <row r="867" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28262,7 +28278,7 @@
       <c r="AC867" s="1"/>
       <c r="AD867" s="1"/>
     </row>
-    <row r="868" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28294,7 +28310,7 @@
       <c r="AC868" s="1"/>
       <c r="AD868" s="1"/>
     </row>
-    <row r="869" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28326,7 +28342,7 @@
       <c r="AC869" s="1"/>
       <c r="AD869" s="1"/>
     </row>
-    <row r="870" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28358,7 +28374,7 @@
       <c r="AC870" s="1"/>
       <c r="AD870" s="1"/>
     </row>
-    <row r="871" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28390,7 +28406,7 @@
       <c r="AC871" s="1"/>
       <c r="AD871" s="1"/>
     </row>
-    <row r="872" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28422,7 +28438,7 @@
       <c r="AC872" s="1"/>
       <c r="AD872" s="1"/>
     </row>
-    <row r="873" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28454,7 +28470,7 @@
       <c r="AC873" s="1"/>
       <c r="AD873" s="1"/>
     </row>
-    <row r="874" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28486,7 +28502,7 @@
       <c r="AC874" s="1"/>
       <c r="AD874" s="1"/>
     </row>
-    <row r="875" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28518,7 +28534,7 @@
       <c r="AC875" s="1"/>
       <c r="AD875" s="1"/>
     </row>
-    <row r="876" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28550,7 +28566,7 @@
       <c r="AC876" s="1"/>
       <c r="AD876" s="1"/>
     </row>
-    <row r="877" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28582,7 +28598,7 @@
       <c r="AC877" s="1"/>
       <c r="AD877" s="1"/>
     </row>
-    <row r="878" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28614,7 +28630,7 @@
       <c r="AC878" s="1"/>
       <c r="AD878" s="1"/>
     </row>
-    <row r="879" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28646,7 +28662,7 @@
       <c r="AC879" s="1"/>
       <c r="AD879" s="1"/>
     </row>
-    <row r="880" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28678,7 +28694,7 @@
       <c r="AC880" s="1"/>
       <c r="AD880" s="1"/>
     </row>
-    <row r="881" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28710,7 +28726,7 @@
       <c r="AC881" s="1"/>
       <c r="AD881" s="1"/>
     </row>
-    <row r="882" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28742,7 +28758,7 @@
       <c r="AC882" s="1"/>
       <c r="AD882" s="1"/>
     </row>
-    <row r="883" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28774,7 +28790,7 @@
       <c r="AC883" s="1"/>
       <c r="AD883" s="1"/>
     </row>
-    <row r="884" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28806,7 +28822,7 @@
       <c r="AC884" s="1"/>
       <c r="AD884" s="1"/>
     </row>
-    <row r="885" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28838,7 +28854,7 @@
       <c r="AC885" s="1"/>
       <c r="AD885" s="1"/>
     </row>
-    <row r="886" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28870,7 +28886,7 @@
       <c r="AC886" s="1"/>
       <c r="AD886" s="1"/>
     </row>
-    <row r="887" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28902,7 +28918,7 @@
       <c r="AC887" s="1"/>
       <c r="AD887" s="1"/>
     </row>
-    <row r="888" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28934,7 +28950,7 @@
       <c r="AC888" s="1"/>
       <c r="AD888" s="1"/>
     </row>
-    <row r="889" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28966,7 +28982,7 @@
       <c r="AC889" s="1"/>
       <c r="AD889" s="1"/>
     </row>
-    <row r="890" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -28998,7 +29014,7 @@
       <c r="AC890" s="1"/>
       <c r="AD890" s="1"/>
     </row>
-    <row r="891" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -29030,7 +29046,7 @@
       <c r="AC891" s="1"/>
       <c r="AD891" s="1"/>
     </row>
-    <row r="892" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -29062,7 +29078,7 @@
       <c r="AC892" s="1"/>
       <c r="AD892" s="1"/>
     </row>
-    <row r="893" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -29094,7 +29110,7 @@
       <c r="AC893" s="1"/>
       <c r="AD893" s="1"/>
     </row>
-    <row r="894" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -29126,7 +29142,7 @@
       <c r="AC894" s="1"/>
       <c r="AD894" s="1"/>
     </row>
-    <row r="895" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -29158,7 +29174,7 @@
       <c r="AC895" s="1"/>
       <c r="AD895" s="1"/>
     </row>
-    <row r="896" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -29190,7 +29206,7 @@
       <c r="AC896" s="1"/>
       <c r="AD896" s="1"/>
     </row>
-    <row r="897" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -29222,7 +29238,7 @@
       <c r="AC897" s="1"/>
       <c r="AD897" s="1"/>
     </row>
-    <row r="898" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -29254,7 +29270,7 @@
       <c r="AC898" s="1"/>
       <c r="AD898" s="1"/>
     </row>
-    <row r="899" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29286,7 +29302,7 @@
       <c r="AC899" s="1"/>
       <c r="AD899" s="1"/>
     </row>
-    <row r="900" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29318,7 +29334,7 @@
       <c r="AC900" s="1"/>
       <c r="AD900" s="1"/>
     </row>
-    <row r="901" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29350,7 +29366,7 @@
       <c r="AC901" s="1"/>
       <c r="AD901" s="1"/>
     </row>
-    <row r="902" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29382,7 +29398,7 @@
       <c r="AC902" s="1"/>
       <c r="AD902" s="1"/>
     </row>
-    <row r="903" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29414,7 +29430,7 @@
       <c r="AC903" s="1"/>
       <c r="AD903" s="1"/>
     </row>
-    <row r="904" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29446,7 +29462,7 @@
       <c r="AC904" s="1"/>
       <c r="AD904" s="1"/>
     </row>
-    <row r="905" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29478,7 +29494,7 @@
       <c r="AC905" s="1"/>
       <c r="AD905" s="1"/>
     </row>
-    <row r="906" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29510,7 +29526,7 @@
       <c r="AC906" s="1"/>
       <c r="AD906" s="1"/>
     </row>
-    <row r="907" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29542,7 +29558,7 @@
       <c r="AC907" s="1"/>
       <c r="AD907" s="1"/>
     </row>
-    <row r="908" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29574,7 +29590,7 @@
       <c r="AC908" s="1"/>
       <c r="AD908" s="1"/>
     </row>
-    <row r="909" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29606,7 +29622,7 @@
       <c r="AC909" s="1"/>
       <c r="AD909" s="1"/>
     </row>
-    <row r="910" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29638,7 +29654,7 @@
       <c r="AC910" s="1"/>
       <c r="AD910" s="1"/>
     </row>
-    <row r="911" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29670,7 +29686,7 @@
       <c r="AC911" s="1"/>
       <c r="AD911" s="1"/>
     </row>
-    <row r="912" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29702,7 +29718,7 @@
       <c r="AC912" s="1"/>
       <c r="AD912" s="1"/>
     </row>
-    <row r="913" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29734,7 +29750,7 @@
       <c r="AC913" s="1"/>
       <c r="AD913" s="1"/>
     </row>
-    <row r="914" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29766,7 +29782,7 @@
       <c r="AC914" s="1"/>
       <c r="AD914" s="1"/>
     </row>
-    <row r="915" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29798,7 +29814,7 @@
       <c r="AC915" s="1"/>
       <c r="AD915" s="1"/>
     </row>
-    <row r="916" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29830,7 +29846,7 @@
       <c r="AC916" s="1"/>
       <c r="AD916" s="1"/>
     </row>
-    <row r="917" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29862,7 +29878,7 @@
       <c r="AC917" s="1"/>
       <c r="AD917" s="1"/>
     </row>
-    <row r="918" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29894,7 +29910,7 @@
       <c r="AC918" s="1"/>
       <c r="AD918" s="1"/>
     </row>
-    <row r="919" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29926,7 +29942,7 @@
       <c r="AC919" s="1"/>
       <c r="AD919" s="1"/>
     </row>
-    <row r="920" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29958,7 +29974,7 @@
       <c r="AC920" s="1"/>
       <c r="AD920" s="1"/>
     </row>
-    <row r="921" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -29990,7 +30006,7 @@
       <c r="AC921" s="1"/>
       <c r="AD921" s="1"/>
     </row>
-    <row r="922" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -30022,7 +30038,7 @@
       <c r="AC922" s="1"/>
       <c r="AD922" s="1"/>
     </row>
-    <row r="923" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -30054,7 +30070,7 @@
       <c r="AC923" s="1"/>
       <c r="AD923" s="1"/>
     </row>
-    <row r="924" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -30086,7 +30102,7 @@
       <c r="AC924" s="1"/>
       <c r="AD924" s="1"/>
     </row>
-    <row r="925" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -30118,7 +30134,7 @@
       <c r="AC925" s="1"/>
       <c r="AD925" s="1"/>
     </row>
-    <row r="926" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -30150,7 +30166,7 @@
       <c r="AC926" s="1"/>
       <c r="AD926" s="1"/>
     </row>
-    <row r="927" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -30182,7 +30198,7 @@
       <c r="AC927" s="1"/>
       <c r="AD927" s="1"/>
     </row>
-    <row r="928" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -30214,7 +30230,7 @@
       <c r="AC928" s="1"/>
       <c r="AD928" s="1"/>
     </row>
-    <row r="929" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -30246,7 +30262,7 @@
       <c r="AC929" s="1"/>
       <c r="AD929" s="1"/>
     </row>
-    <row r="930" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -30278,7 +30294,7 @@
       <c r="AC930" s="1"/>
       <c r="AD930" s="1"/>
     </row>
-    <row r="931" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30310,7 +30326,7 @@
       <c r="AC931" s="1"/>
       <c r="AD931" s="1"/>
     </row>
-    <row r="932" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30342,7 +30358,7 @@
       <c r="AC932" s="1"/>
       <c r="AD932" s="1"/>
     </row>
-    <row r="933" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30374,7 +30390,7 @@
       <c r="AC933" s="1"/>
       <c r="AD933" s="1"/>
     </row>
-    <row r="934" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30406,7 +30422,7 @@
       <c r="AC934" s="1"/>
       <c r="AD934" s="1"/>
     </row>
-    <row r="935" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30438,7 +30454,7 @@
       <c r="AC935" s="1"/>
       <c r="AD935" s="1"/>
     </row>
-    <row r="936" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30470,7 +30486,7 @@
       <c r="AC936" s="1"/>
       <c r="AD936" s="1"/>
     </row>
-    <row r="937" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30502,7 +30518,7 @@
       <c r="AC937" s="1"/>
       <c r="AD937" s="1"/>
     </row>
-    <row r="938" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30534,7 +30550,7 @@
       <c r="AC938" s="1"/>
       <c r="AD938" s="1"/>
     </row>
-    <row r="939" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30566,7 +30582,7 @@
       <c r="AC939" s="1"/>
       <c r="AD939" s="1"/>
     </row>
-    <row r="940" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30598,7 +30614,7 @@
       <c r="AC940" s="1"/>
       <c r="AD940" s="1"/>
     </row>
-    <row r="941" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30630,7 +30646,7 @@
       <c r="AC941" s="1"/>
       <c r="AD941" s="1"/>
     </row>
-    <row r="942" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30662,7 +30678,7 @@
       <c r="AC942" s="1"/>
       <c r="AD942" s="1"/>
     </row>
-    <row r="943" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30694,7 +30710,7 @@
       <c r="AC943" s="1"/>
       <c r="AD943" s="1"/>
     </row>
-    <row r="944" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30726,7 +30742,7 @@
       <c r="AC944" s="1"/>
       <c r="AD944" s="1"/>
     </row>
-    <row r="945" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30758,7 +30774,7 @@
       <c r="AC945" s="1"/>
       <c r="AD945" s="1"/>
     </row>
-    <row r="946" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30790,7 +30806,7 @@
       <c r="AC946" s="1"/>
       <c r="AD946" s="1"/>
     </row>
-    <row r="947" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30822,7 +30838,7 @@
       <c r="AC947" s="1"/>
       <c r="AD947" s="1"/>
     </row>
-    <row r="948" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30854,7 +30870,7 @@
       <c r="AC948" s="1"/>
       <c r="AD948" s="1"/>
     </row>
-    <row r="949" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30886,7 +30902,7 @@
       <c r="AC949" s="1"/>
       <c r="AD949" s="1"/>
     </row>
-    <row r="950" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30918,7 +30934,7 @@
       <c r="AC950" s="1"/>
       <c r="AD950" s="1"/>
     </row>
-    <row r="951" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30950,7 +30966,7 @@
       <c r="AC951" s="1"/>
       <c r="AD951" s="1"/>
     </row>
-    <row r="952" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30982,7 +30998,7 @@
       <c r="AC952" s="1"/>
       <c r="AD952" s="1"/>
     </row>
-    <row r="953" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -31014,7 +31030,7 @@
       <c r="AC953" s="1"/>
       <c r="AD953" s="1"/>
     </row>
-    <row r="954" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -31046,7 +31062,7 @@
       <c r="AC954" s="1"/>
       <c r="AD954" s="1"/>
     </row>
-    <row r="955" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -31078,7 +31094,7 @@
       <c r="AC955" s="1"/>
       <c r="AD955" s="1"/>
     </row>
-    <row r="956" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -31110,7 +31126,7 @@
       <c r="AC956" s="1"/>
       <c r="AD956" s="1"/>
     </row>
-    <row r="957" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -31142,7 +31158,7 @@
       <c r="AC957" s="1"/>
       <c r="AD957" s="1"/>
     </row>
-    <row r="958" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -31174,7 +31190,7 @@
       <c r="AC958" s="1"/>
       <c r="AD958" s="1"/>
     </row>
-    <row r="959" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -31206,7 +31222,7 @@
       <c r="AC959" s="1"/>
       <c r="AD959" s="1"/>
     </row>
-    <row r="960" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -31238,7 +31254,7 @@
       <c r="AC960" s="1"/>
       <c r="AD960" s="1"/>
     </row>
-    <row r="961" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -31270,7 +31286,7 @@
       <c r="AC961" s="1"/>
       <c r="AD961" s="1"/>
     </row>
-    <row r="962" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -31302,7 +31318,7 @@
       <c r="AC962" s="1"/>
       <c r="AD962" s="1"/>
     </row>
-    <row r="963" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -31334,7 +31350,7 @@
       <c r="AC963" s="1"/>
       <c r="AD963" s="1"/>
     </row>
-    <row r="964" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31366,7 +31382,7 @@
       <c r="AC964" s="1"/>
       <c r="AD964" s="1"/>
     </row>
-    <row r="965" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31398,7 +31414,7 @@
       <c r="AC965" s="1"/>
       <c r="AD965" s="1"/>
     </row>
-    <row r="966" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31430,7 +31446,7 @@
       <c r="AC966" s="1"/>
       <c r="AD966" s="1"/>
     </row>
-    <row r="967" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31462,7 +31478,7 @@
       <c r="AC967" s="1"/>
       <c r="AD967" s="1"/>
     </row>
-    <row r="968" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31494,7 +31510,7 @@
       <c r="AC968" s="1"/>
       <c r="AD968" s="1"/>
     </row>
-    <row r="969" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31526,7 +31542,7 @@
       <c r="AC969" s="1"/>
       <c r="AD969" s="1"/>
     </row>
-    <row r="970" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31558,7 +31574,7 @@
       <c r="AC970" s="1"/>
       <c r="AD970" s="1"/>
     </row>
-    <row r="971" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31590,7 +31606,7 @@
       <c r="AC971" s="1"/>
       <c r="AD971" s="1"/>
     </row>
-    <row r="972" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31622,7 +31638,7 @@
       <c r="AC972" s="1"/>
       <c r="AD972" s="1"/>
     </row>
-    <row r="973" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31654,7 +31670,7 @@
       <c r="AC973" s="1"/>
       <c r="AD973" s="1"/>
     </row>
-    <row r="974" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31686,7 +31702,7 @@
       <c r="AC974" s="1"/>
       <c r="AD974" s="1"/>
     </row>
-    <row r="975" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31718,7 +31734,7 @@
       <c r="AC975" s="1"/>
       <c r="AD975" s="1"/>
     </row>
-    <row r="976" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31750,7 +31766,7 @@
       <c r="AC976" s="1"/>
       <c r="AD976" s="1"/>
     </row>
-    <row r="977" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31782,7 +31798,7 @@
       <c r="AC977" s="1"/>
       <c r="AD977" s="1"/>
     </row>
-    <row r="978" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31814,7 +31830,7 @@
       <c r="AC978" s="1"/>
       <c r="AD978" s="1"/>
     </row>
-    <row r="979" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31846,7 +31862,7 @@
       <c r="AC979" s="1"/>
       <c r="AD979" s="1"/>
     </row>
-    <row r="980" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31878,7 +31894,7 @@
       <c r="AC980" s="1"/>
       <c r="AD980" s="1"/>
     </row>
-    <row r="981" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31910,7 +31926,7 @@
       <c r="AC981" s="1"/>
       <c r="AD981" s="1"/>
     </row>
-    <row r="982" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31942,7 +31958,7 @@
       <c r="AC982" s="1"/>
       <c r="AD982" s="1"/>
     </row>
-    <row r="983" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31974,7 +31990,7 @@
       <c r="AC983" s="1"/>
       <c r="AD983" s="1"/>
     </row>
-    <row r="984" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -32006,7 +32022,7 @@
       <c r="AC984" s="1"/>
       <c r="AD984" s="1"/>
     </row>
-    <row r="985" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -32038,7 +32054,7 @@
       <c r="AC985" s="1"/>
       <c r="AD985" s="1"/>
     </row>
-    <row r="986" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -32070,7 +32086,7 @@
       <c r="AC986" s="1"/>
       <c r="AD986" s="1"/>
     </row>
-    <row r="987" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -32102,7 +32118,7 @@
       <c r="AC987" s="1"/>
       <c r="AD987" s="1"/>
     </row>
-    <row r="988" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -32134,7 +32150,7 @@
       <c r="AC988" s="1"/>
       <c r="AD988" s="1"/>
     </row>
-    <row r="989" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -32166,7 +32182,7 @@
       <c r="AC989" s="1"/>
       <c r="AD989" s="1"/>
     </row>
-    <row r="990" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -32198,7 +32214,7 @@
       <c r="AC990" s="1"/>
       <c r="AD990" s="1"/>
     </row>
-    <row r="991" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -32230,7 +32246,7 @@
       <c r="AC991" s="1"/>
       <c r="AD991" s="1"/>
     </row>
-    <row r="992" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -32262,7 +32278,7 @@
       <c r="AC992" s="1"/>
       <c r="AD992" s="1"/>
     </row>
-    <row r="993" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -32294,7 +32310,7 @@
       <c r="AC993" s="1"/>
       <c r="AD993" s="1"/>
     </row>
-    <row r="994" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -32326,7 +32342,7 @@
       <c r="AC994" s="1"/>
       <c r="AD994" s="1"/>
     </row>
-    <row r="995" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -32358,7 +32374,7 @@
       <c r="AC995" s="1"/>
       <c r="AD995" s="1"/>
     </row>
-    <row r="996" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32390,7 +32406,7 @@
       <c r="AC996" s="1"/>
       <c r="AD996" s="1"/>
     </row>
-    <row r="997" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32422,7 +32438,7 @@
       <c r="AC997" s="1"/>
       <c r="AD997" s="1"/>
     </row>
-    <row r="998" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32454,7 +32470,7 @@
       <c r="AC998" s="1"/>
       <c r="AD998" s="1"/>
     </row>
-    <row r="999" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32486,7 +32502,7 @@
       <c r="AC999" s="1"/>
       <c r="AD999" s="1"/>
     </row>
-    <row r="1000" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:30" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32520,11 +32536,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="Q2:W2"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="K9:O9"/>
     <mergeCell ref="K10:O10"/>
     <mergeCell ref="G16:I16"/>
@@ -32536,12 +32547,18 @@
     <mergeCell ref="K25:O25"/>
     <mergeCell ref="G4:I14"/>
     <mergeCell ref="K8:O8"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="G16:I16" r:id="rId2" display="SIMULAÇÃO - Transistor  (print)" xr:uid="{125647E5-AE4D-428E-91F7-FD2605979EE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>